--- a/LibroCuentas_PTP_2026.xlsx
+++ b/LibroCuentas_PTP_2026.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="60">
   <si>
     <t>PEÑA TAURINA PEGUERINOS</t>
   </si>
@@ -180,9 +180,6 @@
     <t>si</t>
   </si>
   <si>
-    <t>cuota semswrtral socios</t>
-  </si>
-  <si>
     <t>suscripcion canal tv y cesion de local</t>
   </si>
   <si>
@@ -193,6 +190,21 @@
   </si>
   <si>
     <t>colaboracion socio</t>
+  </si>
+  <si>
+    <t>compras cena inaugural</t>
+  </si>
+  <si>
+    <t>tarjetas boligrafos</t>
+  </si>
+  <si>
+    <t>cuota semestral socios</t>
+  </si>
+  <si>
+    <t>ver ticket caja</t>
+  </si>
+  <si>
+    <t>ver ticklet caja(2)</t>
   </si>
 </sst>
 </file>
@@ -202,7 +214,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ \€"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -364,6 +376,21 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -489,10 +516,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -585,6 +613,51 @@
     <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="22" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="24" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -617,56 +690,15 @@
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="20" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="22" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="24" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -978,34 +1010,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
     </row>
     <row r="2" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
     </row>
     <row r="3" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="33"/>
-      <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="33"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
     </row>
     <row r="4" spans="1:6" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1028,77 +1060,93 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:6" s="63" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="59">
+    <row r="6" spans="1:6" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="44">
         <v>46093</v>
       </c>
-      <c r="B6" s="60" t="s">
+      <c r="B6" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="46"/>
+      <c r="D6" s="47">
+        <v>650</v>
+      </c>
+      <c r="E6" s="47"/>
+      <c r="F6" s="45"/>
+    </row>
+    <row r="7" spans="1:6" s="43" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="39">
+        <v>46100</v>
+      </c>
+      <c r="B7" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="C6" s="61"/>
-      <c r="D6" s="62">
-        <v>650</v>
-      </c>
-      <c r="E6" s="62"/>
-      <c r="F6" s="60"/>
-    </row>
-    <row r="7" spans="1:6" s="58" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="54">
-        <v>46100</v>
-      </c>
-      <c r="B7" s="55" t="s">
+      <c r="C7" s="41"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="40" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="35">
+        <v>46106</v>
+      </c>
+      <c r="B8" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="C7" s="56"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57"/>
-      <c r="F7" s="55" t="s">
+      <c r="C8" s="64" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37">
+        <v>150</v>
+      </c>
+      <c r="F8" s="36"/>
+    </row>
+    <row r="9" spans="1:6" s="43" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="39">
+        <v>46134</v>
+      </c>
+      <c r="B9" s="40" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="41"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="40" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="35">
+        <v>46138</v>
+      </c>
+      <c r="B10" s="36" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" s="53" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="49">
-        <v>46106</v>
-      </c>
-      <c r="B8" s="50" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" s="51"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52">
-        <v>150</v>
-      </c>
-      <c r="F8" s="50"/>
-    </row>
-    <row r="9" spans="1:6" s="58" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="54">
-        <v>46134</v>
-      </c>
-      <c r="B9" s="55" t="s">
+      <c r="C10" s="64" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="37"/>
+      <c r="E10" s="37">
+        <v>130</v>
+      </c>
+      <c r="F10" s="36"/>
+    </row>
+    <row r="11" spans="1:6" s="43" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="39">
+        <v>46139</v>
+      </c>
+      <c r="B11" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="41"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="56"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="55" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="3"/>
-    </row>
-    <row r="11" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="6"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="7"/>
     </row>
     <row r="12" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
@@ -1374,33 +1422,33 @@
     </row>
     <row r="46" spans="1:6" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="47" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="34" t="s">
+      <c r="A47" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="B47" s="35"/>
-      <c r="C47" s="36"/>
+      <c r="B47" s="52"/>
+      <c r="C47" s="53"/>
       <c r="D47" s="10">
         <f>SUM(D6:D45)</f>
         <v>650</v>
       </c>
       <c r="E47" s="10">
         <f>SUM(E6:E45)</f>
-        <v>150</v>
+        <v>280</v>
       </c>
       <c r="F47" s="11">
         <f>D47-E47</f>
-        <v>500</v>
+        <v>370</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A48" s="39" t="s">
+      <c r="A48" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="B48" s="40"/>
-      <c r="C48" s="41"/>
+      <c r="B48" s="57"/>
+      <c r="C48" s="58"/>
       <c r="F48" s="12">
         <f>D47-E47</f>
-        <v>500</v>
+        <v>370</v>
       </c>
     </row>
   </sheetData>
@@ -1411,7 +1459,12 @@
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A48:C48"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C8" r:id="rId1"/>
+    <hyperlink ref="C10" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -1425,20 +1478,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
     </row>
     <row r="2" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
     </row>
     <row r="3" spans="1:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1496,8 +1549,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="14">
-        <f t="shared" si="0"/>
-        <v>-150</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1561,7 +1613,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="42" t="s">
+      <c r="A12" s="63" t="s">
         <v>22</v>
       </c>
       <c r="B12" s="17">
@@ -1569,12 +1621,10 @@
         <v>650</v>
       </c>
       <c r="C12" s="17">
-        <f>SUM(C5:C11)</f>
-        <v>150</v>
+        <v>280</v>
       </c>
       <c r="D12" s="17">
-        <f>SUM(D5:D11)</f>
-        <v>500</v>
+        <v>370</v>
       </c>
     </row>
   </sheetData>
@@ -1599,26 +1649,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
     </row>
     <row r="2" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
     </row>
     <row r="3" spans="1:7" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1640,7 +1690,7 @@
       <c r="F4" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="46" t="s">
+      <c r="G4" s="32" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1654,7 +1704,7 @@
       <c r="C5" s="9">
         <v>50</v>
       </c>
-      <c r="D5" s="48" t="s">
+      <c r="D5" s="34" t="s">
         <v>50</v>
       </c>
       <c r="E5" s="9">
@@ -1664,7 +1714,7 @@
         <v>33</v>
       </c>
       <c r="G5" s="20" t="str">
-        <f t="shared" ref="G5:G17" si="0">IF(AND(D5="Sí",F5="Sí"),"✓ Al corriente",IF(OR(D5="Sí",F5="Sí"),"Parcial","Pendiente"))</f>
+        <f t="shared" ref="G5:G15" si="0">IF(AND(D5="Sí",F5="Sí"),"✓ Al corriente",IF(OR(D5="Sí",F5="Sí"),"Parcial","Pendiente"))</f>
         <v>Pendiente</v>
       </c>
     </row>
@@ -1678,7 +1728,7 @@
       <c r="C6" s="5">
         <v>50</v>
       </c>
-      <c r="D6" s="47" t="s">
+      <c r="D6" s="33" t="s">
         <v>50</v>
       </c>
       <c r="E6" s="5">
@@ -1702,7 +1752,7 @@
       <c r="C7" s="9">
         <v>50</v>
       </c>
-      <c r="D7" s="48" t="s">
+      <c r="D7" s="34" t="s">
         <v>50</v>
       </c>
       <c r="E7" s="9">
@@ -1726,7 +1776,7 @@
       <c r="C8" s="5">
         <v>50</v>
       </c>
-      <c r="D8" s="47" t="s">
+      <c r="D8" s="33" t="s">
         <v>50</v>
       </c>
       <c r="E8" s="5">
@@ -1750,7 +1800,7 @@
       <c r="C9" s="9">
         <v>50</v>
       </c>
-      <c r="D9" s="48" t="s">
+      <c r="D9" s="34" t="s">
         <v>50</v>
       </c>
       <c r="E9" s="9">
@@ -1774,7 +1824,7 @@
       <c r="C10" s="5">
         <v>50</v>
       </c>
-      <c r="D10" s="47" t="s">
+      <c r="D10" s="33" t="s">
         <v>50</v>
       </c>
       <c r="E10" s="5">
@@ -1798,7 +1848,7 @@
       <c r="C11" s="9">
         <v>50</v>
       </c>
-      <c r="D11" s="48" t="s">
+      <c r="D11" s="34" t="s">
         <v>50</v>
       </c>
       <c r="E11" s="9">
@@ -1822,7 +1872,7 @@
       <c r="C12" s="5">
         <v>50</v>
       </c>
-      <c r="D12" s="47" t="s">
+      <c r="D12" s="33" t="s">
         <v>50</v>
       </c>
       <c r="E12" s="5">
@@ -1846,7 +1896,7 @@
       <c r="C13" s="9">
         <v>50</v>
       </c>
-      <c r="D13" s="48" t="s">
+      <c r="D13" s="34" t="s">
         <v>50</v>
       </c>
       <c r="E13" s="9">
@@ -1870,7 +1920,7 @@
       <c r="C14" s="5">
         <v>50</v>
       </c>
-      <c r="D14" s="47" t="s">
+      <c r="D14" s="33" t="s">
         <v>50</v>
       </c>
       <c r="E14" s="5">
@@ -1955,10 +2005,10 @@
       </c>
     </row>
     <row r="18" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="42" t="s">
+      <c r="A18" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="B18" s="33"/>
+      <c r="B18" s="50"/>
       <c r="C18" s="17">
         <f>SUM(C5:C17)</f>
         <v>650</v>

--- a/LibroCuentas_PTP_2026.xlsx
+++ b/LibroCuentas_PTP_2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22575" windowHeight="7395"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22575" windowHeight="7395" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Registro 2026" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="68">
   <si>
     <t>PEÑA TAURINA PEGUERINOS</t>
   </si>
@@ -222,6 +222,15 @@
   </si>
   <si>
     <t>Si</t>
+  </si>
+  <si>
+    <t>Venta Loteria</t>
+  </si>
+  <si>
+    <t>Victor Perez</t>
+  </si>
+  <si>
+    <t>AntonioRosado</t>
   </si>
 </sst>
 </file>
@@ -231,7 +240,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ \€"/>
   </numFmts>
-  <fonts count="32" x14ac:knownFonts="1">
+  <fonts count="34" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -432,6 +441,21 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -469,7 +493,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -556,30 +580,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FF7A0000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF7A0000"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF7A0000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF7A0000"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF7A0000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -621,7 +621,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -673,48 +673,6 @@
     </xf>
     <xf numFmtId="164" fontId="12" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="20" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -761,6 +719,17 @@
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -793,51 +762,90 @@
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="33" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1208,42 +1216,42 @@
   <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12" style="46" customWidth="1"/>
-    <col min="2" max="2" width="32" style="46" customWidth="1"/>
-    <col min="3" max="3" width="18" style="46" customWidth="1"/>
-    <col min="4" max="5" width="16" style="46" customWidth="1"/>
-    <col min="6" max="6" width="30" style="46" customWidth="1"/>
+    <col min="1" max="1" width="12" style="32" customWidth="1"/>
+    <col min="2" max="2" width="32" style="32" customWidth="1"/>
+    <col min="3" max="3" width="18" style="32" customWidth="1"/>
+    <col min="4" max="5" width="16" style="32" customWidth="1"/>
+    <col min="6" max="6" width="30" style="32" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
     </row>
     <row r="2" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
     </row>
     <row r="3" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
     </row>
     <row r="4" spans="1:6" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1266,101 +1274,107 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:6" s="45" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="41">
+    <row r="6" spans="1:6" s="31" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="27">
         <v>46093</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="43"/>
-      <c r="D6" s="44">
+      <c r="C6" s="29"/>
+      <c r="D6" s="30">
         <v>700</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="42"/>
-    </row>
-    <row r="7" spans="1:6" s="40" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="36">
+      <c r="E6" s="30"/>
+      <c r="F6" s="28"/>
+    </row>
+    <row r="7" spans="1:6" s="26" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="22">
         <v>46100</v>
       </c>
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="38"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="37" t="s">
+      <c r="C7" s="24"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="23" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:6" s="35" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="32">
+    <row r="8" spans="1:6" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="18">
         <v>46106</v>
       </c>
-      <c r="B8" s="33" t="s">
+      <c r="B8" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="48" t="s">
+      <c r="C8" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="34"/>
-      <c r="E8" s="34">
+      <c r="D8" s="20"/>
+      <c r="E8" s="20">
         <v>150</v>
       </c>
-      <c r="F8" s="33"/>
-    </row>
-    <row r="9" spans="1:6" s="40" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="36">
+      <c r="F8" s="19"/>
+    </row>
+    <row r="9" spans="1:6" s="26" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="22">
         <v>46134</v>
       </c>
-      <c r="B9" s="37" t="s">
+      <c r="B9" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="38"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="37" t="s">
+      <c r="C9" s="24"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="23" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="35" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="32">
+    <row r="10" spans="1:6" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="18">
         <v>46138</v>
       </c>
-      <c r="B10" s="33" t="s">
+      <c r="B10" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="47" t="s">
+      <c r="C10" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="34"/>
-      <c r="E10" s="34">
+      <c r="D10" s="20"/>
+      <c r="E10" s="20">
         <v>130</v>
       </c>
-      <c r="F10" s="33"/>
-    </row>
-    <row r="11" spans="1:6" s="40" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="36">
+      <c r="F10" s="19"/>
+    </row>
+    <row r="11" spans="1:6" s="26" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="22">
         <v>46139</v>
       </c>
-      <c r="B11" s="37" t="s">
+      <c r="B11" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="38"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="37" t="s">
+      <c r="C11" s="24"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="23" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="3"/>
+    <row r="12" spans="1:6" s="87" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="83">
+        <v>46158</v>
+      </c>
+      <c r="B12" s="84" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="85"/>
+      <c r="D12" s="86">
+        <v>27.5</v>
+      </c>
+      <c r="E12" s="86"/>
+      <c r="F12" s="84"/>
     </row>
     <row r="13" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6"/>
@@ -1628,14 +1642,14 @@
     </row>
     <row r="46" spans="1:6" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="47" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="53" t="s">
+      <c r="A47" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="B47" s="54"/>
-      <c r="C47" s="55"/>
+      <c r="B47" s="45"/>
+      <c r="C47" s="46"/>
       <c r="D47" s="10">
         <f>SUM(D6:D45)</f>
-        <v>700</v>
+        <v>727.5</v>
       </c>
       <c r="E47" s="10">
         <f>SUM(E6:E45)</f>
@@ -1643,18 +1657,18 @@
       </c>
       <c r="F47" s="11">
         <f>D47-E47</f>
-        <v>420</v>
+        <v>447.5</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="58" t="s">
+      <c r="A48" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="B48" s="59"/>
-      <c r="C48" s="60"/>
+      <c r="B48" s="50"/>
+      <c r="C48" s="51"/>
       <c r="F48" s="12">
         <f>D47-E47</f>
-        <v>420</v>
+        <v>447.5</v>
       </c>
     </row>
   </sheetData>
@@ -1670,7 +1684,7 @@
     <hyperlink ref="C10" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1679,25 +1693,25 @@
   <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28" style="46" customWidth="1"/>
-    <col min="2" max="4" width="18" style="46" customWidth="1"/>
+    <col min="1" max="1" width="28" style="32" customWidth="1"/>
+    <col min="2" max="4" width="18" style="32" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
     </row>
     <row r="2" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
     </row>
     <row r="3" spans="1:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1719,14 +1733,14 @@
         <v>24</v>
       </c>
       <c r="B5" s="9">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="C5" s="9">
         <v>0</v>
       </c>
       <c r="D5" s="14">
         <f>B5-C5</f>
-        <v>0</v>
+        <v>800</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1819,12 +1833,12 @@
       </c>
     </row>
     <row r="12" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="61" t="s">
+      <c r="A12" s="52" t="s">
         <v>31</v>
       </c>
       <c r="B12" s="17">
         <f>SUM(B5:B11)</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="C12" s="17">
         <v>280</v>
@@ -1845,382 +1859,757 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6" style="46" customWidth="1"/>
-    <col min="2" max="2" width="30" style="46" customWidth="1"/>
-    <col min="3" max="6" width="14" style="46" customWidth="1"/>
-    <col min="7" max="7" width="16" style="46" customWidth="1"/>
+    <col min="1" max="1" width="6" style="32" customWidth="1"/>
+    <col min="2" max="2" width="30" style="32" customWidth="1"/>
+    <col min="3" max="6" width="14" style="32" customWidth="1"/>
+    <col min="7" max="7" width="16" style="32" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="53" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
     </row>
     <row r="2" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="55" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
     </row>
     <row r="3" spans="1:7" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="57" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="57" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="57" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="57" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="G4" s="29" t="s">
+      <c r="G4" s="58" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="19">
+      <c r="A5" s="59">
         <v>1</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="9">
-        <v>50</v>
-      </c>
-      <c r="D5" s="31" t="s">
+      <c r="C5" s="61">
+        <v>50</v>
+      </c>
+      <c r="D5" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="E5" s="9">
-        <v>50</v>
-      </c>
-      <c r="F5" s="8" t="s">
+      <c r="E5" s="61">
+        <v>50</v>
+      </c>
+      <c r="F5" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="G5" s="20"/>
-    </row>
-    <row r="6" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="21">
-        <v>2</v>
-      </c>
-      <c r="B6" s="15" t="s">
+      <c r="G5" s="64"/>
+    </row>
+    <row r="6" spans="1:7" s="37" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="59"/>
+      <c r="B6" s="60"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="64"/>
+    </row>
+    <row r="7" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="39">
+        <v>3</v>
+      </c>
+      <c r="B7" s="65" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="5">
-        <v>50</v>
-      </c>
-      <c r="D6" s="30" t="s">
+      <c r="C7" s="66">
+        <v>50</v>
+      </c>
+      <c r="D7" s="67" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="5">
-        <v>50</v>
-      </c>
-      <c r="F6" s="4" t="s">
+      <c r="E7" s="66">
+        <v>50</v>
+      </c>
+      <c r="F7" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="G6" s="22"/>
-    </row>
-    <row r="7" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="19">
-        <v>3</v>
-      </c>
-      <c r="B7" s="13" t="s">
+      <c r="G7" s="69"/>
+    </row>
+    <row r="8" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="59">
+        <v>4</v>
+      </c>
+      <c r="B8" s="60" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="9">
-        <v>50</v>
-      </c>
-      <c r="D7" s="31" t="s">
+      <c r="C8" s="61">
+        <v>50</v>
+      </c>
+      <c r="D8" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="E7" s="9">
-        <v>50</v>
-      </c>
-      <c r="F7" s="8" t="s">
+      <c r="E8" s="61">
+        <v>50</v>
+      </c>
+      <c r="F8" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="20"/>
-    </row>
-    <row r="8" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="21">
-        <v>4</v>
-      </c>
-      <c r="B8" s="15" t="s">
+      <c r="G8" s="64"/>
+    </row>
+    <row r="9" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="39">
+        <v>5</v>
+      </c>
+      <c r="B9" s="65" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="5">
-        <v>50</v>
-      </c>
-      <c r="D8" s="30" t="s">
+      <c r="C9" s="66">
+        <v>50</v>
+      </c>
+      <c r="D9" s="67" t="s">
         <v>42</v>
       </c>
-      <c r="E8" s="5">
-        <v>50</v>
-      </c>
-      <c r="F8" s="4" t="s">
+      <c r="E9" s="66">
+        <v>50</v>
+      </c>
+      <c r="F9" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="G8" s="22"/>
-    </row>
-    <row r="9" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="19">
-        <v>5</v>
-      </c>
-      <c r="B9" s="13" t="s">
+      <c r="G9" s="69"/>
+    </row>
+    <row r="10" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="59">
+        <v>6</v>
+      </c>
+      <c r="B10" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="9">
-        <v>50</v>
-      </c>
-      <c r="D9" s="31" t="s">
+      <c r="C10" s="61">
+        <v>50</v>
+      </c>
+      <c r="D10" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="E9" s="9">
-        <v>50</v>
-      </c>
-      <c r="F9" s="8" t="s">
+      <c r="E10" s="61">
+        <v>50</v>
+      </c>
+      <c r="F10" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="G9" s="20"/>
-    </row>
-    <row r="10" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="21">
-        <v>6</v>
-      </c>
-      <c r="B10" s="15" t="s">
+      <c r="G10" s="64"/>
+    </row>
+    <row r="11" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="39">
+        <v>7</v>
+      </c>
+      <c r="B11" s="65" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="5">
-        <v>50</v>
-      </c>
-      <c r="D10" s="30" t="s">
+      <c r="C11" s="66">
+        <v>50</v>
+      </c>
+      <c r="D11" s="67" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="5">
-        <v>50</v>
-      </c>
-      <c r="F10" s="4" t="s">
+      <c r="E11" s="66">
+        <v>50</v>
+      </c>
+      <c r="F11" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="G10" s="22"/>
-    </row>
-    <row r="11" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="19">
-        <v>7</v>
-      </c>
-      <c r="B11" s="13" t="s">
+      <c r="G11" s="69"/>
+    </row>
+    <row r="12" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="59">
+        <v>8</v>
+      </c>
+      <c r="B12" s="60" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="9">
-        <v>50</v>
-      </c>
-      <c r="D11" s="31" t="s">
+      <c r="C12" s="61">
+        <v>50</v>
+      </c>
+      <c r="D12" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="9">
-        <v>50</v>
-      </c>
-      <c r="F11" s="8" t="s">
+      <c r="E12" s="61">
+        <v>50</v>
+      </c>
+      <c r="F12" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="G11" s="20"/>
-    </row>
-    <row r="12" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="21">
-        <v>8</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" s="5">
-        <v>50</v>
-      </c>
-      <c r="D12" s="30" t="s">
+      <c r="G12" s="64"/>
+    </row>
+    <row r="13" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="39">
+        <v>9</v>
+      </c>
+      <c r="B13" s="65" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="66">
+        <v>50</v>
+      </c>
+      <c r="D13" s="67" t="s">
         <v>42</v>
       </c>
-      <c r="E12" s="5">
-        <v>50</v>
-      </c>
-      <c r="F12" s="4" t="s">
+      <c r="E13" s="66">
+        <v>50</v>
+      </c>
+      <c r="F13" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="G12" s="22"/>
-    </row>
-    <row r="13" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="19">
-        <v>9</v>
-      </c>
-      <c r="B13" s="13" t="s">
+      <c r="G13" s="69"/>
+    </row>
+    <row r="14" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="59">
+        <v>10</v>
+      </c>
+      <c r="B14" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="9">
-        <v>50</v>
-      </c>
-      <c r="D13" s="31" t="s">
+      <c r="C14" s="61">
+        <v>50</v>
+      </c>
+      <c r="D14" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="E13" s="9">
-        <v>50</v>
-      </c>
-      <c r="F13" s="8" t="s">
+      <c r="E14" s="61">
+        <v>50</v>
+      </c>
+      <c r="F14" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="G13" s="20"/>
-    </row>
-    <row r="14" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="21">
-        <v>10</v>
-      </c>
-      <c r="B14" s="15" t="s">
+      <c r="G14" s="64"/>
+    </row>
+    <row r="15" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="39">
+        <v>11</v>
+      </c>
+      <c r="B15" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="5">
-        <v>50</v>
-      </c>
-      <c r="D14" s="30" t="s">
+      <c r="C15" s="66">
+        <v>50</v>
+      </c>
+      <c r="D15" s="67" t="s">
         <v>42</v>
       </c>
-      <c r="E14" s="5">
-        <v>50</v>
-      </c>
-      <c r="F14" s="4" t="s">
+      <c r="E15" s="66">
+        <v>50</v>
+      </c>
+      <c r="F15" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="G14" s="22"/>
-    </row>
-    <row r="15" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="19">
-        <v>11</v>
-      </c>
-      <c r="B15" s="13" t="s">
+      <c r="G15" s="69"/>
+    </row>
+    <row r="16" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="59">
+        <v>12</v>
+      </c>
+      <c r="B16" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="9">
-        <v>50</v>
-      </c>
-      <c r="D15" s="8" t="s">
+      <c r="C16" s="61">
+        <v>50</v>
+      </c>
+      <c r="D16" s="63" t="s">
         <v>54</v>
       </c>
-      <c r="E15" s="9">
-        <v>50</v>
-      </c>
-      <c r="F15" s="8" t="s">
+      <c r="E16" s="61">
+        <v>50</v>
+      </c>
+      <c r="F16" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="G15" s="20"/>
-    </row>
-    <row r="16" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="19">
+      <c r="G16" s="64"/>
+    </row>
+    <row r="17" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="59">
         <v>13</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B17" s="70" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="24">
-        <v>50</v>
-      </c>
-      <c r="D16" s="25" t="s">
+      <c r="C17" s="71">
+        <v>50</v>
+      </c>
+      <c r="D17" s="72" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="24">
-        <v>50</v>
-      </c>
-      <c r="F16" s="25" t="s">
+      <c r="E17" s="71">
+        <v>50</v>
+      </c>
+      <c r="F17" s="72" t="s">
         <v>43</v>
       </c>
-      <c r="G16" s="26"/>
-    </row>
-    <row r="17" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="75">
+      <c r="G17" s="73"/>
+    </row>
+    <row r="18" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="39">
         <v>14</v>
       </c>
-      <c r="B17" s="27" t="s">
+      <c r="B18" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="C17" s="77">
-        <v>50</v>
-      </c>
-      <c r="D17" s="79" t="s">
+      <c r="C18" s="40">
+        <v>50</v>
+      </c>
+      <c r="D18" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="E17" s="77">
-        <v>50</v>
-      </c>
-      <c r="F17" s="79" t="s">
+      <c r="E18" s="40">
+        <v>50</v>
+      </c>
+      <c r="F18" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="G17" s="28"/>
-    </row>
-    <row r="18" spans="1:7" s="74" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="76">
+      <c r="G18" s="75"/>
+    </row>
+    <row r="19" spans="1:7" s="38" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="39">
         <v>15</v>
       </c>
-      <c r="B18" s="70" t="s">
+      <c r="B19" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="C18" s="78">
-        <v>50</v>
-      </c>
-      <c r="D18" s="80" t="s">
+      <c r="C19" s="40">
+        <v>50</v>
+      </c>
+      <c r="D19" s="41" t="s">
         <v>64</v>
       </c>
-      <c r="E18" s="78">
-        <v>50</v>
-      </c>
-      <c r="F18" s="80" t="s">
+      <c r="E19" s="40">
+        <v>50</v>
+      </c>
+      <c r="F19" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="G18" s="81"/>
-    </row>
-    <row r="19" spans="1:7" s="46" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="69"/>
-      <c r="B19" s="70"/>
-      <c r="C19" s="71"/>
-      <c r="D19" s="72"/>
-      <c r="E19" s="71"/>
-      <c r="F19" s="72"/>
-      <c r="G19" s="73"/>
-    </row>
-    <row r="20" spans="1:7" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="65" t="s">
+      <c r="G19" s="76"/>
+    </row>
+    <row r="20" spans="1:7" s="37" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="39">
+        <v>16</v>
+      </c>
+      <c r="B20" s="74" t="s">
+        <v>66</v>
+      </c>
+      <c r="C20" s="40">
+        <v>50</v>
+      </c>
+      <c r="D20" s="41" t="s">
+        <v>64</v>
+      </c>
+      <c r="E20" s="40">
+        <v>50</v>
+      </c>
+      <c r="F20" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="G20" s="75"/>
+    </row>
+    <row r="21" spans="1:7" s="56" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="39">
+        <v>17</v>
+      </c>
+      <c r="B21" s="74" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="40">
+        <v>50</v>
+      </c>
+      <c r="D21" s="41" t="s">
+        <v>64</v>
+      </c>
+      <c r="E21" s="40">
+        <v>50</v>
+      </c>
+      <c r="F21" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="G21" s="76"/>
+    </row>
+    <row r="22" spans="1:7" s="56" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="39"/>
+      <c r="B22" s="74"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="40"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="76"/>
+    </row>
+    <row r="23" spans="1:7" s="32" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="39"/>
+      <c r="B23" s="74"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="40"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="75"/>
+    </row>
+    <row r="24" spans="1:7" s="37" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="39"/>
+      <c r="B24" s="74"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="75"/>
+    </row>
+    <row r="25" spans="1:7" s="37" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="39"/>
+      <c r="B25" s="74"/>
+      <c r="C25" s="40"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="75"/>
+    </row>
+    <row r="26" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="77" t="s">
         <v>58</v>
       </c>
-      <c r="B20" s="66"/>
-      <c r="C20" s="67">
-        <v>700</v>
-      </c>
-      <c r="D20" s="68"/>
-      <c r="E20" s="67">
+      <c r="B26" s="78"/>
+      <c r="C26" s="79">
+        <v>800</v>
+      </c>
+      <c r="D26" s="80"/>
+      <c r="E26" s="79">
         <v>0</v>
       </c>
-      <c r="F20" s="68"/>
-      <c r="G20" s="68"/>
+      <c r="F26" s="80"/>
+      <c r="G26" s="80"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="81"/>
+      <c r="B27" s="81"/>
+      <c r="C27" s="82"/>
+      <c r="D27" s="81"/>
+      <c r="E27" s="81"/>
+      <c r="F27" s="81"/>
+      <c r="G27" s="81"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="81"/>
+      <c r="B28" s="81"/>
+      <c r="C28" s="81"/>
+      <c r="D28" s="81"/>
+      <c r="E28" s="81"/>
+      <c r="F28" s="81"/>
+      <c r="G28" s="81"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="81"/>
+      <c r="B29" s="81"/>
+      <c r="C29" s="81"/>
+      <c r="D29" s="81"/>
+      <c r="E29" s="81"/>
+      <c r="F29" s="81"/>
+      <c r="G29" s="81"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="81"/>
+      <c r="B30" s="81"/>
+      <c r="C30" s="81"/>
+      <c r="D30" s="81"/>
+      <c r="E30" s="81"/>
+      <c r="F30" s="81"/>
+      <c r="G30" s="81"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="81"/>
+      <c r="B31" s="81"/>
+      <c r="C31" s="81"/>
+      <c r="D31" s="81"/>
+      <c r="E31" s="81"/>
+      <c r="F31" s="81"/>
+      <c r="G31" s="81"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="81"/>
+      <c r="B32" s="81"/>
+      <c r="C32" s="81"/>
+      <c r="D32" s="81"/>
+      <c r="E32" s="81"/>
+      <c r="F32" s="81"/>
+      <c r="G32" s="81"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="81"/>
+      <c r="B33" s="81"/>
+      <c r="C33" s="81"/>
+      <c r="D33" s="81"/>
+      <c r="E33" s="81"/>
+      <c r="F33" s="81"/>
+      <c r="G33" s="81"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="81"/>
+      <c r="B34" s="81"/>
+      <c r="C34" s="81"/>
+      <c r="D34" s="81"/>
+      <c r="E34" s="81"/>
+      <c r="F34" s="81"/>
+      <c r="G34" s="81"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="81"/>
+      <c r="B35" s="81"/>
+      <c r="C35" s="81"/>
+      <c r="D35" s="81"/>
+      <c r="E35" s="81"/>
+      <c r="F35" s="81"/>
+      <c r="G35" s="81"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="81"/>
+      <c r="B36" s="81"/>
+      <c r="C36" s="81"/>
+      <c r="D36" s="81"/>
+      <c r="E36" s="81"/>
+      <c r="F36" s="81"/>
+      <c r="G36" s="81"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="81"/>
+      <c r="B37" s="81"/>
+      <c r="C37" s="81"/>
+      <c r="D37" s="81"/>
+      <c r="E37" s="81"/>
+      <c r="F37" s="81"/>
+      <c r="G37" s="81"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="81"/>
+      <c r="B38" s="81"/>
+      <c r="C38" s="81"/>
+      <c r="D38" s="81"/>
+      <c r="E38" s="81"/>
+      <c r="F38" s="81"/>
+      <c r="G38" s="81"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="81"/>
+      <c r="B39" s="81"/>
+      <c r="C39" s="81"/>
+      <c r="D39" s="81"/>
+      <c r="E39" s="81"/>
+      <c r="F39" s="81"/>
+      <c r="G39" s="81"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="81"/>
+      <c r="B40" s="81"/>
+      <c r="C40" s="81"/>
+      <c r="D40" s="81"/>
+      <c r="E40" s="81"/>
+      <c r="F40" s="81"/>
+      <c r="G40" s="81"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="81"/>
+      <c r="B41" s="81"/>
+      <c r="C41" s="81"/>
+      <c r="D41" s="81"/>
+      <c r="E41" s="81"/>
+      <c r="F41" s="81"/>
+      <c r="G41" s="81"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="81"/>
+      <c r="B42" s="81"/>
+      <c r="C42" s="81"/>
+      <c r="D42" s="81"/>
+      <c r="E42" s="81"/>
+      <c r="F42" s="81"/>
+      <c r="G42" s="81"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="81"/>
+      <c r="B43" s="81"/>
+      <c r="C43" s="81"/>
+      <c r="D43" s="81"/>
+      <c r="E43" s="81"/>
+      <c r="F43" s="81"/>
+      <c r="G43" s="81"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="81"/>
+      <c r="B44" s="81"/>
+      <c r="C44" s="81"/>
+      <c r="D44" s="81"/>
+      <c r="E44" s="81"/>
+      <c r="F44" s="81"/>
+      <c r="G44" s="81"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="81"/>
+      <c r="B45" s="81"/>
+      <c r="C45" s="81"/>
+      <c r="D45" s="81"/>
+      <c r="E45" s="81"/>
+      <c r="F45" s="81"/>
+      <c r="G45" s="81"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="81"/>
+      <c r="B46" s="81"/>
+      <c r="C46" s="81"/>
+      <c r="D46" s="81"/>
+      <c r="E46" s="81"/>
+      <c r="F46" s="81"/>
+      <c r="G46" s="81"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="81"/>
+      <c r="B47" s="81"/>
+      <c r="C47" s="81"/>
+      <c r="D47" s="81"/>
+      <c r="E47" s="81"/>
+      <c r="F47" s="81"/>
+      <c r="G47" s="81"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="81"/>
+      <c r="B48" s="81"/>
+      <c r="C48" s="81"/>
+      <c r="D48" s="81"/>
+      <c r="E48" s="81"/>
+      <c r="F48" s="81"/>
+      <c r="G48" s="81"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="81"/>
+      <c r="B49" s="81"/>
+      <c r="C49" s="81"/>
+      <c r="D49" s="81"/>
+      <c r="E49" s="81"/>
+      <c r="F49" s="81"/>
+      <c r="G49" s="81"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="81"/>
+      <c r="B50" s="81"/>
+      <c r="C50" s="81"/>
+      <c r="D50" s="81"/>
+      <c r="E50" s="81"/>
+      <c r="F50" s="81"/>
+      <c r="G50" s="81"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="81"/>
+      <c r="B51" s="81"/>
+      <c r="C51" s="81"/>
+      <c r="D51" s="81"/>
+      <c r="E51" s="81"/>
+      <c r="F51" s="81"/>
+      <c r="G51" s="81"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="81"/>
+      <c r="B52" s="81"/>
+      <c r="C52" s="81"/>
+      <c r="D52" s="81"/>
+      <c r="E52" s="81"/>
+      <c r="F52" s="81"/>
+      <c r="G52" s="81"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="81"/>
+      <c r="B53" s="81"/>
+      <c r="C53" s="81"/>
+      <c r="D53" s="81"/>
+      <c r="E53" s="81"/>
+      <c r="F53" s="81"/>
+      <c r="G53" s="81"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="81"/>
+      <c r="B54" s="81"/>
+      <c r="C54" s="81"/>
+      <c r="D54" s="81"/>
+      <c r="E54" s="81"/>
+      <c r="F54" s="81"/>
+      <c r="G54" s="81"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="81"/>
+      <c r="B55" s="81"/>
+      <c r="C55" s="81"/>
+      <c r="D55" s="81"/>
+      <c r="E55" s="81"/>
+      <c r="F55" s="81"/>
+      <c r="G55" s="81"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="81"/>
+      <c r="B56" s="81"/>
+      <c r="C56" s="81"/>
+      <c r="D56" s="81"/>
+      <c r="E56" s="81"/>
+      <c r="F56" s="81"/>
+      <c r="G56" s="81"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="81"/>
+      <c r="B57" s="81"/>
+      <c r="C57" s="81"/>
+      <c r="D57" s="81"/>
+      <c r="E57" s="81"/>
+      <c r="F57" s="81"/>
+      <c r="G57" s="81"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="81"/>
+      <c r="B58" s="81"/>
+      <c r="C58" s="81"/>
+      <c r="D58" s="81"/>
+      <c r="E58" s="81"/>
+      <c r="F58" s="81"/>
+      <c r="G58" s="81"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="81"/>
+      <c r="B59" s="81"/>
+      <c r="C59" s="81"/>
+      <c r="D59" s="81"/>
+      <c r="E59" s="81"/>
+      <c r="F59" s="81"/>
+      <c r="G59" s="81"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A26:B26"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
@@ -2234,16 +2623,16 @@
   <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="55" style="46" customWidth="1"/>
+    <col min="1" max="1" width="55" style="32" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="35" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="36" t="s">
         <v>60</v>
       </c>
     </row>
@@ -2259,16 +2648,16 @@
   <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="80" style="46" customWidth="1"/>
+    <col min="1" max="1" width="80" style="32" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="35" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="36" t="s">
         <v>62</v>
       </c>
     </row>

--- a/LibroCuentas_PTP_2026.xlsx
+++ b/LibroCuentas_PTP_2026.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="103">
   <si>
     <t xml:space="preserve">PEÑA TAURINA PEGUERINOS</t>
   </si>
@@ -98,6 +98,9 @@
   </si>
   <si>
     <t xml:space="preserve">📊 TOTAL PARCIAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saldo →</t>
   </si>
   <si>
     <t xml:space="preserve">TOTALES</t>
@@ -349,7 +352,7 @@
     <numFmt numFmtId="167" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="168" formatCode="General"/>
   </numFmts>
-  <fonts count="47">
+  <fonts count="48">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -477,8 +480,9 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
       <sz val="11"/>
-      <color rgb="FF003399"/>
+      <color rgb="FF000000"/>
       <name val="Cambria"/>
       <family val="0"/>
       <charset val="1"/>
@@ -494,7 +498,7 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Cambria"/>
       <family val="0"/>
       <charset val="1"/>
@@ -560,6 +564,13 @@
       <sz val="11"/>
       <color rgb="FF7A0000"/>
       <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF003399"/>
+      <name val="Cambria"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -748,14 +759,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFF5F0E8"/>
+        <fgColor rgb="FFA00000"/>
+        <bgColor rgb="FF9B0000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA00000"/>
-        <bgColor rgb="FF9B0000"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFF5F0E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -905,7 +916,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="119">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1022,83 +1033,63 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="17" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="20" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="20" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="21" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="19" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1110,27 +1101,63 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="21" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="19" fillId="8" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="21" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="19" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="21" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="17" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="20" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="20" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="17" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="8" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="20" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="21" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="21" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="167" fontId="22" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="22" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="22" fillId="8" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1138,7 +1165,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="23" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="23" fillId="8" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1154,6 +1181,14 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="24" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1166,14 +1201,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="166" fontId="21" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1186,35 +1213,35 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="28" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="17" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="28" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="30" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="31" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1222,43 +1249,43 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="3" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="33" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="34" fillId="3" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="8" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="8" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="35" fillId="3" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="36" fillId="9" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="9" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="20" fillId="8" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="20" fillId="9" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="8" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="8" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="37" fillId="8" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="35" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="37" fillId="9" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="9" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="9" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="36" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1270,7 +1297,7 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="37" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1278,43 +1305,43 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="37" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="38" fillId="8" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="38" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="39" fillId="9" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="38" fillId="8" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="39" fillId="9" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="38" fillId="8" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="39" fillId="8" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="38" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="39" fillId="9" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="40" fillId="9" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="39" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="38" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="39" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="38" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="39" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="40" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="41" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1322,11 +1349,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="41" fillId="3" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="41" fillId="9" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="42" fillId="3" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="42" fillId="8" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1342,10 +1369,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1354,15 +1377,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1449,9 +1476,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>3327120</xdr:colOff>
+      <xdr:colOff>3324960</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>127080</xdr:rowOff>
+      <xdr:rowOff>124920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1465,7 +1492,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="600120"/>
-          <a:ext cx="3327120" cy="5708520"/>
+          <a:ext cx="3324960" cy="5706360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1491,9 +1518,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>69840</xdr:colOff>
+      <xdr:colOff>67680</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>4755960</xdr:rowOff>
+      <xdr:rowOff>4753800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1507,7 +1534,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="600120"/>
-          <a:ext cx="5708520" cy="4755960"/>
+          <a:ext cx="5706360" cy="4753800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1533,9 +1560,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>3616560</xdr:colOff>
+      <xdr:colOff>3614400</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>4745160</xdr:rowOff>
+      <xdr:rowOff>4743000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1549,7 +1576,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="566640"/>
-          <a:ext cx="3616560" cy="4759560"/>
+          <a:ext cx="3614400" cy="4757400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1744,7 +1771,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
@@ -1936,346 +1963,361 @@
       <c r="F14" s="26"/>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="29" t="n">
+      <c r="A15" s="6" t="n">
         <v>46182</v>
       </c>
-      <c r="B15" s="30" t="s">
+      <c r="B15" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="31"/>
-      <c r="D15" s="32" t="n">
+      <c r="C15" s="8"/>
+      <c r="D15" s="9" t="n">
         <v>23.5</v>
       </c>
-      <c r="E15" s="33"/>
-      <c r="F15" s="34"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="7"/>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="35" t="n">
+      <c r="A16" s="29" t="n">
         <v>46188</v>
       </c>
-      <c r="B16" s="36" t="s">
+      <c r="B16" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="36" t="s">
+      <c r="C16" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="37"/>
-      <c r="E16" s="36" t="n">
+      <c r="D16" s="31"/>
+      <c r="E16" s="32" t="n">
         <v>308</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="38" t="s">
+      <c r="A17" s="6" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="8"/>
+      <c r="D17" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E17" s="9"/>
+      <c r="F17" s="7"/>
+    </row>
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="39"/>
-      <c r="C17" s="40"/>
-      <c r="D17" s="41" t="n">
-        <f aca="false">SUM(D6:D16)</f>
-        <v>908</v>
-      </c>
-      <c r="E17" s="42" t="n">
-        <f aca="false">SUM(E6:E16)</f>
+      <c r="B18" s="34"/>
+      <c r="C18" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="36" t="n">
+        <f aca="false">SUM(D6:D17)</f>
+        <v>938</v>
+      </c>
+      <c r="E18" s="37" t="n">
+        <f aca="false">SUM(E6:E17)</f>
         <v>618</v>
       </c>
-      <c r="F17" s="34"/>
-    </row>
-    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="43"/>
-      <c r="B18" s="34"/>
-      <c r="C18" s="31"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="34"/>
+      <c r="F18" s="38" t="n">
+        <f aca="false">D18-E18</f>
+        <v>320</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="43"/>
-      <c r="B19" s="34"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="34"/>
+      <c r="A19" s="39"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="40"/>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="43"/>
-      <c r="B20" s="34"/>
-      <c r="C20" s="31"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="34"/>
+      <c r="A20" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="44"/>
+      <c r="C20" s="45"/>
+      <c r="D20" s="46" t="n">
+        <f aca="false">SUM(D6:D17)</f>
+        <v>938</v>
+      </c>
+      <c r="E20" s="46" t="n">
+        <f aca="false">SUM(E6:E17)</f>
+        <v>618</v>
+      </c>
+      <c r="F20" s="47" t="n">
+        <f aca="false">D20-E20</f>
+        <v>320</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="43"/>
-      <c r="B21" s="34"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="34"/>
+      <c r="A21" s="48" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="49"/>
+      <c r="C21" s="50"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="52" t="n">
+        <f aca="false">D20-E20</f>
+        <v>320</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="43"/>
-      <c r="B22" s="34"/>
-      <c r="C22" s="31"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="34"/>
+      <c r="A22" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="43"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="46" t="n">
+        <f aca="false">D20</f>
+        <v>938</v>
+      </c>
+      <c r="E22" s="53"/>
+      <c r="F22" s="54"/>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="43"/>
-      <c r="B23" s="34"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="34"/>
+      <c r="A23" s="43" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="43"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="53"/>
+      <c r="E23" s="46" t="n">
+        <f aca="false">E20</f>
+        <v>618</v>
+      </c>
+      <c r="F23" s="54"/>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="43"/>
-      <c r="B24" s="34"/>
-      <c r="C24" s="31"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="34"/>
+      <c r="A24" s="39"/>
+      <c r="B24" s="40"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="42"/>
+      <c r="E24" s="42"/>
+      <c r="F24" s="40"/>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="43"/>
-      <c r="B25" s="34"/>
-      <c r="C25" s="31"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="34"/>
+      <c r="A25" s="39"/>
+      <c r="B25" s="40"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="40"/>
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="43"/>
-      <c r="B26" s="34"/>
-      <c r="C26" s="31"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="34"/>
+      <c r="A26" s="39"/>
+      <c r="B26" s="40"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="42"/>
+      <c r="F26" s="40"/>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="43"/>
-      <c r="B27" s="34"/>
-      <c r="C27" s="31"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="34"/>
+      <c r="A27" s="39"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="42"/>
+      <c r="F27" s="40"/>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="43"/>
-      <c r="B28" s="34"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="34"/>
+      <c r="A28" s="39"/>
+      <c r="B28" s="40"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="42"/>
+      <c r="E28" s="42"/>
+      <c r="F28" s="40"/>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="43"/>
-      <c r="B29" s="34"/>
-      <c r="C29" s="31"/>
-      <c r="D29" s="33"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="34"/>
+      <c r="A29" s="39"/>
+      <c r="B29" s="40"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="42"/>
+      <c r="E29" s="42"/>
+      <c r="F29" s="40"/>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="43"/>
-      <c r="B30" s="34"/>
-      <c r="C30" s="31"/>
-      <c r="D30" s="33"/>
-      <c r="E30" s="33"/>
-      <c r="F30" s="34"/>
+      <c r="A30" s="39"/>
+      <c r="B30" s="40"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="42"/>
+      <c r="E30" s="42"/>
+      <c r="F30" s="40"/>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="43"/>
-      <c r="B31" s="34"/>
-      <c r="C31" s="31"/>
-      <c r="D31" s="33"/>
-      <c r="E31" s="33"/>
-      <c r="F31" s="34"/>
+      <c r="A31" s="39"/>
+      <c r="B31" s="40"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="42"/>
+      <c r="E31" s="42"/>
+      <c r="F31" s="40"/>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="43"/>
-      <c r="B32" s="34"/>
-      <c r="C32" s="31"/>
-      <c r="D32" s="33"/>
-      <c r="E32" s="33"/>
-      <c r="F32" s="34"/>
+      <c r="A32" s="39"/>
+      <c r="B32" s="40"/>
+      <c r="C32" s="41"/>
+      <c r="D32" s="42"/>
+      <c r="E32" s="42"/>
+      <c r="F32" s="40"/>
     </row>
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="43"/>
-      <c r="B33" s="34"/>
-      <c r="C33" s="31"/>
-      <c r="D33" s="33"/>
-      <c r="E33" s="33"/>
-      <c r="F33" s="34"/>
+      <c r="A33" s="39"/>
+      <c r="B33" s="40"/>
+      <c r="C33" s="41"/>
+      <c r="D33" s="42"/>
+      <c r="E33" s="42"/>
+      <c r="F33" s="40"/>
     </row>
     <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="43"/>
-      <c r="B34" s="34"/>
-      <c r="C34" s="31"/>
-      <c r="D34" s="33"/>
-      <c r="E34" s="33"/>
-      <c r="F34" s="34"/>
+      <c r="A34" s="39"/>
+      <c r="B34" s="40"/>
+      <c r="C34" s="41"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="40"/>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="43"/>
-      <c r="B35" s="34"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="33"/>
-      <c r="E35" s="33"/>
-      <c r="F35" s="34"/>
+      <c r="A35" s="39"/>
+      <c r="B35" s="40"/>
+      <c r="C35" s="41"/>
+      <c r="D35" s="42"/>
+      <c r="E35" s="42"/>
+      <c r="F35" s="40"/>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="43"/>
-      <c r="B36" s="34"/>
-      <c r="C36" s="31"/>
-      <c r="D36" s="33"/>
-      <c r="E36" s="33"/>
-      <c r="F36" s="34"/>
+      <c r="A36" s="39"/>
+      <c r="B36" s="40"/>
+      <c r="C36" s="41"/>
+      <c r="D36" s="42"/>
+      <c r="E36" s="42"/>
+      <c r="F36" s="40"/>
     </row>
     <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="43"/>
-      <c r="B37" s="34"/>
-      <c r="C37" s="31"/>
-      <c r="D37" s="33"/>
-      <c r="E37" s="33"/>
-      <c r="F37" s="34"/>
+      <c r="A37" s="39"/>
+      <c r="B37" s="40"/>
+      <c r="C37" s="41"/>
+      <c r="D37" s="42"/>
+      <c r="E37" s="42"/>
+      <c r="F37" s="40"/>
     </row>
     <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="43"/>
-      <c r="B38" s="34"/>
-      <c r="C38" s="31"/>
-      <c r="D38" s="33"/>
-      <c r="E38" s="33"/>
-      <c r="F38" s="34"/>
+      <c r="A38" s="39"/>
+      <c r="B38" s="40"/>
+      <c r="C38" s="41"/>
+      <c r="D38" s="42"/>
+      <c r="E38" s="42"/>
+      <c r="F38" s="40"/>
     </row>
     <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="43"/>
-      <c r="B39" s="34"/>
-      <c r="C39" s="31"/>
-      <c r="D39" s="33"/>
-      <c r="E39" s="33"/>
-      <c r="F39" s="34"/>
+      <c r="A39" s="39"/>
+      <c r="B39" s="40"/>
+      <c r="C39" s="41"/>
+      <c r="D39" s="42"/>
+      <c r="E39" s="42"/>
+      <c r="F39" s="40"/>
     </row>
     <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="43"/>
-      <c r="B40" s="34"/>
-      <c r="C40" s="31"/>
-      <c r="D40" s="33"/>
-      <c r="E40" s="33"/>
-      <c r="F40" s="34"/>
+      <c r="A40" s="39"/>
+      <c r="B40" s="40"/>
+      <c r="C40" s="41"/>
+      <c r="D40" s="42"/>
+      <c r="E40" s="42"/>
+      <c r="F40" s="40"/>
     </row>
     <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="43"/>
-      <c r="B41" s="34"/>
-      <c r="C41" s="31"/>
-      <c r="D41" s="33"/>
-      <c r="E41" s="33"/>
-      <c r="F41" s="34"/>
+      <c r="A41" s="39"/>
+      <c r="B41" s="40"/>
+      <c r="C41" s="41"/>
+      <c r="D41" s="42"/>
+      <c r="E41" s="42"/>
+      <c r="F41" s="40"/>
     </row>
     <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="44"/>
-      <c r="B42" s="45"/>
-      <c r="C42" s="46"/>
-      <c r="D42" s="47"/>
-      <c r="E42" s="47"/>
-      <c r="F42" s="45"/>
+      <c r="A42" s="39"/>
+      <c r="B42" s="40"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="40"/>
     </row>
     <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="48" t="s">
-        <v>24</v>
-      </c>
+      <c r="A43" s="55"/>
       <c r="B43" s="49"/>
       <c r="C43" s="50"/>
-      <c r="D43" s="51" t="n">
-        <f aca="false">SUM(D6:D40)</f>
-        <v>1816</v>
-      </c>
-      <c r="E43" s="51" t="n">
-        <f aca="false">SUM(E6:E40)</f>
-        <v>1236</v>
-      </c>
-      <c r="F43" s="52" t="n">
-        <f aca="false">D42-E42</f>
-        <v>0</v>
-      </c>
+      <c r="D43" s="51"/>
+      <c r="E43" s="51"/>
+      <c r="F43" s="49"/>
     </row>
     <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="B44" s="45"/>
-      <c r="C44" s="46"/>
-      <c r="D44" s="47"/>
-      <c r="E44" s="47"/>
-      <c r="F44" s="54" t="n">
-        <f aca="false">D42-E42</f>
-        <v>0</v>
-      </c>
+      <c r="A44" s="56"/>
+      <c r="B44" s="44"/>
+      <c r="C44" s="45"/>
+      <c r="D44" s="53"/>
+      <c r="E44" s="53"/>
+      <c r="F44" s="54"/>
     </row>
     <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="55" t="s">
-        <v>26</v>
-      </c>
+      <c r="A45" s="57"/>
       <c r="B45" s="49"/>
       <c r="C45" s="50"/>
-      <c r="D45" s="56" t="n">
-        <f aca="false">D42</f>
-        <v>0</v>
-      </c>
+      <c r="D45" s="51"/>
       <c r="E45" s="51"/>
-      <c r="F45" s="52"/>
+      <c r="F45" s="58"/>
     </row>
     <row r="46" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="57" t="s">
-        <v>27</v>
-      </c>
-      <c r="B46" s="49"/>
-      <c r="C46" s="50"/>
-      <c r="D46" s="51"/>
-      <c r="E46" s="58" t="n">
-        <f aca="false">E42</f>
-        <v>0</v>
-      </c>
-      <c r="F46" s="52"/>
+      <c r="A46" s="59"/>
+      <c r="B46" s="44"/>
+      <c r="C46" s="45"/>
+      <c r="D46" s="60"/>
+      <c r="E46" s="53"/>
+      <c r="F46" s="54"/>
     </row>
     <row r="47" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="59"/>
-      <c r="B47" s="59"/>
-      <c r="C47" s="59"/>
-      <c r="D47" s="60"/>
-      <c r="E47" s="60"/>
-      <c r="F47" s="61"/>
+      <c r="A47" s="61"/>
+      <c r="D47" s="53"/>
+      <c r="E47" s="62"/>
+      <c r="F47" s="54"/>
     </row>
     <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="44"/>
-      <c r="B48" s="44"/>
-      <c r="C48" s="44"/>
-      <c r="D48" s="47"/>
-      <c r="E48" s="47"/>
-      <c r="F48" s="45"/>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="62"/>
-      <c r="B50" s="49"/>
-      <c r="C50" s="50"/>
-      <c r="D50" s="51"/>
-      <c r="E50" s="51"/>
-      <c r="F50" s="63"/>
-    </row>
+      <c r="A48" s="63"/>
+      <c r="D48" s="64"/>
+      <c r="E48" s="64"/>
+      <c r="F48" s="65"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="55"/>
+      <c r="B49" s="66"/>
+      <c r="C49" s="67"/>
+      <c r="D49" s="51"/>
+      <c r="E49" s="51"/>
+      <c r="F49" s="49"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="64"/>
-      <c r="B51" s="65"/>
-      <c r="C51" s="66"/>
-      <c r="F51" s="67"/>
+      <c r="A51" s="68"/>
+      <c r="B51" s="44"/>
+      <c r="C51" s="45"/>
+      <c r="D51" s="53"/>
+      <c r="E51" s="53"/>
+      <c r="F51" s="69"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="70"/>
+      <c r="B52" s="66"/>
+      <c r="C52" s="67"/>
+      <c r="F52" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A23:C23"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C8" location="'Ticket Cena'!A1" display="🧾 Ver Ticket Cena"/>
@@ -2304,162 +2346,162 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="68" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
+      <c r="A1" s="72" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
     </row>
     <row r="3" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="70" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="71" t="n">
+      <c r="A5" s="74" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="75" t="n">
         <v>800</v>
       </c>
-      <c r="C5" s="71" t="n">
+      <c r="C5" s="75" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="71" t="n">
+      <c r="D5" s="75" t="n">
         <f aca="false">B5-C5</f>
         <v>800</v>
       </c>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="70" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="71" t="n">
+      <c r="A6" s="74" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="75" t="n">
         <v>0</v>
       </c>
-      <c r="C6" s="71" t="n">
+      <c r="C6" s="75" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="71" t="n">
+      <c r="D6" s="75" t="n">
         <f aca="false">B6-C6</f>
         <v>0</v>
       </c>
-      <c r="E6" s="72"/>
-      <c r="F6" s="72"/>
+      <c r="E6" s="76"/>
+      <c r="F6" s="76"/>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="73" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="74" t="n">
+      <c r="A7" s="77" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="78" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="74" t="n">
+      <c r="C7" s="78" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="74" t="n">
+      <c r="D7" s="78" t="n">
         <f aca="false">B7-C7</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="73" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="74" t="n">
+      <c r="A8" s="77" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="78" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="74" t="n">
+      <c r="C8" s="78" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="74" t="n">
+      <c r="D8" s="78" t="n">
         <f aca="false">B8-C8</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="75" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="76" t="n">
+      <c r="A9" s="79" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="80" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="76" t="n">
+      <c r="C9" s="80" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="76" t="n">
+      <c r="D9" s="80" t="n">
         <f aca="false">B9-C9</f>
         <v>0</v>
       </c>
-      <c r="E9" s="77"/>
-      <c r="F9" s="77"/>
+      <c r="E9" s="81"/>
+      <c r="F9" s="81"/>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="70" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="71" t="n">
+      <c r="A10" s="74" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="75" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="71" t="n">
+      <c r="C10" s="75" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="71" t="n">
+      <c r="D10" s="75" t="n">
         <f aca="false">B10-C10</f>
         <v>0</v>
       </c>
-      <c r="E10" s="72"/>
-      <c r="F10" s="72"/>
+      <c r="E10" s="76"/>
+      <c r="F10" s="76"/>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="73" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="74" t="n">
+      <c r="A11" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="78" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="74" t="n">
+      <c r="C11" s="78" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="74" t="n">
+      <c r="D11" s="78" t="n">
         <f aca="false">B11-C11</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="78" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="51" t="n">
+      <c r="A12" s="82" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="53" t="n">
         <f aca="false">SUM(B5:B11)</f>
         <v>800</v>
       </c>
-      <c r="C12" s="51" t="n">
+      <c r="C12" s="53" t="n">
         <f aca="false">SUM(C5:C11)</f>
         <v>0</v>
       </c>
-      <c r="D12" s="51" t="n">
+      <c r="D12" s="53" t="n">
         <f aca="false">B12-C12</f>
         <v>800</v>
       </c>
@@ -2494,745 +2536,745 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="68" t="s">
-        <v>41</v>
-      </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
+      <c r="A1" s="72" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="79" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
+      <c r="A2" s="83" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
     </row>
     <row r="3" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="80" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="80" t="s">
+      <c r="A4" s="84" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="80" t="s">
+      <c r="B4" s="84" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="80" t="s">
+      <c r="C4" s="84" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="80" t="s">
+      <c r="D4" s="84" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="80" t="s">
+      <c r="E4" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="G4" s="81" t="s">
+      <c r="F4" s="84" t="s">
         <v>49</v>
       </c>
+      <c r="G4" s="85" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="82" t="n">
+      <c r="A5" s="86" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="83" t="s">
+      <c r="B5" s="87" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="88" t="n">
         <v>50</v>
       </c>
-      <c r="C5" s="84" t="n">
+      <c r="D5" s="89" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="88" t="n">
         <v>50</v>
       </c>
-      <c r="D5" s="85" t="s">
-        <v>51</v>
-      </c>
-      <c r="E5" s="84" t="n">
+      <c r="F5" s="90" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" s="91"/>
+    </row>
+    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="86" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="87"/>
+      <c r="C6" s="88"/>
+      <c r="D6" s="89"/>
+      <c r="E6" s="88"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="91"/>
+    </row>
+    <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="92" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="93" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="94" t="n">
         <v>50</v>
       </c>
-      <c r="F5" s="86" t="s">
+      <c r="D7" s="95" t="s">
         <v>52</v>
       </c>
-      <c r="G5" s="87"/>
-    </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="82" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="83"/>
-      <c r="C6" s="84"/>
-      <c r="D6" s="85"/>
-      <c r="E6" s="84"/>
-      <c r="F6" s="86"/>
-      <c r="G6" s="87"/>
-    </row>
-    <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="88" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="89" t="s">
+      <c r="E7" s="94" t="n">
+        <v>50</v>
+      </c>
+      <c r="F7" s="96" t="s">
         <v>53</v>
       </c>
-      <c r="C7" s="90" t="n">
+      <c r="G7" s="97"/>
+    </row>
+    <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="86" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="87" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="88" t="n">
         <v>50</v>
       </c>
-      <c r="D7" s="91" t="s">
-        <v>51</v>
-      </c>
-      <c r="E7" s="90" t="n">
+      <c r="D8" s="89" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="88" t="n">
         <v>50</v>
       </c>
-      <c r="F7" s="92" t="s">
+      <c r="F8" s="90" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" s="91"/>
+    </row>
+    <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="92" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="93" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="94" t="n">
+        <v>50</v>
+      </c>
+      <c r="D9" s="95" t="s">
         <v>52</v>
       </c>
-      <c r="G7" s="93"/>
-    </row>
-    <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="82" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="83" t="s">
-        <v>54</v>
-      </c>
-      <c r="C8" s="84" t="n">
+      <c r="E9" s="94" t="n">
         <v>50</v>
       </c>
-      <c r="D8" s="85" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" s="84" t="n">
+      <c r="F9" s="96" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9" s="97"/>
+    </row>
+    <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="86" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="87" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="88" t="n">
         <v>50</v>
       </c>
-      <c r="F8" s="86" t="s">
+      <c r="D10" s="89" t="s">
         <v>52</v>
       </c>
-      <c r="G8" s="87"/>
-    </row>
-    <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="88" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="89" t="s">
-        <v>55</v>
-      </c>
-      <c r="C9" s="90" t="n">
+      <c r="E10" s="88" t="n">
         <v>50</v>
       </c>
-      <c r="D9" s="91" t="s">
-        <v>51</v>
-      </c>
-      <c r="E9" s="90" t="n">
+      <c r="F10" s="90" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" s="91"/>
+    </row>
+    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="92" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="93" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="94" t="n">
         <v>50</v>
       </c>
-      <c r="F9" s="92" t="s">
+      <c r="D11" s="95" t="s">
         <v>52</v>
       </c>
-      <c r="G9" s="93"/>
-    </row>
-    <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="82" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="83" t="s">
-        <v>56</v>
-      </c>
-      <c r="C10" s="84" t="n">
+      <c r="E11" s="94" t="n">
         <v>50</v>
       </c>
-      <c r="D10" s="85" t="s">
-        <v>51</v>
-      </c>
-      <c r="E10" s="84" t="n">
+      <c r="F11" s="96" t="s">
+        <v>53</v>
+      </c>
+      <c r="G11" s="97"/>
+    </row>
+    <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="86" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="87" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="88" t="n">
         <v>50</v>
       </c>
-      <c r="F10" s="86" t="s">
+      <c r="D12" s="89" t="s">
         <v>52</v>
       </c>
-      <c r="G10" s="87"/>
-    </row>
-    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="88" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="89" t="s">
-        <v>57</v>
-      </c>
-      <c r="C11" s="90" t="n">
+      <c r="E12" s="88" t="n">
         <v>50</v>
       </c>
-      <c r="D11" s="91" t="s">
-        <v>51</v>
-      </c>
-      <c r="E11" s="90" t="n">
+      <c r="F12" s="90" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12" s="91"/>
+    </row>
+    <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="92" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="93" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="94" t="n">
         <v>50</v>
       </c>
-      <c r="F11" s="92" t="s">
+      <c r="D13" s="95" t="s">
         <v>52</v>
       </c>
-      <c r="G11" s="93"/>
-    </row>
-    <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="82" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="83" t="s">
-        <v>58</v>
-      </c>
-      <c r="C12" s="84" t="n">
+      <c r="E13" s="94" t="n">
         <v>50</v>
       </c>
-      <c r="D12" s="85" t="s">
-        <v>51</v>
-      </c>
-      <c r="E12" s="84" t="n">
+      <c r="F13" s="96" t="s">
+        <v>53</v>
+      </c>
+      <c r="G13" s="97"/>
+    </row>
+    <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="86" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="87" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="88" t="n">
         <v>50</v>
       </c>
-      <c r="F12" s="86" t="s">
+      <c r="D14" s="89" t="s">
         <v>52</v>
       </c>
-      <c r="G12" s="87"/>
-    </row>
-    <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="88" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="89" t="s">
-        <v>59</v>
-      </c>
-      <c r="C13" s="90" t="n">
+      <c r="E14" s="88" t="n">
         <v>50</v>
       </c>
-      <c r="D13" s="91" t="s">
-        <v>51</v>
-      </c>
-      <c r="E13" s="90" t="n">
+      <c r="F14" s="90" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14" s="91"/>
+    </row>
+    <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="92" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="93" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" s="94" t="n">
         <v>50</v>
       </c>
-      <c r="F13" s="92" t="s">
+      <c r="D15" s="95" t="s">
         <v>52</v>
       </c>
-      <c r="G13" s="93"/>
-    </row>
-    <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="82" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="83" t="s">
-        <v>60</v>
-      </c>
-      <c r="C14" s="84" t="n">
+      <c r="E15" s="94" t="n">
         <v>50</v>
       </c>
-      <c r="D14" s="85" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14" s="84" t="n">
+      <c r="F15" s="96" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15" s="97"/>
+    </row>
+    <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="86" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="87" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="88" t="n">
         <v>50</v>
       </c>
-      <c r="F14" s="86" t="s">
-        <v>52</v>
-      </c>
-      <c r="G14" s="87"/>
-    </row>
-    <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="88" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="89" t="s">
-        <v>61</v>
-      </c>
-      <c r="C15" s="90" t="n">
+      <c r="D16" s="90" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" s="88" t="n">
         <v>50</v>
       </c>
-      <c r="D15" s="91" t="s">
-        <v>51</v>
-      </c>
-      <c r="E15" s="90" t="n">
+      <c r="F16" s="90" t="s">
+        <v>53</v>
+      </c>
+      <c r="G16" s="91"/>
+    </row>
+    <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="86" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="98" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="99" t="n">
         <v>50</v>
       </c>
-      <c r="F15" s="92" t="s">
-        <v>52</v>
-      </c>
-      <c r="G15" s="93"/>
-    </row>
-    <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="82" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="83" t="s">
-        <v>62</v>
-      </c>
-      <c r="C16" s="84" t="n">
+      <c r="D17" s="100" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17" s="99" t="n">
         <v>50</v>
       </c>
-      <c r="D16" s="86" t="s">
-        <v>63</v>
-      </c>
-      <c r="E16" s="84" t="n">
+      <c r="F17" s="100" t="s">
+        <v>53</v>
+      </c>
+      <c r="G17" s="101"/>
+    </row>
+    <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="92" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="102" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="103" t="n">
         <v>50</v>
       </c>
-      <c r="F16" s="86" t="s">
-        <v>52</v>
-      </c>
-      <c r="G16" s="87"/>
-    </row>
-    <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="82" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="94" t="s">
-        <v>64</v>
-      </c>
-      <c r="C17" s="95" t="n">
+      <c r="D18" s="104" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18" s="103" t="n">
         <v>50</v>
       </c>
-      <c r="D17" s="96" t="s">
-        <v>65</v>
-      </c>
-      <c r="E17" s="95" t="n">
+      <c r="F18" s="104" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18" s="105"/>
+    </row>
+    <row r="19" s="107" customFormat="true" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="92" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="102" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="103" t="n">
         <v>50</v>
       </c>
-      <c r="F17" s="96" t="s">
-        <v>52</v>
-      </c>
-      <c r="G17" s="97"/>
-    </row>
-    <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="88" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="98" t="s">
-        <v>66</v>
-      </c>
-      <c r="C18" s="99" t="n">
+      <c r="D19" s="104" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" s="103" t="n">
         <v>50</v>
       </c>
-      <c r="D18" s="100" t="s">
-        <v>65</v>
-      </c>
-      <c r="E18" s="99" t="n">
+      <c r="F19" s="104" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19" s="106"/>
+    </row>
+    <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="92" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="102" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20" s="103" t="n">
         <v>50</v>
       </c>
-      <c r="F18" s="100" t="s">
-        <v>52</v>
-      </c>
-      <c r="G18" s="101"/>
-    </row>
-    <row r="19" s="103" customFormat="true" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="88" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="98" t="s">
-        <v>67</v>
-      </c>
-      <c r="C19" s="99" t="n">
+      <c r="D20" s="104" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" s="103" t="n">
         <v>50</v>
       </c>
-      <c r="D19" s="100" t="s">
-        <v>68</v>
-      </c>
-      <c r="E19" s="99" t="n">
+      <c r="F20" s="104" t="s">
+        <v>53</v>
+      </c>
+      <c r="G20" s="97"/>
+    </row>
+    <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="92" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="102" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" s="103" t="n">
         <v>50</v>
       </c>
-      <c r="F19" s="100" t="s">
-        <v>52</v>
-      </c>
-      <c r="G19" s="102"/>
-    </row>
-    <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="88" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="98" t="s">
+      <c r="D21" s="104" t="s">
         <v>69</v>
       </c>
-      <c r="C20" s="99" t="n">
+      <c r="E21" s="103" t="n">
         <v>50</v>
       </c>
-      <c r="D20" s="100" t="s">
-        <v>68</v>
-      </c>
-      <c r="E20" s="99" t="n">
-        <v>50</v>
-      </c>
-      <c r="F20" s="100" t="s">
-        <v>52</v>
-      </c>
-      <c r="G20" s="93"/>
-    </row>
-    <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="88" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="98" t="s">
-        <v>70</v>
-      </c>
-      <c r="C21" s="99" t="n">
-        <v>50</v>
-      </c>
-      <c r="D21" s="100" t="s">
-        <v>68</v>
-      </c>
-      <c r="E21" s="99" t="n">
-        <v>50</v>
-      </c>
-      <c r="F21" s="100" t="s">
-        <v>52</v>
-      </c>
-      <c r="G21" s="102"/>
+      <c r="F21" s="104" t="s">
+        <v>53</v>
+      </c>
+      <c r="G21" s="106"/>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="88"/>
-      <c r="B22" s="98"/>
-      <c r="C22" s="99"/>
-      <c r="D22" s="100"/>
-      <c r="E22" s="99"/>
-      <c r="F22" s="100"/>
-      <c r="G22" s="102"/>
+      <c r="A22" s="92"/>
+      <c r="B22" s="102"/>
+      <c r="C22" s="103"/>
+      <c r="D22" s="104"/>
+      <c r="E22" s="103"/>
+      <c r="F22" s="104"/>
+      <c r="G22" s="106"/>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="88"/>
-      <c r="B23" s="98"/>
-      <c r="C23" s="99"/>
-      <c r="D23" s="100"/>
-      <c r="E23" s="99"/>
-      <c r="F23" s="100"/>
-      <c r="G23" s="101"/>
+      <c r="A23" s="92"/>
+      <c r="B23" s="102"/>
+      <c r="C23" s="103"/>
+      <c r="D23" s="104"/>
+      <c r="E23" s="103"/>
+      <c r="F23" s="104"/>
+      <c r="G23" s="105"/>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="88"/>
-      <c r="B24" s="98"/>
-      <c r="C24" s="99"/>
-      <c r="D24" s="100"/>
-      <c r="E24" s="99"/>
-      <c r="F24" s="100"/>
-      <c r="G24" s="101"/>
+      <c r="A24" s="92"/>
+      <c r="B24" s="102"/>
+      <c r="C24" s="103"/>
+      <c r="D24" s="104"/>
+      <c r="E24" s="103"/>
+      <c r="F24" s="104"/>
+      <c r="G24" s="105"/>
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="88"/>
-      <c r="B25" s="98"/>
-      <c r="C25" s="99"/>
-      <c r="D25" s="100"/>
-      <c r="E25" s="99"/>
-      <c r="F25" s="100"/>
-      <c r="G25" s="101"/>
+      <c r="A25" s="92"/>
+      <c r="B25" s="102"/>
+      <c r="C25" s="103"/>
+      <c r="D25" s="104"/>
+      <c r="E25" s="103"/>
+      <c r="F25" s="104"/>
+      <c r="G25" s="105"/>
     </row>
     <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="104" t="s">
-        <v>71</v>
-      </c>
-      <c r="B26" s="104"/>
-      <c r="C26" s="105" t="n">
+      <c r="A26" s="108" t="s">
+        <v>72</v>
+      </c>
+      <c r="B26" s="108"/>
+      <c r="C26" s="109" t="n">
         <v>800</v>
       </c>
-      <c r="D26" s="106"/>
-      <c r="E26" s="105" t="n">
+      <c r="D26" s="110"/>
+      <c r="E26" s="109" t="n">
         <v>0</v>
       </c>
-      <c r="F26" s="106"/>
-      <c r="G26" s="106"/>
+      <c r="F26" s="110"/>
+      <c r="G26" s="110"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="107"/>
-      <c r="B27" s="107"/>
-      <c r="C27" s="108"/>
-      <c r="D27" s="107"/>
-      <c r="E27" s="107"/>
-      <c r="F27" s="107"/>
-      <c r="G27" s="107"/>
+      <c r="A27" s="111"/>
+      <c r="B27" s="111"/>
+      <c r="C27" s="112"/>
+      <c r="D27" s="111"/>
+      <c r="E27" s="111"/>
+      <c r="F27" s="111"/>
+      <c r="G27" s="111"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="107"/>
-      <c r="B28" s="107"/>
-      <c r="C28" s="107"/>
-      <c r="D28" s="107"/>
-      <c r="E28" s="107"/>
-      <c r="F28" s="107"/>
-      <c r="G28" s="107"/>
+      <c r="A28" s="111"/>
+      <c r="B28" s="111"/>
+      <c r="C28" s="111"/>
+      <c r="D28" s="111"/>
+      <c r="E28" s="111"/>
+      <c r="F28" s="111"/>
+      <c r="G28" s="111"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="107"/>
-      <c r="B29" s="107"/>
-      <c r="C29" s="107"/>
-      <c r="D29" s="107"/>
-      <c r="E29" s="107"/>
-      <c r="F29" s="107"/>
-      <c r="G29" s="107"/>
+      <c r="A29" s="111"/>
+      <c r="B29" s="111"/>
+      <c r="C29" s="111"/>
+      <c r="D29" s="111"/>
+      <c r="E29" s="111"/>
+      <c r="F29" s="111"/>
+      <c r="G29" s="111"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="107"/>
-      <c r="B30" s="107"/>
-      <c r="C30" s="107"/>
-      <c r="D30" s="107"/>
-      <c r="E30" s="107"/>
-      <c r="F30" s="107"/>
-      <c r="G30" s="107"/>
+      <c r="A30" s="111"/>
+      <c r="B30" s="111"/>
+      <c r="C30" s="111"/>
+      <c r="D30" s="111"/>
+      <c r="E30" s="111"/>
+      <c r="F30" s="111"/>
+      <c r="G30" s="111"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="107"/>
-      <c r="B31" s="107"/>
-      <c r="C31" s="107"/>
-      <c r="D31" s="107"/>
-      <c r="E31" s="107"/>
-      <c r="F31" s="107"/>
-      <c r="G31" s="107"/>
+      <c r="A31" s="111"/>
+      <c r="B31" s="111"/>
+      <c r="C31" s="111"/>
+      <c r="D31" s="111"/>
+      <c r="E31" s="111"/>
+      <c r="F31" s="111"/>
+      <c r="G31" s="111"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="107"/>
-      <c r="B32" s="107"/>
-      <c r="C32" s="107"/>
-      <c r="D32" s="107"/>
-      <c r="E32" s="107"/>
-      <c r="F32" s="107"/>
-      <c r="G32" s="107"/>
+      <c r="A32" s="111"/>
+      <c r="B32" s="111"/>
+      <c r="C32" s="111"/>
+      <c r="D32" s="111"/>
+      <c r="E32" s="111"/>
+      <c r="F32" s="111"/>
+      <c r="G32" s="111"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="107"/>
-      <c r="B33" s="107"/>
-      <c r="C33" s="107"/>
-      <c r="D33" s="107"/>
-      <c r="E33" s="107"/>
-      <c r="F33" s="107"/>
-      <c r="G33" s="107"/>
+      <c r="A33" s="111"/>
+      <c r="B33" s="111"/>
+      <c r="C33" s="111"/>
+      <c r="D33" s="111"/>
+      <c r="E33" s="111"/>
+      <c r="F33" s="111"/>
+      <c r="G33" s="111"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="107"/>
-      <c r="B34" s="107"/>
-      <c r="C34" s="107"/>
-      <c r="D34" s="107"/>
-      <c r="E34" s="107"/>
-      <c r="F34" s="107"/>
-      <c r="G34" s="107"/>
+      <c r="A34" s="111"/>
+      <c r="B34" s="111"/>
+      <c r="C34" s="111"/>
+      <c r="D34" s="111"/>
+      <c r="E34" s="111"/>
+      <c r="F34" s="111"/>
+      <c r="G34" s="111"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="107"/>
-      <c r="B35" s="107"/>
-      <c r="C35" s="107"/>
-      <c r="D35" s="107"/>
-      <c r="E35" s="107"/>
-      <c r="F35" s="107"/>
-      <c r="G35" s="107"/>
+      <c r="A35" s="111"/>
+      <c r="B35" s="111"/>
+      <c r="C35" s="111"/>
+      <c r="D35" s="111"/>
+      <c r="E35" s="111"/>
+      <c r="F35" s="111"/>
+      <c r="G35" s="111"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="107"/>
-      <c r="B36" s="107"/>
-      <c r="C36" s="107"/>
-      <c r="D36" s="107"/>
-      <c r="E36" s="107"/>
-      <c r="F36" s="107"/>
-      <c r="G36" s="107"/>
+      <c r="A36" s="111"/>
+      <c r="B36" s="111"/>
+      <c r="C36" s="111"/>
+      <c r="D36" s="111"/>
+      <c r="E36" s="111"/>
+      <c r="F36" s="111"/>
+      <c r="G36" s="111"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="107"/>
-      <c r="B37" s="107"/>
-      <c r="C37" s="107"/>
-      <c r="D37" s="107"/>
-      <c r="E37" s="107"/>
-      <c r="F37" s="107"/>
-      <c r="G37" s="107"/>
+      <c r="A37" s="111"/>
+      <c r="B37" s="111"/>
+      <c r="C37" s="111"/>
+      <c r="D37" s="111"/>
+      <c r="E37" s="111"/>
+      <c r="F37" s="111"/>
+      <c r="G37" s="111"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="107"/>
-      <c r="B38" s="107"/>
-      <c r="C38" s="107"/>
-      <c r="D38" s="107"/>
-      <c r="E38" s="107"/>
-      <c r="F38" s="107"/>
-      <c r="G38" s="107"/>
+      <c r="A38" s="111"/>
+      <c r="B38" s="111"/>
+      <c r="C38" s="111"/>
+      <c r="D38" s="111"/>
+      <c r="E38" s="111"/>
+      <c r="F38" s="111"/>
+      <c r="G38" s="111"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="107"/>
-      <c r="B39" s="107"/>
-      <c r="C39" s="107"/>
-      <c r="D39" s="107"/>
-      <c r="E39" s="107"/>
-      <c r="F39" s="107"/>
-      <c r="G39" s="107"/>
+      <c r="A39" s="111"/>
+      <c r="B39" s="111"/>
+      <c r="C39" s="111"/>
+      <c r="D39" s="111"/>
+      <c r="E39" s="111"/>
+      <c r="F39" s="111"/>
+      <c r="G39" s="111"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="107"/>
-      <c r="B40" s="107"/>
-      <c r="C40" s="107"/>
-      <c r="D40" s="107"/>
-      <c r="E40" s="107"/>
-      <c r="F40" s="107"/>
-      <c r="G40" s="107"/>
+      <c r="A40" s="111"/>
+      <c r="B40" s="111"/>
+      <c r="C40" s="111"/>
+      <c r="D40" s="111"/>
+      <c r="E40" s="111"/>
+      <c r="F40" s="111"/>
+      <c r="G40" s="111"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="107"/>
-      <c r="B41" s="107"/>
-      <c r="C41" s="107"/>
-      <c r="D41" s="107"/>
-      <c r="E41" s="107"/>
-      <c r="F41" s="107"/>
-      <c r="G41" s="107"/>
+      <c r="A41" s="111"/>
+      <c r="B41" s="111"/>
+      <c r="C41" s="111"/>
+      <c r="D41" s="111"/>
+      <c r="E41" s="111"/>
+      <c r="F41" s="111"/>
+      <c r="G41" s="111"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="107"/>
-      <c r="B42" s="107"/>
-      <c r="C42" s="107"/>
-      <c r="D42" s="107"/>
-      <c r="E42" s="107"/>
-      <c r="F42" s="107"/>
-      <c r="G42" s="107"/>
+      <c r="A42" s="111"/>
+      <c r="B42" s="111"/>
+      <c r="C42" s="111"/>
+      <c r="D42" s="111"/>
+      <c r="E42" s="111"/>
+      <c r="F42" s="111"/>
+      <c r="G42" s="111"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="107"/>
-      <c r="B43" s="107"/>
-      <c r="C43" s="107"/>
-      <c r="D43" s="107"/>
-      <c r="E43" s="107"/>
-      <c r="F43" s="107"/>
-      <c r="G43" s="107"/>
+      <c r="A43" s="111"/>
+      <c r="B43" s="111"/>
+      <c r="C43" s="111"/>
+      <c r="D43" s="111"/>
+      <c r="E43" s="111"/>
+      <c r="F43" s="111"/>
+      <c r="G43" s="111"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="107"/>
-      <c r="B44" s="107"/>
-      <c r="C44" s="107"/>
-      <c r="D44" s="107"/>
-      <c r="E44" s="107"/>
-      <c r="F44" s="107"/>
-      <c r="G44" s="107"/>
+      <c r="A44" s="111"/>
+      <c r="B44" s="111"/>
+      <c r="C44" s="111"/>
+      <c r="D44" s="111"/>
+      <c r="E44" s="111"/>
+      <c r="F44" s="111"/>
+      <c r="G44" s="111"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="107"/>
-      <c r="B45" s="107"/>
-      <c r="C45" s="107"/>
-      <c r="D45" s="107"/>
-      <c r="E45" s="107"/>
-      <c r="F45" s="107"/>
-      <c r="G45" s="107"/>
+      <c r="A45" s="111"/>
+      <c r="B45" s="111"/>
+      <c r="C45" s="111"/>
+      <c r="D45" s="111"/>
+      <c r="E45" s="111"/>
+      <c r="F45" s="111"/>
+      <c r="G45" s="111"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="107"/>
-      <c r="B46" s="107"/>
-      <c r="C46" s="107"/>
-      <c r="D46" s="107"/>
-      <c r="E46" s="107"/>
-      <c r="F46" s="107"/>
-      <c r="G46" s="107"/>
+      <c r="A46" s="111"/>
+      <c r="B46" s="111"/>
+      <c r="C46" s="111"/>
+      <c r="D46" s="111"/>
+      <c r="E46" s="111"/>
+      <c r="F46" s="111"/>
+      <c r="G46" s="111"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="107"/>
-      <c r="B47" s="107"/>
-      <c r="C47" s="107"/>
-      <c r="D47" s="107"/>
-      <c r="E47" s="107"/>
-      <c r="F47" s="107"/>
-      <c r="G47" s="107"/>
+      <c r="A47" s="111"/>
+      <c r="B47" s="111"/>
+      <c r="C47" s="111"/>
+      <c r="D47" s="111"/>
+      <c r="E47" s="111"/>
+      <c r="F47" s="111"/>
+      <c r="G47" s="111"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="107"/>
-      <c r="B48" s="107"/>
-      <c r="C48" s="107"/>
-      <c r="D48" s="107"/>
-      <c r="E48" s="107"/>
-      <c r="F48" s="107"/>
-      <c r="G48" s="107"/>
+      <c r="A48" s="111"/>
+      <c r="B48" s="111"/>
+      <c r="C48" s="111"/>
+      <c r="D48" s="111"/>
+      <c r="E48" s="111"/>
+      <c r="F48" s="111"/>
+      <c r="G48" s="111"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="107"/>
-      <c r="B49" s="107"/>
-      <c r="C49" s="107"/>
-      <c r="D49" s="107"/>
-      <c r="E49" s="107"/>
-      <c r="F49" s="107"/>
-      <c r="G49" s="107"/>
+      <c r="A49" s="111"/>
+      <c r="B49" s="111"/>
+      <c r="C49" s="111"/>
+      <c r="D49" s="111"/>
+      <c r="E49" s="111"/>
+      <c r="F49" s="111"/>
+      <c r="G49" s="111"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="107"/>
-      <c r="B50" s="107"/>
-      <c r="C50" s="107"/>
-      <c r="D50" s="107"/>
-      <c r="E50" s="107"/>
-      <c r="F50" s="107"/>
-      <c r="G50" s="107"/>
+      <c r="A50" s="111"/>
+      <c r="B50" s="111"/>
+      <c r="C50" s="111"/>
+      <c r="D50" s="111"/>
+      <c r="E50" s="111"/>
+      <c r="F50" s="111"/>
+      <c r="G50" s="111"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="107"/>
-      <c r="B51" s="107"/>
-      <c r="C51" s="107"/>
-      <c r="D51" s="107"/>
-      <c r="E51" s="107"/>
-      <c r="F51" s="107"/>
-      <c r="G51" s="107"/>
+      <c r="A51" s="111"/>
+      <c r="B51" s="111"/>
+      <c r="C51" s="111"/>
+      <c r="D51" s="111"/>
+      <c r="E51" s="111"/>
+      <c r="F51" s="111"/>
+      <c r="G51" s="111"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="107"/>
-      <c r="B52" s="107"/>
-      <c r="C52" s="107"/>
-      <c r="D52" s="107"/>
-      <c r="E52" s="107"/>
-      <c r="F52" s="107"/>
-      <c r="G52" s="107"/>
+      <c r="A52" s="111"/>
+      <c r="B52" s="111"/>
+      <c r="C52" s="111"/>
+      <c r="D52" s="111"/>
+      <c r="E52" s="111"/>
+      <c r="F52" s="111"/>
+      <c r="G52" s="111"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="107"/>
-      <c r="B53" s="107"/>
-      <c r="C53" s="107"/>
-      <c r="D53" s="107"/>
-      <c r="E53" s="107"/>
-      <c r="F53" s="107"/>
-      <c r="G53" s="107"/>
+      <c r="A53" s="111"/>
+      <c r="B53" s="111"/>
+      <c r="C53" s="111"/>
+      <c r="D53" s="111"/>
+      <c r="E53" s="111"/>
+      <c r="F53" s="111"/>
+      <c r="G53" s="111"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="107"/>
-      <c r="B54" s="107"/>
-      <c r="C54" s="107"/>
-      <c r="D54" s="107"/>
-      <c r="E54" s="107"/>
-      <c r="F54" s="107"/>
-      <c r="G54" s="107"/>
+      <c r="A54" s="111"/>
+      <c r="B54" s="111"/>
+      <c r="C54" s="111"/>
+      <c r="D54" s="111"/>
+      <c r="E54" s="111"/>
+      <c r="F54" s="111"/>
+      <c r="G54" s="111"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="107"/>
-      <c r="B55" s="107"/>
-      <c r="C55" s="107"/>
-      <c r="D55" s="107"/>
-      <c r="E55" s="107"/>
-      <c r="F55" s="107"/>
-      <c r="G55" s="107"/>
+      <c r="A55" s="111"/>
+      <c r="B55" s="111"/>
+      <c r="C55" s="111"/>
+      <c r="D55" s="111"/>
+      <c r="E55" s="111"/>
+      <c r="F55" s="111"/>
+      <c r="G55" s="111"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="107"/>
-      <c r="B56" s="107"/>
-      <c r="C56" s="107"/>
-      <c r="D56" s="107"/>
-      <c r="E56" s="107"/>
-      <c r="F56" s="107"/>
-      <c r="G56" s="107"/>
+      <c r="A56" s="111"/>
+      <c r="B56" s="111"/>
+      <c r="C56" s="111"/>
+      <c r="D56" s="111"/>
+      <c r="E56" s="111"/>
+      <c r="F56" s="111"/>
+      <c r="G56" s="111"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="107"/>
-      <c r="B57" s="107"/>
-      <c r="C57" s="107"/>
-      <c r="D57" s="107"/>
-      <c r="E57" s="107"/>
-      <c r="F57" s="107"/>
-      <c r="G57" s="107"/>
+      <c r="A57" s="111"/>
+      <c r="B57" s="111"/>
+      <c r="C57" s="111"/>
+      <c r="D57" s="111"/>
+      <c r="E57" s="111"/>
+      <c r="F57" s="111"/>
+      <c r="G57" s="111"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="107"/>
-      <c r="B58" s="107"/>
-      <c r="C58" s="107"/>
-      <c r="D58" s="107"/>
-      <c r="E58" s="107"/>
-      <c r="F58" s="107"/>
-      <c r="G58" s="107"/>
+      <c r="A58" s="111"/>
+      <c r="B58" s="111"/>
+      <c r="C58" s="111"/>
+      <c r="D58" s="111"/>
+      <c r="E58" s="111"/>
+      <c r="F58" s="111"/>
+      <c r="G58" s="111"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="107"/>
-      <c r="B59" s="107"/>
-      <c r="C59" s="107"/>
-      <c r="D59" s="107"/>
-      <c r="E59" s="107"/>
-      <c r="F59" s="107"/>
-      <c r="G59" s="107"/>
+      <c r="A59" s="111"/>
+      <c r="B59" s="111"/>
+      <c r="C59" s="111"/>
+      <c r="D59" s="111"/>
+      <c r="E59" s="111"/>
+      <c r="F59" s="111"/>
+      <c r="G59" s="111"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3262,13 +3304,13 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="109" t="s">
-        <v>72</v>
+      <c r="A1" s="113" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="110" t="s">
-        <v>73</v>
+      <c r="A2" s="114" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="409.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3296,13 +3338,13 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="109" t="s">
-        <v>74</v>
+      <c r="A1" s="113" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="110" t="s">
-        <v>75</v>
+      <c r="A2" s="114" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="379.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3330,13 +3372,13 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="111" t="s">
-        <v>76</v>
+      <c r="A1" s="115" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="112" t="s">
-        <v>77</v>
+      <c r="A2" s="116" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="379.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3365,92 +3407,92 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="113" t="s">
-        <v>78</v>
+      <c r="A1" s="117" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="112" t="s">
-        <v>85</v>
+      <c r="A7" s="116" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="112" t="s">
-        <v>90</v>
+      <c r="A13" s="116" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="112" t="s">
-        <v>95</v>
+      <c r="A19" s="116" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B20" s="1" t="n">
         <v>280</v>
@@ -3458,33 +3500,33 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B21" s="1" t="n">
         <v>28</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="114" t="s">
-        <v>98</v>
-      </c>
-      <c r="B22" s="114" t="n">
+      <c r="A22" s="118" t="s">
+        <v>99</v>
+      </c>
+      <c r="B22" s="118" t="n">
         <v>308</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/LibroCuentas_PTP_2026.xlsx
+++ b/LibroCuentas_PTP_2026.xlsx
@@ -452,7 +452,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -633,6 +633,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC9A227"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC9A227"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC9A227"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC9A227"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -644,7 +658,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="247">
+  <cellXfs count="250">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1366,6 +1380,9 @@
     <xf numFmtId="165" fontId="48" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="48" fillId="5" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="5" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="48" fillId="5" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2028,34 +2045,34 @@
       <c r="F17" s="127" t="n"/>
     </row>
     <row r="18" ht="19.5" customHeight="1" s="120">
-      <c r="A18" s="243" t="n">
+      <c r="A18" s="247" t="n">
         <v>46197</v>
       </c>
-      <c r="B18" s="153" t="inlineStr">
+      <c r="B18" s="248" t="inlineStr">
         <is>
           <t>Venta Lotería</t>
         </is>
       </c>
-      <c r="C18" s="153" t="n"/>
-      <c r="D18" s="244" t="n">
+      <c r="C18" s="248" t="n"/>
+      <c r="D18" s="249" t="n">
         <v>30</v>
       </c>
-      <c r="E18" s="153" t="n"/>
+      <c r="E18" s="248" t="n"/>
     </row>
     <row r="19" ht="19.5" customHeight="1" s="120">
-      <c r="A19" s="243" t="n">
+      <c r="A19" s="247" t="n">
         <v>46197</v>
       </c>
-      <c r="B19" s="153" t="inlineStr">
+      <c r="B19" s="248" t="inlineStr">
         <is>
           <t>Devolución entrada</t>
         </is>
       </c>
-      <c r="C19" s="153" t="n"/>
-      <c r="D19" s="244" t="n">
+      <c r="C19" s="248" t="n"/>
+      <c r="D19" s="249" t="n">
         <v>40</v>
       </c>
-      <c r="E19" s="153" t="n"/>
+      <c r="E19" s="248" t="n"/>
     </row>
     <row r="20" ht="19.5" customHeight="1" s="120">
       <c r="A20" s="154" t="inlineStr">

--- a/LibroCuentas_PTP_2026.xlsx
+++ b/LibroCuentas_PTP_2026.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="103">
   <si>
     <t xml:space="preserve">PEÑA TAURINA PEGUERINOS</t>
   </si>
@@ -101,9 +101,6 @@
   </si>
   <si>
     <t xml:space="preserve">📊 TOTAL PARCIAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saldo →</t>
   </si>
   <si>
     <t xml:space="preserve">TOTALES</t>
@@ -919,7 +916,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="120">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1052,28 +1049,20 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="17" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1116,11 +1105,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1132,11 +1121,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1168,14 +1157,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="167" fontId="21" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1210,14 +1191,6 @@
     </xf>
     <xf numFmtId="164" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="24" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1507,9 +1480,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>3324600</xdr:colOff>
+      <xdr:colOff>3324240</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>124560</xdr:rowOff>
+      <xdr:rowOff>124200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1523,7 +1496,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="600120"/>
-          <a:ext cx="3324600" cy="5706000"/>
+          <a:ext cx="3324240" cy="5705640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1549,9 +1522,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>67320</xdr:colOff>
+      <xdr:colOff>66960</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>4753440</xdr:rowOff>
+      <xdr:rowOff>4753080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1565,7 +1538,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="600120"/>
-          <a:ext cx="5706000" cy="4753440"/>
+          <a:ext cx="5705640" cy="4753080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1591,9 +1564,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>3614040</xdr:colOff>
+      <xdr:colOff>3613680</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>4742640</xdr:rowOff>
+      <xdr:rowOff>4742280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1607,7 +1580,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="566640"/>
-          <a:ext cx="3614040" cy="4757040"/>
+          <a:ext cx="3613680" cy="4756680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1802,7 +1775,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
@@ -2076,320 +2049,330 @@
       <c r="E20" s="34"/>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="36" t="s">
+      <c r="A21" s="33" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B21" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="34"/>
+      <c r="D21" s="35" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="E21" s="34"/>
+    </row>
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="37"/>
-      <c r="C21" s="38" t="s">
+      <c r="D22" s="37" t="n">
+        <f aca="false">SUM(D6:D21)</f>
+        <v>1080.5</v>
+      </c>
+      <c r="E22" s="38" t="n">
+        <f aca="false">SUM(E6:E21)</f>
+        <v>618</v>
+      </c>
+      <c r="F22" s="39" t="n">
+        <f aca="false">D22-E22</f>
+        <v>462.5</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="40"/>
+      <c r="B23" s="40"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="42"/>
+    </row>
+    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="39" t="n">
-        <f aca="false">SUM(D6:D20)</f>
-        <v>1060</v>
-      </c>
-      <c r="E21" s="40" t="n">
-        <f aca="false">SUM(E6:E20)</f>
+      <c r="B24" s="43"/>
+      <c r="C24" s="43"/>
+      <c r="D24" s="44" t="n">
+        <f aca="false">SUM(D6:D21)</f>
+        <v>1080.5</v>
+      </c>
+      <c r="E24" s="44" t="n">
+        <f aca="false">SUM(E6:E21)</f>
         <v>618</v>
       </c>
-      <c r="F21" s="41" t="n">
-        <f aca="false">D21-E21</f>
-        <v>442</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="42"/>
-      <c r="B22" s="42"/>
-      <c r="C22" s="42"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="43"/>
-      <c r="F22" s="44"/>
-    </row>
-    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="45" t="s">
+      <c r="F24" s="45" t="n">
+        <f aca="false">D24-E24</f>
+        <v>462.5</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="45"/>
-      <c r="C23" s="45"/>
-      <c r="D23" s="46" t="n">
-        <f aca="false">SUM(D6:D20)</f>
-        <v>1060</v>
-      </c>
-      <c r="E23" s="46" t="n">
-        <f aca="false">SUM(E6:E20)</f>
+      <c r="B25" s="47"/>
+      <c r="C25" s="48"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="50" t="n">
+        <f aca="false">D22-E22</f>
+        <v>462.5</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="51"/>
+      <c r="C26" s="52"/>
+      <c r="D26" s="44" t="n">
+        <f aca="false">D24</f>
+        <v>1080.5</v>
+      </c>
+      <c r="E26" s="53" t="n">
+        <f aca="false">E24</f>
         <v>618</v>
       </c>
-      <c r="F23" s="47" t="n">
-        <f aca="false">D23-E23</f>
-        <v>442</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="B24" s="49"/>
-      <c r="C24" s="50"/>
-      <c r="D24" s="51"/>
-      <c r="E24" s="51"/>
-      <c r="F24" s="52" t="n">
-        <f aca="false">D21-E21</f>
-        <v>442</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="45" t="s">
+      <c r="F26" s="54"/>
+    </row>
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="53"/>
-      <c r="C25" s="54"/>
-      <c r="D25" s="46" t="n">
-        <f aca="false">D23</f>
-        <v>1060</v>
-      </c>
-      <c r="E25" s="55" t="n">
-        <f aca="false">E23</f>
+      <c r="B27" s="51"/>
+      <c r="C27" s="52"/>
+      <c r="D27" s="53"/>
+      <c r="E27" s="44" t="n">
+        <f aca="false">E22</f>
         <v>618</v>
       </c>
-      <c r="F25" s="56"/>
-    </row>
-    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="45" t="s">
-        <v>29</v>
-      </c>
-      <c r="B26" s="53"/>
-      <c r="C26" s="54"/>
-      <c r="D26" s="55"/>
-      <c r="E26" s="46" t="n">
-        <f aca="false">E21</f>
-        <v>618</v>
-      </c>
-      <c r="F26" s="56"/>
-    </row>
-    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="42"/>
-      <c r="B27" s="44"/>
-      <c r="C27" s="57"/>
-      <c r="D27" s="43"/>
-      <c r="E27" s="43"/>
-      <c r="F27" s="44"/>
+      <c r="F27" s="54"/>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="42"/>
-      <c r="B28" s="44"/>
-      <c r="C28" s="57"/>
-      <c r="D28" s="43"/>
-      <c r="E28" s="43"/>
-      <c r="F28" s="44"/>
+      <c r="A28" s="40"/>
+      <c r="B28" s="42"/>
+      <c r="C28" s="55"/>
+      <c r="D28" s="41"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="42"/>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="42"/>
-      <c r="B29" s="44"/>
-      <c r="C29" s="57"/>
-      <c r="D29" s="43"/>
-      <c r="E29" s="43"/>
-      <c r="F29" s="44"/>
+      <c r="A29" s="40"/>
+      <c r="B29" s="42"/>
+      <c r="C29" s="55"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="42"/>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="42"/>
-      <c r="B30" s="44"/>
-      <c r="C30" s="57"/>
-      <c r="D30" s="43"/>
-      <c r="E30" s="43"/>
-      <c r="F30" s="44"/>
+      <c r="A30" s="40"/>
+      <c r="B30" s="42"/>
+      <c r="C30" s="55"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="41"/>
+      <c r="F30" s="42"/>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="42"/>
-      <c r="B31" s="44"/>
-      <c r="C31" s="57"/>
-      <c r="D31" s="43"/>
-      <c r="E31" s="43"/>
-      <c r="F31" s="44"/>
+      <c r="A31" s="40"/>
+      <c r="B31" s="42"/>
+      <c r="C31" s="55"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="42"/>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="42"/>
-      <c r="B32" s="44"/>
-      <c r="C32" s="57"/>
-      <c r="D32" s="43"/>
-      <c r="E32" s="43"/>
-      <c r="F32" s="44"/>
+      <c r="A32" s="40"/>
+      <c r="B32" s="42"/>
+      <c r="C32" s="55"/>
+      <c r="D32" s="41"/>
+      <c r="E32" s="41"/>
+      <c r="F32" s="42"/>
     </row>
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="42"/>
-      <c r="B33" s="44"/>
-      <c r="C33" s="57"/>
-      <c r="D33" s="43"/>
-      <c r="E33" s="43"/>
-      <c r="F33" s="44"/>
+      <c r="A33" s="40"/>
+      <c r="B33" s="42"/>
+      <c r="C33" s="55"/>
+      <c r="D33" s="41"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="42"/>
     </row>
     <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="42"/>
-      <c r="B34" s="44"/>
-      <c r="C34" s="57"/>
-      <c r="D34" s="43"/>
-      <c r="E34" s="43"/>
-      <c r="F34" s="44"/>
+      <c r="A34" s="40"/>
+      <c r="B34" s="42"/>
+      <c r="C34" s="55"/>
+      <c r="D34" s="41"/>
+      <c r="E34" s="41"/>
+      <c r="F34" s="42"/>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="42"/>
-      <c r="B35" s="44"/>
-      <c r="C35" s="57"/>
-      <c r="D35" s="43"/>
-      <c r="E35" s="43"/>
-      <c r="F35" s="44"/>
+      <c r="A35" s="40"/>
+      <c r="B35" s="42"/>
+      <c r="C35" s="55"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="41"/>
+      <c r="F35" s="42"/>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="42"/>
-      <c r="B36" s="44"/>
-      <c r="C36" s="57"/>
-      <c r="D36" s="43"/>
-      <c r="E36" s="43"/>
-      <c r="F36" s="44"/>
+      <c r="A36" s="40"/>
+      <c r="B36" s="42"/>
+      <c r="C36" s="55"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="41"/>
+      <c r="F36" s="42"/>
     </row>
     <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="42"/>
-      <c r="B37" s="44"/>
-      <c r="C37" s="57"/>
-      <c r="D37" s="43"/>
-      <c r="E37" s="43"/>
-      <c r="F37" s="44"/>
+      <c r="A37" s="40"/>
+      <c r="B37" s="42"/>
+      <c r="C37" s="55"/>
+      <c r="D37" s="41"/>
+      <c r="E37" s="41"/>
+      <c r="F37" s="42"/>
     </row>
     <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="42"/>
-      <c r="B38" s="44"/>
-      <c r="C38" s="57"/>
-      <c r="D38" s="43"/>
-      <c r="E38" s="43"/>
-      <c r="F38" s="44"/>
+      <c r="A38" s="40"/>
+      <c r="B38" s="42"/>
+      <c r="C38" s="55"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="41"/>
+      <c r="F38" s="42"/>
     </row>
     <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="42"/>
-      <c r="B39" s="44"/>
-      <c r="C39" s="57"/>
-      <c r="D39" s="43"/>
-      <c r="E39" s="43"/>
-      <c r="F39" s="44"/>
+      <c r="A39" s="40"/>
+      <c r="B39" s="42"/>
+      <c r="C39" s="55"/>
+      <c r="D39" s="41"/>
+      <c r="E39" s="41"/>
+      <c r="F39" s="42"/>
     </row>
     <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="42"/>
-      <c r="B40" s="44"/>
-      <c r="C40" s="57"/>
-      <c r="D40" s="43"/>
-      <c r="E40" s="43"/>
-      <c r="F40" s="44"/>
+      <c r="A40" s="40"/>
+      <c r="B40" s="42"/>
+      <c r="C40" s="55"/>
+      <c r="D40" s="41"/>
+      <c r="E40" s="41"/>
+      <c r="F40" s="42"/>
     </row>
     <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="42"/>
-      <c r="B41" s="44"/>
-      <c r="C41" s="57"/>
-      <c r="D41" s="43"/>
-      <c r="E41" s="43"/>
-      <c r="F41" s="44"/>
+      <c r="A41" s="40"/>
+      <c r="B41" s="42"/>
+      <c r="C41" s="55"/>
+      <c r="D41" s="41"/>
+      <c r="E41" s="41"/>
+      <c r="F41" s="42"/>
     </row>
     <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="42"/>
-      <c r="B42" s="44"/>
-      <c r="C42" s="57"/>
-      <c r="D42" s="43"/>
-      <c r="E42" s="43"/>
-      <c r="F42" s="44"/>
+      <c r="A42" s="40"/>
+      <c r="B42" s="42"/>
+      <c r="C42" s="55"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="41"/>
+      <c r="F42" s="42"/>
     </row>
     <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="42"/>
-      <c r="B43" s="44"/>
-      <c r="C43" s="57"/>
-      <c r="D43" s="43"/>
-      <c r="E43" s="43"/>
-      <c r="F43" s="44"/>
+      <c r="A43" s="40"/>
+      <c r="B43" s="42"/>
+      <c r="C43" s="55"/>
+      <c r="D43" s="41"/>
+      <c r="E43" s="41"/>
+      <c r="F43" s="42"/>
     </row>
     <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="42"/>
-      <c r="B44" s="44"/>
-      <c r="C44" s="57"/>
-      <c r="D44" s="43"/>
-      <c r="E44" s="43"/>
-      <c r="F44" s="44"/>
+      <c r="A44" s="40"/>
+      <c r="B44" s="42"/>
+      <c r="C44" s="55"/>
+      <c r="D44" s="41"/>
+      <c r="E44" s="41"/>
+      <c r="F44" s="42"/>
     </row>
     <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="42"/>
-      <c r="B45" s="44"/>
-      <c r="C45" s="57"/>
-      <c r="D45" s="43"/>
-      <c r="E45" s="43"/>
-      <c r="F45" s="44"/>
+      <c r="A45" s="40"/>
+      <c r="B45" s="42"/>
+      <c r="C45" s="55"/>
+      <c r="D45" s="41"/>
+      <c r="E45" s="41"/>
+      <c r="F45" s="42"/>
     </row>
     <row r="46" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="58"/>
-      <c r="B46" s="59"/>
-      <c r="C46" s="60"/>
-      <c r="D46" s="51"/>
-      <c r="E46" s="51"/>
-      <c r="F46" s="59"/>
+      <c r="A46" s="40"/>
+      <c r="B46" s="42"/>
+      <c r="C46" s="55"/>
+      <c r="D46" s="41"/>
+      <c r="E46" s="41"/>
+      <c r="F46" s="42"/>
     </row>
     <row r="47" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="61"/>
-      <c r="B47" s="62"/>
-      <c r="C47" s="63"/>
-      <c r="D47" s="55"/>
-      <c r="E47" s="55"/>
-      <c r="F47" s="56"/>
+      <c r="A47" s="56"/>
+      <c r="B47" s="57"/>
+      <c r="C47" s="58"/>
+      <c r="D47" s="49"/>
+      <c r="E47" s="49"/>
+      <c r="F47" s="57"/>
     </row>
     <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="64"/>
-      <c r="B48" s="59"/>
-      <c r="C48" s="60"/>
-      <c r="D48" s="51"/>
-      <c r="E48" s="51"/>
-      <c r="F48" s="65"/>
+      <c r="A48" s="59"/>
+      <c r="B48" s="51"/>
+      <c r="C48" s="52"/>
+      <c r="D48" s="53"/>
+      <c r="E48" s="53"/>
+      <c r="F48" s="54"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="66"/>
-      <c r="B49" s="62"/>
-      <c r="C49" s="63"/>
-      <c r="D49" s="67"/>
-      <c r="E49" s="55"/>
-      <c r="F49" s="56"/>
+      <c r="A49" s="60"/>
+      <c r="B49" s="57"/>
+      <c r="C49" s="58"/>
+      <c r="D49" s="49"/>
+      <c r="E49" s="49"/>
+      <c r="F49" s="61"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="68"/>
-      <c r="D50" s="55"/>
-      <c r="E50" s="69"/>
-      <c r="F50" s="56"/>
+      <c r="A50" s="62"/>
+      <c r="B50" s="51"/>
+      <c r="C50" s="52"/>
+      <c r="D50" s="63"/>
+      <c r="E50" s="53"/>
+      <c r="F50" s="54"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="70"/>
-      <c r="D51" s="71"/>
-      <c r="E51" s="71"/>
-      <c r="F51" s="72"/>
+      <c r="A51" s="64"/>
+      <c r="D51" s="53"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="54"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="58"/>
-      <c r="B52" s="73"/>
-      <c r="C52" s="74"/>
-      <c r="D52" s="51"/>
-      <c r="E52" s="51"/>
-      <c r="F52" s="59"/>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="75"/>
-      <c r="B54" s="62"/>
-      <c r="C54" s="63"/>
-      <c r="D54" s="55"/>
-      <c r="E54" s="55"/>
-      <c r="F54" s="76"/>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="77"/>
-      <c r="B55" s="73"/>
-      <c r="C55" s="74"/>
-      <c r="F55" s="78"/>
+      <c r="A52" s="66"/>
+      <c r="D52" s="67"/>
+      <c r="E52" s="67"/>
+      <c r="F52" s="68"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="56"/>
+      <c r="B53" s="47"/>
+      <c r="C53" s="48"/>
+      <c r="D53" s="49"/>
+      <c r="E53" s="49"/>
+      <c r="F53" s="57"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="69"/>
+      <c r="B55" s="51"/>
+      <c r="C55" s="52"/>
+      <c r="D55" s="53"/>
+      <c r="E55" s="53"/>
+      <c r="F55" s="70"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="71"/>
+      <c r="B56" s="47"/>
+      <c r="C56" s="48"/>
+      <c r="F56" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A24:C24"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C8" location="'Ticket Cena'!A1" display="🧾 Ver Ticket Cena"/>
@@ -2418,162 +2401,162 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="79" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
+      <c r="A1" s="73" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="80" t="s">
+      <c r="A2" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="80"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
     </row>
     <row r="3" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="5" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="75" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="81" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="82" t="n">
+      <c r="B5" s="76" t="n">
         <v>800</v>
       </c>
-      <c r="C5" s="82" t="n">
+      <c r="C5" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="82" t="n">
+      <c r="D5" s="76" t="n">
         <f aca="false">B5-C5</f>
         <v>800</v>
       </c>
-      <c r="E5" s="83"/>
-      <c r="F5" s="83"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="81" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" s="82" t="n">
+      <c r="A6" s="75" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="C6" s="82" t="n">
+      <c r="C6" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="82" t="n">
+      <c r="D6" s="76" t="n">
         <f aca="false">B6-C6</f>
         <v>0</v>
       </c>
-      <c r="E6" s="83"/>
-      <c r="F6" s="83"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="84" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="85" t="n">
+      <c r="A7" s="78" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="79" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="85" t="n">
+      <c r="C7" s="79" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="85" t="n">
+      <c r="D7" s="79" t="n">
         <f aca="false">B7-C7</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="84" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="85" t="n">
+      <c r="A8" s="78" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="79" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="85" t="n">
+      <c r="C8" s="79" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="85" t="n">
+      <c r="D8" s="79" t="n">
         <f aca="false">B8-C8</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="86" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="87" t="n">
+      <c r="A9" s="80" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="87" t="n">
+      <c r="C9" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="87" t="n">
+      <c r="D9" s="81" t="n">
         <f aca="false">B9-C9</f>
         <v>0</v>
       </c>
-      <c r="E9" s="88"/>
-      <c r="F9" s="88"/>
+      <c r="E9" s="82"/>
+      <c r="F9" s="82"/>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="81" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="82" t="n">
+      <c r="A10" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="82" t="n">
+      <c r="C10" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="82" t="n">
+      <c r="D10" s="76" t="n">
         <f aca="false">B10-C10</f>
         <v>0</v>
       </c>
-      <c r="E10" s="83"/>
-      <c r="F10" s="83"/>
+      <c r="E10" s="77"/>
+      <c r="F10" s="77"/>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="84" t="s">
-        <v>41</v>
-      </c>
-      <c r="B11" s="85" t="n">
+      <c r="A11" s="78" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="79" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="85" t="n">
+      <c r="C11" s="79" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="85" t="n">
+      <c r="D11" s="79" t="n">
         <f aca="false">B11-C11</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="89" t="s">
-        <v>42</v>
-      </c>
-      <c r="B12" s="55" t="n">
+      <c r="A12" s="83" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="53" t="n">
         <f aca="false">SUM(B5:B11)</f>
         <v>800</v>
       </c>
-      <c r="C12" s="55" t="n">
+      <c r="C12" s="53" t="n">
         <f aca="false">SUM(C5:C11)</f>
         <v>0</v>
       </c>
-      <c r="D12" s="55" t="n">
+      <c r="D12" s="53" t="n">
         <f aca="false">B12-C12</f>
         <v>800</v>
       </c>
@@ -2608,745 +2591,745 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="73" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+    </row>
+    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="84" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-    </row>
-    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="90" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="90"/>
-      <c r="C2" s="90"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="90"/>
-      <c r="F2" s="90"/>
-      <c r="G2" s="90"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
     </row>
     <row r="3" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="91" t="s">
+      <c r="A4" s="85" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="85" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="91" t="s">
+      <c r="C4" s="85" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="91" t="s">
+      <c r="D4" s="85" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="91" t="s">
+      <c r="E4" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="91" t="s">
+      <c r="F4" s="85" t="s">
         <v>49</v>
       </c>
-      <c r="F4" s="91" t="s">
+      <c r="G4" s="86" t="s">
         <v>50</v>
       </c>
-      <c r="G4" s="92" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="87" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="88" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="93" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="94" t="s">
+      <c r="C5" s="89" t="n">
+        <v>50</v>
+      </c>
+      <c r="D5" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="C5" s="95" t="n">
+      <c r="E5" s="89" t="n">
         <v>50</v>
       </c>
-      <c r="D5" s="96" t="s">
+      <c r="F5" s="91" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="95" t="n">
+      <c r="G5" s="92"/>
+    </row>
+    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="87" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="88"/>
+      <c r="C6" s="89"/>
+      <c r="D6" s="90"/>
+      <c r="E6" s="89"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="92"/>
+    </row>
+    <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="93" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="94" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="95" t="n">
         <v>50</v>
       </c>
-      <c r="F5" s="97" t="s">
-        <v>54</v>
-      </c>
-      <c r="G5" s="98"/>
-    </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="93" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="94"/>
-      <c r="C6" s="95"/>
-      <c r="D6" s="96"/>
-      <c r="E6" s="95"/>
-      <c r="F6" s="97"/>
-      <c r="G6" s="98"/>
-    </row>
-    <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="99" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="100" t="s">
+      <c r="D7" s="96" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="95" t="n">
+        <v>50</v>
+      </c>
+      <c r="F7" s="97" t="s">
+        <v>53</v>
+      </c>
+      <c r="G7" s="98"/>
+    </row>
+    <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="87" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="88" t="s">
         <v>55</v>
       </c>
-      <c r="C7" s="101" t="n">
+      <c r="C8" s="89" t="n">
         <v>50</v>
       </c>
-      <c r="D7" s="102" t="s">
+      <c r="D8" s="90" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="89" t="n">
+        <v>50</v>
+      </c>
+      <c r="F8" s="91" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="101" t="n">
+      <c r="G8" s="92"/>
+    </row>
+    <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="93" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="94" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="95" t="n">
         <v>50</v>
       </c>
-      <c r="F7" s="103" t="s">
-        <v>54</v>
-      </c>
-      <c r="G7" s="104"/>
-    </row>
-    <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="93" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="94" t="s">
-        <v>56</v>
-      </c>
-      <c r="C8" s="95" t="n">
+      <c r="D9" s="96" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="95" t="n">
         <v>50</v>
       </c>
-      <c r="D8" s="96" t="s">
+      <c r="F9" s="97" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="95" t="n">
+      <c r="G9" s="98"/>
+    </row>
+    <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="87" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="88" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="89" t="n">
         <v>50</v>
       </c>
-      <c r="F8" s="97" t="s">
-        <v>54</v>
-      </c>
-      <c r="G8" s="98"/>
-    </row>
-    <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="99" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="100" t="s">
-        <v>57</v>
-      </c>
-      <c r="C9" s="101" t="n">
+      <c r="D10" s="90" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" s="89" t="n">
         <v>50</v>
       </c>
-      <c r="D9" s="102" t="s">
+      <c r="F10" s="91" t="s">
         <v>53</v>
       </c>
-      <c r="E9" s="101" t="n">
+      <c r="G10" s="92"/>
+    </row>
+    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="93" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="94" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="95" t="n">
         <v>50</v>
       </c>
-      <c r="F9" s="103" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9" s="104"/>
-    </row>
-    <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="93" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="94" t="s">
-        <v>58</v>
-      </c>
-      <c r="C10" s="95" t="n">
+      <c r="D11" s="96" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" s="95" t="n">
         <v>50</v>
       </c>
-      <c r="D10" s="96" t="s">
+      <c r="F11" s="97" t="s">
         <v>53</v>
       </c>
-      <c r="E10" s="95" t="n">
+      <c r="G11" s="98"/>
+    </row>
+    <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="87" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="88" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="89" t="n">
         <v>50</v>
       </c>
-      <c r="F10" s="97" t="s">
-        <v>54</v>
-      </c>
-      <c r="G10" s="98"/>
-    </row>
-    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="99" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="100" t="s">
-        <v>59</v>
-      </c>
-      <c r="C11" s="101" t="n">
+      <c r="D12" s="90" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="89" t="n">
         <v>50</v>
       </c>
-      <c r="D11" s="102" t="s">
+      <c r="F12" s="91" t="s">
         <v>53</v>
       </c>
-      <c r="E11" s="101" t="n">
+      <c r="G12" s="92"/>
+    </row>
+    <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="93" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="94" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="95" t="n">
         <v>50</v>
       </c>
-      <c r="F11" s="103" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11" s="104"/>
-    </row>
-    <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="93" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="94" t="s">
-        <v>60</v>
-      </c>
-      <c r="C12" s="95" t="n">
+      <c r="D13" s="96" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="95" t="n">
         <v>50</v>
       </c>
-      <c r="D12" s="96" t="s">
+      <c r="F13" s="97" t="s">
         <v>53</v>
       </c>
-      <c r="E12" s="95" t="n">
+      <c r="G13" s="98"/>
+    </row>
+    <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="87" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="88" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="89" t="n">
         <v>50</v>
       </c>
-      <c r="F12" s="97" t="s">
-        <v>54</v>
-      </c>
-      <c r="G12" s="98"/>
-    </row>
-    <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="99" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="100" t="s">
-        <v>61</v>
-      </c>
-      <c r="C13" s="101" t="n">
+      <c r="D14" s="90" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="89" t="n">
         <v>50</v>
       </c>
-      <c r="D13" s="102" t="s">
+      <c r="F14" s="91" t="s">
         <v>53</v>
       </c>
-      <c r="E13" s="101" t="n">
+      <c r="G14" s="92"/>
+    </row>
+    <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="93" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="94" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" s="95" t="n">
         <v>50</v>
       </c>
-      <c r="F13" s="103" t="s">
-        <v>54</v>
-      </c>
-      <c r="G13" s="104"/>
-    </row>
-    <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="93" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="94" t="s">
-        <v>62</v>
-      </c>
-      <c r="C14" s="95" t="n">
+      <c r="D15" s="96" t="s">
+        <v>52</v>
+      </c>
+      <c r="E15" s="95" t="n">
         <v>50</v>
       </c>
-      <c r="D14" s="96" t="s">
+      <c r="F15" s="97" t="s">
         <v>53</v>
       </c>
-      <c r="E14" s="95" t="n">
+      <c r="G15" s="98"/>
+    </row>
+    <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="87" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="88" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="89" t="n">
         <v>50</v>
       </c>
-      <c r="F14" s="97" t="s">
-        <v>54</v>
-      </c>
-      <c r="G14" s="98"/>
-    </row>
-    <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="99" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="100" t="s">
-        <v>63</v>
-      </c>
-      <c r="C15" s="101" t="n">
+      <c r="D16" s="91" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" s="89" t="n">
         <v>50</v>
       </c>
-      <c r="D15" s="102" t="s">
+      <c r="F16" s="91" t="s">
         <v>53</v>
       </c>
-      <c r="E15" s="101" t="n">
+      <c r="G16" s="92"/>
+    </row>
+    <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="87" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="99" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="100" t="n">
         <v>50</v>
       </c>
-      <c r="F15" s="103" t="s">
-        <v>54</v>
-      </c>
-      <c r="G15" s="104"/>
-    </row>
-    <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="93" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="94" t="s">
-        <v>64</v>
-      </c>
-      <c r="C16" s="95" t="n">
+      <c r="D17" s="101" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17" s="100" t="n">
         <v>50</v>
       </c>
-      <c r="D16" s="97" t="s">
-        <v>65</v>
-      </c>
-      <c r="E16" s="95" t="n">
+      <c r="F17" s="101" t="s">
+        <v>53</v>
+      </c>
+      <c r="G17" s="102"/>
+    </row>
+    <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="93" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="103" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="104" t="n">
         <v>50</v>
       </c>
-      <c r="F16" s="97" t="s">
-        <v>54</v>
-      </c>
-      <c r="G16" s="98"/>
-    </row>
-    <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="93" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="105" t="s">
+      <c r="D18" s="105" t="s">
         <v>66</v>
       </c>
-      <c r="C17" s="106" t="n">
+      <c r="E18" s="104" t="n">
         <v>50</v>
       </c>
-      <c r="D17" s="107" t="s">
-        <v>67</v>
-      </c>
-      <c r="E17" s="106" t="n">
+      <c r="F18" s="105" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18" s="106"/>
+    </row>
+    <row r="19" s="108" customFormat="true" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="93" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="103" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="104" t="n">
         <v>50</v>
       </c>
-      <c r="F17" s="107" t="s">
-        <v>54</v>
-      </c>
-      <c r="G17" s="108"/>
-    </row>
-    <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="99" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="109" t="s">
-        <v>68</v>
-      </c>
-      <c r="C18" s="110" t="n">
+      <c r="D19" s="105" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" s="104" t="n">
         <v>50</v>
       </c>
-      <c r="D18" s="111" t="s">
-        <v>67</v>
-      </c>
-      <c r="E18" s="110" t="n">
+      <c r="F19" s="105" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19" s="107"/>
+    </row>
+    <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="93" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="103" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20" s="104" t="n">
         <v>50</v>
       </c>
-      <c r="F18" s="111" t="s">
-        <v>54</v>
-      </c>
-      <c r="G18" s="112"/>
-    </row>
-    <row r="19" s="114" customFormat="true" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="99" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="109" t="s">
+      <c r="D20" s="105" t="s">
         <v>69</v>
       </c>
-      <c r="C19" s="110" t="n">
+      <c r="E20" s="104" t="n">
         <v>50</v>
       </c>
-      <c r="D19" s="111" t="s">
-        <v>70</v>
-      </c>
-      <c r="E19" s="110" t="n">
+      <c r="F20" s="105" t="s">
+        <v>53</v>
+      </c>
+      <c r="G20" s="98"/>
+    </row>
+    <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="93" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="103" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" s="104" t="n">
         <v>50</v>
       </c>
-      <c r="F19" s="111" t="s">
-        <v>54</v>
-      </c>
-      <c r="G19" s="113"/>
-    </row>
-    <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="99" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="109" t="s">
-        <v>71</v>
-      </c>
-      <c r="C20" s="110" t="n">
+      <c r="D21" s="105" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" s="104" t="n">
         <v>50</v>
       </c>
-      <c r="D20" s="111" t="s">
-        <v>70</v>
-      </c>
-      <c r="E20" s="110" t="n">
-        <v>50</v>
-      </c>
-      <c r="F20" s="111" t="s">
-        <v>54</v>
-      </c>
-      <c r="G20" s="104"/>
-    </row>
-    <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="99" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="109" t="s">
+      <c r="F21" s="105" t="s">
+        <v>53</v>
+      </c>
+      <c r="G21" s="107"/>
+    </row>
+    <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="93"/>
+      <c r="B22" s="103"/>
+      <c r="C22" s="104"/>
+      <c r="D22" s="105"/>
+      <c r="E22" s="104"/>
+      <c r="F22" s="105"/>
+      <c r="G22" s="107"/>
+    </row>
+    <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="93"/>
+      <c r="B23" s="103"/>
+      <c r="C23" s="104"/>
+      <c r="D23" s="105"/>
+      <c r="E23" s="104"/>
+      <c r="F23" s="105"/>
+      <c r="G23" s="106"/>
+    </row>
+    <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="93"/>
+      <c r="B24" s="103"/>
+      <c r="C24" s="104"/>
+      <c r="D24" s="105"/>
+      <c r="E24" s="104"/>
+      <c r="F24" s="105"/>
+      <c r="G24" s="106"/>
+    </row>
+    <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="93"/>
+      <c r="B25" s="103"/>
+      <c r="C25" s="104"/>
+      <c r="D25" s="105"/>
+      <c r="E25" s="104"/>
+      <c r="F25" s="105"/>
+      <c r="G25" s="106"/>
+    </row>
+    <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="109" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="110" t="n">
-        <v>50</v>
-      </c>
-      <c r="D21" s="111" t="s">
-        <v>70</v>
-      </c>
-      <c r="E21" s="110" t="n">
-        <v>50</v>
-      </c>
-      <c r="F21" s="111" t="s">
-        <v>54</v>
-      </c>
-      <c r="G21" s="113"/>
-    </row>
-    <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="99"/>
-      <c r="B22" s="109"/>
-      <c r="C22" s="110"/>
-      <c r="D22" s="111"/>
-      <c r="E22" s="110"/>
-      <c r="F22" s="111"/>
-      <c r="G22" s="113"/>
-    </row>
-    <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="99"/>
-      <c r="B23" s="109"/>
-      <c r="C23" s="110"/>
-      <c r="D23" s="111"/>
-      <c r="E23" s="110"/>
-      <c r="F23" s="111"/>
-      <c r="G23" s="112"/>
-    </row>
-    <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="99"/>
-      <c r="B24" s="109"/>
-      <c r="C24" s="110"/>
-      <c r="D24" s="111"/>
-      <c r="E24" s="110"/>
-      <c r="F24" s="111"/>
-      <c r="G24" s="112"/>
-    </row>
-    <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="99"/>
-      <c r="B25" s="109"/>
-      <c r="C25" s="110"/>
-      <c r="D25" s="111"/>
-      <c r="E25" s="110"/>
-      <c r="F25" s="111"/>
-      <c r="G25" s="112"/>
-    </row>
-    <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="115" t="s">
-        <v>73</v>
-      </c>
-      <c r="B26" s="115"/>
-      <c r="C26" s="116" t="n">
+      <c r="B26" s="109"/>
+      <c r="C26" s="110" t="n">
         <v>800</v>
       </c>
-      <c r="D26" s="117"/>
-      <c r="E26" s="116" t="n">
+      <c r="D26" s="111"/>
+      <c r="E26" s="110" t="n">
         <v>0</v>
       </c>
-      <c r="F26" s="117"/>
-      <c r="G26" s="117"/>
+      <c r="F26" s="111"/>
+      <c r="G26" s="111"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="118"/>
-      <c r="B27" s="118"/>
-      <c r="C27" s="119"/>
-      <c r="D27" s="118"/>
-      <c r="E27" s="118"/>
-      <c r="F27" s="118"/>
-      <c r="G27" s="118"/>
+      <c r="A27" s="112"/>
+      <c r="B27" s="112"/>
+      <c r="C27" s="113"/>
+      <c r="D27" s="112"/>
+      <c r="E27" s="112"/>
+      <c r="F27" s="112"/>
+      <c r="G27" s="112"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="118"/>
-      <c r="B28" s="118"/>
-      <c r="C28" s="118"/>
-      <c r="D28" s="118"/>
-      <c r="E28" s="118"/>
-      <c r="F28" s="118"/>
-      <c r="G28" s="118"/>
+      <c r="A28" s="112"/>
+      <c r="B28" s="112"/>
+      <c r="C28" s="112"/>
+      <c r="D28" s="112"/>
+      <c r="E28" s="112"/>
+      <c r="F28" s="112"/>
+      <c r="G28" s="112"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="118"/>
-      <c r="B29" s="118"/>
-      <c r="C29" s="118"/>
-      <c r="D29" s="118"/>
-      <c r="E29" s="118"/>
-      <c r="F29" s="118"/>
-      <c r="G29" s="118"/>
+      <c r="A29" s="112"/>
+      <c r="B29" s="112"/>
+      <c r="C29" s="112"/>
+      <c r="D29" s="112"/>
+      <c r="E29" s="112"/>
+      <c r="F29" s="112"/>
+      <c r="G29" s="112"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="118"/>
-      <c r="B30" s="118"/>
-      <c r="C30" s="118"/>
-      <c r="D30" s="118"/>
-      <c r="E30" s="118"/>
-      <c r="F30" s="118"/>
-      <c r="G30" s="118"/>
+      <c r="A30" s="112"/>
+      <c r="B30" s="112"/>
+      <c r="C30" s="112"/>
+      <c r="D30" s="112"/>
+      <c r="E30" s="112"/>
+      <c r="F30" s="112"/>
+      <c r="G30" s="112"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="118"/>
-      <c r="B31" s="118"/>
-      <c r="C31" s="118"/>
-      <c r="D31" s="118"/>
-      <c r="E31" s="118"/>
-      <c r="F31" s="118"/>
-      <c r="G31" s="118"/>
+      <c r="A31" s="112"/>
+      <c r="B31" s="112"/>
+      <c r="C31" s="112"/>
+      <c r="D31" s="112"/>
+      <c r="E31" s="112"/>
+      <c r="F31" s="112"/>
+      <c r="G31" s="112"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="118"/>
-      <c r="B32" s="118"/>
-      <c r="C32" s="118"/>
-      <c r="D32" s="118"/>
-      <c r="E32" s="118"/>
-      <c r="F32" s="118"/>
-      <c r="G32" s="118"/>
+      <c r="A32" s="112"/>
+      <c r="B32" s="112"/>
+      <c r="C32" s="112"/>
+      <c r="D32" s="112"/>
+      <c r="E32" s="112"/>
+      <c r="F32" s="112"/>
+      <c r="G32" s="112"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="118"/>
-      <c r="B33" s="118"/>
-      <c r="C33" s="118"/>
-      <c r="D33" s="118"/>
-      <c r="E33" s="118"/>
-      <c r="F33" s="118"/>
-      <c r="G33" s="118"/>
+      <c r="A33" s="112"/>
+      <c r="B33" s="112"/>
+      <c r="C33" s="112"/>
+      <c r="D33" s="112"/>
+      <c r="E33" s="112"/>
+      <c r="F33" s="112"/>
+      <c r="G33" s="112"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="118"/>
-      <c r="B34" s="118"/>
-      <c r="C34" s="118"/>
-      <c r="D34" s="118"/>
-      <c r="E34" s="118"/>
-      <c r="F34" s="118"/>
-      <c r="G34" s="118"/>
+      <c r="A34" s="112"/>
+      <c r="B34" s="112"/>
+      <c r="C34" s="112"/>
+      <c r="D34" s="112"/>
+      <c r="E34" s="112"/>
+      <c r="F34" s="112"/>
+      <c r="G34" s="112"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="118"/>
-      <c r="B35" s="118"/>
-      <c r="C35" s="118"/>
-      <c r="D35" s="118"/>
-      <c r="E35" s="118"/>
-      <c r="F35" s="118"/>
-      <c r="G35" s="118"/>
+      <c r="A35" s="112"/>
+      <c r="B35" s="112"/>
+      <c r="C35" s="112"/>
+      <c r="D35" s="112"/>
+      <c r="E35" s="112"/>
+      <c r="F35" s="112"/>
+      <c r="G35" s="112"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="118"/>
-      <c r="B36" s="118"/>
-      <c r="C36" s="118"/>
-      <c r="D36" s="118"/>
-      <c r="E36" s="118"/>
-      <c r="F36" s="118"/>
-      <c r="G36" s="118"/>
+      <c r="A36" s="112"/>
+      <c r="B36" s="112"/>
+      <c r="C36" s="112"/>
+      <c r="D36" s="112"/>
+      <c r="E36" s="112"/>
+      <c r="F36" s="112"/>
+      <c r="G36" s="112"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="118"/>
-      <c r="B37" s="118"/>
-      <c r="C37" s="118"/>
-      <c r="D37" s="118"/>
-      <c r="E37" s="118"/>
-      <c r="F37" s="118"/>
-      <c r="G37" s="118"/>
+      <c r="A37" s="112"/>
+      <c r="B37" s="112"/>
+      <c r="C37" s="112"/>
+      <c r="D37" s="112"/>
+      <c r="E37" s="112"/>
+      <c r="F37" s="112"/>
+      <c r="G37" s="112"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="118"/>
-      <c r="B38" s="118"/>
-      <c r="C38" s="118"/>
-      <c r="D38" s="118"/>
-      <c r="E38" s="118"/>
-      <c r="F38" s="118"/>
-      <c r="G38" s="118"/>
+      <c r="A38" s="112"/>
+      <c r="B38" s="112"/>
+      <c r="C38" s="112"/>
+      <c r="D38" s="112"/>
+      <c r="E38" s="112"/>
+      <c r="F38" s="112"/>
+      <c r="G38" s="112"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="118"/>
-      <c r="B39" s="118"/>
-      <c r="C39" s="118"/>
-      <c r="D39" s="118"/>
-      <c r="E39" s="118"/>
-      <c r="F39" s="118"/>
-      <c r="G39" s="118"/>
+      <c r="A39" s="112"/>
+      <c r="B39" s="112"/>
+      <c r="C39" s="112"/>
+      <c r="D39" s="112"/>
+      <c r="E39" s="112"/>
+      <c r="F39" s="112"/>
+      <c r="G39" s="112"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="118"/>
-      <c r="B40" s="118"/>
-      <c r="C40" s="118"/>
-      <c r="D40" s="118"/>
-      <c r="E40" s="118"/>
-      <c r="F40" s="118"/>
-      <c r="G40" s="118"/>
+      <c r="A40" s="112"/>
+      <c r="B40" s="112"/>
+      <c r="C40" s="112"/>
+      <c r="D40" s="112"/>
+      <c r="E40" s="112"/>
+      <c r="F40" s="112"/>
+      <c r="G40" s="112"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="118"/>
-      <c r="B41" s="118"/>
-      <c r="C41" s="118"/>
-      <c r="D41" s="118"/>
-      <c r="E41" s="118"/>
-      <c r="F41" s="118"/>
-      <c r="G41" s="118"/>
+      <c r="A41" s="112"/>
+      <c r="B41" s="112"/>
+      <c r="C41" s="112"/>
+      <c r="D41" s="112"/>
+      <c r="E41" s="112"/>
+      <c r="F41" s="112"/>
+      <c r="G41" s="112"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="118"/>
-      <c r="B42" s="118"/>
-      <c r="C42" s="118"/>
-      <c r="D42" s="118"/>
-      <c r="E42" s="118"/>
-      <c r="F42" s="118"/>
-      <c r="G42" s="118"/>
+      <c r="A42" s="112"/>
+      <c r="B42" s="112"/>
+      <c r="C42" s="112"/>
+      <c r="D42" s="112"/>
+      <c r="E42" s="112"/>
+      <c r="F42" s="112"/>
+      <c r="G42" s="112"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="118"/>
-      <c r="B43" s="118"/>
-      <c r="C43" s="118"/>
-      <c r="D43" s="118"/>
-      <c r="E43" s="118"/>
-      <c r="F43" s="118"/>
-      <c r="G43" s="118"/>
+      <c r="A43" s="112"/>
+      <c r="B43" s="112"/>
+      <c r="C43" s="112"/>
+      <c r="D43" s="112"/>
+      <c r="E43" s="112"/>
+      <c r="F43" s="112"/>
+      <c r="G43" s="112"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="118"/>
-      <c r="B44" s="118"/>
-      <c r="C44" s="118"/>
-      <c r="D44" s="118"/>
-      <c r="E44" s="118"/>
-      <c r="F44" s="118"/>
-      <c r="G44" s="118"/>
+      <c r="A44" s="112"/>
+      <c r="B44" s="112"/>
+      <c r="C44" s="112"/>
+      <c r="D44" s="112"/>
+      <c r="E44" s="112"/>
+      <c r="F44" s="112"/>
+      <c r="G44" s="112"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="118"/>
-      <c r="B45" s="118"/>
-      <c r="C45" s="118"/>
-      <c r="D45" s="118"/>
-      <c r="E45" s="118"/>
-      <c r="F45" s="118"/>
-      <c r="G45" s="118"/>
+      <c r="A45" s="112"/>
+      <c r="B45" s="112"/>
+      <c r="C45" s="112"/>
+      <c r="D45" s="112"/>
+      <c r="E45" s="112"/>
+      <c r="F45" s="112"/>
+      <c r="G45" s="112"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="118"/>
-      <c r="B46" s="118"/>
-      <c r="C46" s="118"/>
-      <c r="D46" s="118"/>
-      <c r="E46" s="118"/>
-      <c r="F46" s="118"/>
-      <c r="G46" s="118"/>
+      <c r="A46" s="112"/>
+      <c r="B46" s="112"/>
+      <c r="C46" s="112"/>
+      <c r="D46" s="112"/>
+      <c r="E46" s="112"/>
+      <c r="F46" s="112"/>
+      <c r="G46" s="112"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="118"/>
-      <c r="B47" s="118"/>
-      <c r="C47" s="118"/>
-      <c r="D47" s="118"/>
-      <c r="E47" s="118"/>
-      <c r="F47" s="118"/>
-      <c r="G47" s="118"/>
+      <c r="A47" s="112"/>
+      <c r="B47" s="112"/>
+      <c r="C47" s="112"/>
+      <c r="D47" s="112"/>
+      <c r="E47" s="112"/>
+      <c r="F47" s="112"/>
+      <c r="G47" s="112"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="118"/>
-      <c r="B48" s="118"/>
-      <c r="C48" s="118"/>
-      <c r="D48" s="118"/>
-      <c r="E48" s="118"/>
-      <c r="F48" s="118"/>
-      <c r="G48" s="118"/>
+      <c r="A48" s="112"/>
+      <c r="B48" s="112"/>
+      <c r="C48" s="112"/>
+      <c r="D48" s="112"/>
+      <c r="E48" s="112"/>
+      <c r="F48" s="112"/>
+      <c r="G48" s="112"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="118"/>
-      <c r="B49" s="118"/>
-      <c r="C49" s="118"/>
-      <c r="D49" s="118"/>
-      <c r="E49" s="118"/>
-      <c r="F49" s="118"/>
-      <c r="G49" s="118"/>
+      <c r="A49" s="112"/>
+      <c r="B49" s="112"/>
+      <c r="C49" s="112"/>
+      <c r="D49" s="112"/>
+      <c r="E49" s="112"/>
+      <c r="F49" s="112"/>
+      <c r="G49" s="112"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="118"/>
-      <c r="B50" s="118"/>
-      <c r="C50" s="118"/>
-      <c r="D50" s="118"/>
-      <c r="E50" s="118"/>
-      <c r="F50" s="118"/>
-      <c r="G50" s="118"/>
+      <c r="A50" s="112"/>
+      <c r="B50" s="112"/>
+      <c r="C50" s="112"/>
+      <c r="D50" s="112"/>
+      <c r="E50" s="112"/>
+      <c r="F50" s="112"/>
+      <c r="G50" s="112"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="118"/>
-      <c r="B51" s="118"/>
-      <c r="C51" s="118"/>
-      <c r="D51" s="118"/>
-      <c r="E51" s="118"/>
-      <c r="F51" s="118"/>
-      <c r="G51" s="118"/>
+      <c r="A51" s="112"/>
+      <c r="B51" s="112"/>
+      <c r="C51" s="112"/>
+      <c r="D51" s="112"/>
+      <c r="E51" s="112"/>
+      <c r="F51" s="112"/>
+      <c r="G51" s="112"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="118"/>
-      <c r="B52" s="118"/>
-      <c r="C52" s="118"/>
-      <c r="D52" s="118"/>
-      <c r="E52" s="118"/>
-      <c r="F52" s="118"/>
-      <c r="G52" s="118"/>
+      <c r="A52" s="112"/>
+      <c r="B52" s="112"/>
+      <c r="C52" s="112"/>
+      <c r="D52" s="112"/>
+      <c r="E52" s="112"/>
+      <c r="F52" s="112"/>
+      <c r="G52" s="112"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="118"/>
-      <c r="B53" s="118"/>
-      <c r="C53" s="118"/>
-      <c r="D53" s="118"/>
-      <c r="E53" s="118"/>
-      <c r="F53" s="118"/>
-      <c r="G53" s="118"/>
+      <c r="A53" s="112"/>
+      <c r="B53" s="112"/>
+      <c r="C53" s="112"/>
+      <c r="D53" s="112"/>
+      <c r="E53" s="112"/>
+      <c r="F53" s="112"/>
+      <c r="G53" s="112"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="118"/>
-      <c r="B54" s="118"/>
-      <c r="C54" s="118"/>
-      <c r="D54" s="118"/>
-      <c r="E54" s="118"/>
-      <c r="F54" s="118"/>
-      <c r="G54" s="118"/>
+      <c r="A54" s="112"/>
+      <c r="B54" s="112"/>
+      <c r="C54" s="112"/>
+      <c r="D54" s="112"/>
+      <c r="E54" s="112"/>
+      <c r="F54" s="112"/>
+      <c r="G54" s="112"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="118"/>
-      <c r="B55" s="118"/>
-      <c r="C55" s="118"/>
-      <c r="D55" s="118"/>
-      <c r="E55" s="118"/>
-      <c r="F55" s="118"/>
-      <c r="G55" s="118"/>
+      <c r="A55" s="112"/>
+      <c r="B55" s="112"/>
+      <c r="C55" s="112"/>
+      <c r="D55" s="112"/>
+      <c r="E55" s="112"/>
+      <c r="F55" s="112"/>
+      <c r="G55" s="112"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="118"/>
-      <c r="B56" s="118"/>
-      <c r="C56" s="118"/>
-      <c r="D56" s="118"/>
-      <c r="E56" s="118"/>
-      <c r="F56" s="118"/>
-      <c r="G56" s="118"/>
+      <c r="A56" s="112"/>
+      <c r="B56" s="112"/>
+      <c r="C56" s="112"/>
+      <c r="D56" s="112"/>
+      <c r="E56" s="112"/>
+      <c r="F56" s="112"/>
+      <c r="G56" s="112"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="118"/>
-      <c r="B57" s="118"/>
-      <c r="C57" s="118"/>
-      <c r="D57" s="118"/>
-      <c r="E57" s="118"/>
-      <c r="F57" s="118"/>
-      <c r="G57" s="118"/>
+      <c r="A57" s="112"/>
+      <c r="B57" s="112"/>
+      <c r="C57" s="112"/>
+      <c r="D57" s="112"/>
+      <c r="E57" s="112"/>
+      <c r="F57" s="112"/>
+      <c r="G57" s="112"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="118"/>
-      <c r="B58" s="118"/>
-      <c r="C58" s="118"/>
-      <c r="D58" s="118"/>
-      <c r="E58" s="118"/>
-      <c r="F58" s="118"/>
-      <c r="G58" s="118"/>
+      <c r="A58" s="112"/>
+      <c r="B58" s="112"/>
+      <c r="C58" s="112"/>
+      <c r="D58" s="112"/>
+      <c r="E58" s="112"/>
+      <c r="F58" s="112"/>
+      <c r="G58" s="112"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="118"/>
-      <c r="B59" s="118"/>
-      <c r="C59" s="118"/>
-      <c r="D59" s="118"/>
-      <c r="E59" s="118"/>
-      <c r="F59" s="118"/>
-      <c r="G59" s="118"/>
+      <c r="A59" s="112"/>
+      <c r="B59" s="112"/>
+      <c r="C59" s="112"/>
+      <c r="D59" s="112"/>
+      <c r="E59" s="112"/>
+      <c r="F59" s="112"/>
+      <c r="G59" s="112"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3376,13 +3359,13 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="114" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="115" t="s">
         <v>74</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="121" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="409.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3410,13 +3393,13 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="114" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="115" t="s">
         <v>76</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="121" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="379.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3444,13 +3427,13 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="116" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="117" t="s">
         <v>78</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="123" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="379.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3479,92 +3462,92 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="124" t="s">
-        <v>80</v>
+      <c r="A1" s="118" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B5" s="1" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="117" t="s">
         <v>86</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="123" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="117" t="s">
         <v>91</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="123" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="117" t="s">
         <v>96</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="123" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B20" s="1" t="n">
         <v>280</v>
@@ -3572,33 +3555,33 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B21" s="1" t="n">
         <v>28</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="125" t="s">
-        <v>100</v>
-      </c>
-      <c r="B22" s="125" t="n">
+      <c r="A22" s="119" t="s">
+        <v>99</v>
+      </c>
+      <c r="B22" s="119" t="n">
         <v>308</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/LibroCuentas_PTP_2026.xlsx
+++ b/LibroCuentas_PTP_2026.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="103">
   <si>
     <t xml:space="preserve">PEÑA TAURINA PEGUERINOS</t>
   </si>
@@ -818,6 +818,30 @@
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
+      <top style="medium">
+        <color rgb="FF7A0000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF7A0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="medium">
+        <color rgb="FF7A0000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF7A0000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF7A0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FFC9A227"/>
       </top>
@@ -836,30 +860,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFC9A227"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="FF7A0000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF7A0000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right style="medium">
-        <color rgb="FF7A0000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF7A0000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF7A0000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -916,7 +916,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="122">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1093,6 +1093,14 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="19" fillId="8" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1105,27 +1113,27 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="20" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="17" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="20" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="17" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1480,9 +1488,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>3324240</xdr:colOff>
+      <xdr:colOff>3323880</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>124200</xdr:rowOff>
+      <xdr:rowOff>123840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1496,7 +1504,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="600120"/>
-          <a:ext cx="3324240" cy="5705640"/>
+          <a:ext cx="3323880" cy="5705280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1522,9 +1530,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>66960</xdr:colOff>
+      <xdr:colOff>66600</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>4753080</xdr:rowOff>
+      <xdr:rowOff>4752720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1538,7 +1546,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="600120"/>
-          <a:ext cx="5705640" cy="4753080"/>
+          <a:ext cx="5705280" cy="4752720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1564,9 +1572,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>3613680</xdr:colOff>
+      <xdr:colOff>3613320</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>4742280</xdr:rowOff>
+      <xdr:rowOff>4741920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1580,7 +1588,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="566640"/>
-          <a:ext cx="3613680" cy="4756680"/>
+          <a:ext cx="3613320" cy="4756320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1775,7 +1783,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
@@ -2062,103 +2070,110 @@
       <c r="E21" s="34"/>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="36" t="s">
+      <c r="A22" s="33" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B22" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="34"/>
+      <c r="D22" s="35" t="n">
+        <v>34</v>
+      </c>
+      <c r="E22" s="34"/>
+    </row>
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="D22" s="37" t="n">
-        <f aca="false">SUM(D6:D21)</f>
-        <v>1080.5</v>
-      </c>
-      <c r="E22" s="38" t="n">
-        <f aca="false">SUM(E6:E21)</f>
+      <c r="B23" s="36"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="37" t="n">
+        <f aca="false">SUM(D6:D22)</f>
+        <v>1114.5</v>
+      </c>
+      <c r="E23" s="38" t="n">
+        <f aca="false">SUM(E6:E22)</f>
         <v>618</v>
       </c>
-      <c r="F22" s="39" t="n">
-        <f aca="false">D22-E22</f>
-        <v>462.5</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="40"/>
-      <c r="B23" s="40"/>
-      <c r="C23" s="40"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="42"/>
+      <c r="F23" s="39" t="n">
+        <f aca="false">D23-E23</f>
+        <v>496.5</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="43" t="s">
+      <c r="A24" s="40"/>
+      <c r="B24" s="40"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="42"/>
+    </row>
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="43"/>
-      <c r="C24" s="43"/>
-      <c r="D24" s="44" t="n">
-        <f aca="false">SUM(D6:D21)</f>
-        <v>1080.5</v>
-      </c>
-      <c r="E24" s="44" t="n">
-        <f aca="false">SUM(E6:E21)</f>
+      <c r="B25" s="44"/>
+      <c r="C25" s="45"/>
+      <c r="D25" s="46" t="n">
+        <f aca="false">SUM(D6:D22)</f>
+        <v>1114.5</v>
+      </c>
+      <c r="E25" s="46" t="n">
+        <f aca="false">SUM(E6:E22)</f>
         <v>618</v>
       </c>
-      <c r="F24" s="45" t="n">
-        <f aca="false">D24-E24</f>
-        <v>462.5</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="46" t="s">
+      <c r="F25" s="47" t="n">
+        <f aca="false">D25-E25</f>
+        <v>496.5</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="47"/>
-      <c r="C25" s="48"/>
-      <c r="D25" s="49"/>
-      <c r="E25" s="49"/>
-      <c r="F25" s="50" t="n">
-        <f aca="false">D22-E22</f>
-        <v>462.5</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="B26" s="51"/>
-      <c r="C26" s="52"/>
-      <c r="D26" s="44" t="n">
-        <f aca="false">D24</f>
-        <v>1080.5</v>
-      </c>
-      <c r="E26" s="53" t="n">
-        <f aca="false">E24</f>
-        <v>618</v>
-      </c>
-      <c r="F26" s="54"/>
+      <c r="B26" s="49"/>
+      <c r="C26" s="50"/>
+      <c r="D26" s="51"/>
+      <c r="E26" s="51"/>
+      <c r="F26" s="52" t="n">
+        <f aca="false">D23-E23</f>
+        <v>496.5</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="53"/>
+      <c r="C27" s="54"/>
+      <c r="D27" s="46" t="n">
+        <f aca="false">D25</f>
+        <v>1114.5</v>
+      </c>
+      <c r="E27" s="55" t="n">
+        <f aca="false">E25</f>
+        <v>618</v>
+      </c>
+      <c r="F27" s="56"/>
+    </row>
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="B27" s="51"/>
-      <c r="C27" s="52"/>
-      <c r="D27" s="53"/>
-      <c r="E27" s="44" t="n">
-        <f aca="false">E22</f>
+      <c r="B28" s="53"/>
+      <c r="C28" s="54"/>
+      <c r="D28" s="55"/>
+      <c r="E28" s="46" t="n">
+        <f aca="false">E23</f>
         <v>618</v>
       </c>
-      <c r="F27" s="54"/>
-    </row>
-    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="40"/>
-      <c r="B28" s="42"/>
-      <c r="C28" s="55"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="41"/>
-      <c r="F28" s="42"/>
+      <c r="F28" s="56"/>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="40"/>
       <c r="B29" s="42"/>
-      <c r="C29" s="55"/>
+      <c r="C29" s="57"/>
       <c r="D29" s="41"/>
       <c r="E29" s="41"/>
       <c r="F29" s="42"/>
@@ -2166,7 +2181,7 @@
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="40"/>
       <c r="B30" s="42"/>
-      <c r="C30" s="55"/>
+      <c r="C30" s="57"/>
       <c r="D30" s="41"/>
       <c r="E30" s="41"/>
       <c r="F30" s="42"/>
@@ -2174,7 +2189,7 @@
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="40"/>
       <c r="B31" s="42"/>
-      <c r="C31" s="55"/>
+      <c r="C31" s="57"/>
       <c r="D31" s="41"/>
       <c r="E31" s="41"/>
       <c r="F31" s="42"/>
@@ -2182,7 +2197,7 @@
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="40"/>
       <c r="B32" s="42"/>
-      <c r="C32" s="55"/>
+      <c r="C32" s="57"/>
       <c r="D32" s="41"/>
       <c r="E32" s="41"/>
       <c r="F32" s="42"/>
@@ -2190,7 +2205,7 @@
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="40"/>
       <c r="B33" s="42"/>
-      <c r="C33" s="55"/>
+      <c r="C33" s="57"/>
       <c r="D33" s="41"/>
       <c r="E33" s="41"/>
       <c r="F33" s="42"/>
@@ -2198,7 +2213,7 @@
     <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="40"/>
       <c r="B34" s="42"/>
-      <c r="C34" s="55"/>
+      <c r="C34" s="57"/>
       <c r="D34" s="41"/>
       <c r="E34" s="41"/>
       <c r="F34" s="42"/>
@@ -2206,7 +2221,7 @@
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="40"/>
       <c r="B35" s="42"/>
-      <c r="C35" s="55"/>
+      <c r="C35" s="57"/>
       <c r="D35" s="41"/>
       <c r="E35" s="41"/>
       <c r="F35" s="42"/>
@@ -2214,7 +2229,7 @@
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="40"/>
       <c r="B36" s="42"/>
-      <c r="C36" s="55"/>
+      <c r="C36" s="57"/>
       <c r="D36" s="41"/>
       <c r="E36" s="41"/>
       <c r="F36" s="42"/>
@@ -2222,7 +2237,7 @@
     <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="40"/>
       <c r="B37" s="42"/>
-      <c r="C37" s="55"/>
+      <c r="C37" s="57"/>
       <c r="D37" s="41"/>
       <c r="E37" s="41"/>
       <c r="F37" s="42"/>
@@ -2230,7 +2245,7 @@
     <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="40"/>
       <c r="B38" s="42"/>
-      <c r="C38" s="55"/>
+      <c r="C38" s="57"/>
       <c r="D38" s="41"/>
       <c r="E38" s="41"/>
       <c r="F38" s="42"/>
@@ -2238,7 +2253,7 @@
     <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="40"/>
       <c r="B39" s="42"/>
-      <c r="C39" s="55"/>
+      <c r="C39" s="57"/>
       <c r="D39" s="41"/>
       <c r="E39" s="41"/>
       <c r="F39" s="42"/>
@@ -2246,7 +2261,7 @@
     <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="40"/>
       <c r="B40" s="42"/>
-      <c r="C40" s="55"/>
+      <c r="C40" s="57"/>
       <c r="D40" s="41"/>
       <c r="E40" s="41"/>
       <c r="F40" s="42"/>
@@ -2254,7 +2269,7 @@
     <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="40"/>
       <c r="B41" s="42"/>
-      <c r="C41" s="55"/>
+      <c r="C41" s="57"/>
       <c r="D41" s="41"/>
       <c r="E41" s="41"/>
       <c r="F41" s="42"/>
@@ -2262,7 +2277,7 @@
     <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="40"/>
       <c r="B42" s="42"/>
-      <c r="C42" s="55"/>
+      <c r="C42" s="57"/>
       <c r="D42" s="41"/>
       <c r="E42" s="41"/>
       <c r="F42" s="42"/>
@@ -2270,7 +2285,7 @@
     <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="40"/>
       <c r="B43" s="42"/>
-      <c r="C43" s="55"/>
+      <c r="C43" s="57"/>
       <c r="D43" s="41"/>
       <c r="E43" s="41"/>
       <c r="F43" s="42"/>
@@ -2278,7 +2293,7 @@
     <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="40"/>
       <c r="B44" s="42"/>
-      <c r="C44" s="55"/>
+      <c r="C44" s="57"/>
       <c r="D44" s="41"/>
       <c r="E44" s="41"/>
       <c r="F44" s="42"/>
@@ -2286,7 +2301,7 @@
     <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="40"/>
       <c r="B45" s="42"/>
-      <c r="C45" s="55"/>
+      <c r="C45" s="57"/>
       <c r="D45" s="41"/>
       <c r="E45" s="41"/>
       <c r="F45" s="42"/>
@@ -2294,77 +2309,85 @@
     <row r="46" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="40"/>
       <c r="B46" s="42"/>
-      <c r="C46" s="55"/>
+      <c r="C46" s="57"/>
       <c r="D46" s="41"/>
       <c r="E46" s="41"/>
       <c r="F46" s="42"/>
     </row>
     <row r="47" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="56"/>
-      <c r="B47" s="57"/>
-      <c r="C47" s="58"/>
-      <c r="D47" s="49"/>
-      <c r="E47" s="49"/>
-      <c r="F47" s="57"/>
+      <c r="A47" s="40"/>
+      <c r="B47" s="42"/>
+      <c r="C47" s="57"/>
+      <c r="D47" s="41"/>
+      <c r="E47" s="41"/>
+      <c r="F47" s="42"/>
     </row>
     <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="59"/>
-      <c r="B48" s="51"/>
-      <c r="C48" s="52"/>
-      <c r="D48" s="53"/>
-      <c r="E48" s="53"/>
-      <c r="F48" s="54"/>
+      <c r="A48" s="58"/>
+      <c r="B48" s="59"/>
+      <c r="C48" s="60"/>
+      <c r="D48" s="51"/>
+      <c r="E48" s="51"/>
+      <c r="F48" s="59"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="60"/>
-      <c r="B49" s="57"/>
-      <c r="C49" s="58"/>
-      <c r="D49" s="49"/>
-      <c r="E49" s="49"/>
-      <c r="F49" s="61"/>
+      <c r="A49" s="61"/>
+      <c r="B49" s="53"/>
+      <c r="C49" s="54"/>
+      <c r="D49" s="55"/>
+      <c r="E49" s="55"/>
+      <c r="F49" s="56"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="62"/>
-      <c r="B50" s="51"/>
-      <c r="C50" s="52"/>
-      <c r="D50" s="63"/>
-      <c r="E50" s="53"/>
-      <c r="F50" s="54"/>
+      <c r="B50" s="59"/>
+      <c r="C50" s="60"/>
+      <c r="D50" s="51"/>
+      <c r="E50" s="51"/>
+      <c r="F50" s="63"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="64"/>
-      <c r="D51" s="53"/>
-      <c r="E51" s="65"/>
-      <c r="F51" s="54"/>
+      <c r="B51" s="53"/>
+      <c r="C51" s="54"/>
+      <c r="D51" s="65"/>
+      <c r="E51" s="55"/>
+      <c r="F51" s="56"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="66"/>
-      <c r="D52" s="67"/>
+      <c r="D52" s="55"/>
       <c r="E52" s="67"/>
-      <c r="F52" s="68"/>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="56"/>
-      <c r="B53" s="47"/>
-      <c r="C53" s="48"/>
-      <c r="D53" s="49"/>
-      <c r="E53" s="49"/>
-      <c r="F53" s="57"/>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="69"/>
-      <c r="B55" s="51"/>
-      <c r="C55" s="52"/>
-      <c r="D55" s="53"/>
-      <c r="E55" s="53"/>
-      <c r="F55" s="70"/>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F52" s="56"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="68"/>
+      <c r="D53" s="69"/>
+      <c r="E53" s="69"/>
+      <c r="F53" s="70"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="58"/>
+      <c r="B54" s="49"/>
+      <c r="C54" s="50"/>
+      <c r="D54" s="51"/>
+      <c r="E54" s="51"/>
+      <c r="F54" s="59"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="71"/>
-      <c r="B56" s="47"/>
-      <c r="C56" s="48"/>
+      <c r="B56" s="53"/>
+      <c r="C56" s="54"/>
+      <c r="D56" s="55"/>
+      <c r="E56" s="55"/>
       <c r="F56" s="72"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="73"/>
+      <c r="B57" s="49"/>
+      <c r="C57" s="50"/>
+      <c r="F57" s="74"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2401,20 +2424,20 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="75" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
     </row>
     <row r="3" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2432,131 +2455,131 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="75" t="s">
+      <c r="A5" s="77" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="76" t="n">
+      <c r="B5" s="78" t="n">
         <v>800</v>
       </c>
-      <c r="C5" s="76" t="n">
+      <c r="C5" s="78" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="76" t="n">
+      <c r="D5" s="78" t="n">
         <f aca="false">B5-C5</f>
         <v>800</v>
       </c>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="75" t="s">
+      <c r="A6" s="77" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="76" t="n">
+      <c r="B6" s="78" t="n">
         <v>0</v>
       </c>
-      <c r="C6" s="76" t="n">
+      <c r="C6" s="78" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="76" t="n">
+      <c r="D6" s="78" t="n">
         <f aca="false">B6-C6</f>
         <v>0</v>
       </c>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="78" t="s">
+      <c r="A7" s="80" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="79" t="n">
+      <c r="B7" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="79" t="n">
+      <c r="C7" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="79" t="n">
+      <c r="D7" s="81" t="n">
         <f aca="false">B7-C7</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="78" t="s">
+      <c r="A8" s="80" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="79" t="n">
+      <c r="B8" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="79" t="n">
+      <c r="C8" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="79" t="n">
+      <c r="D8" s="81" t="n">
         <f aca="false">B8-C8</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="80" t="s">
+      <c r="A9" s="82" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="81" t="n">
+      <c r="B9" s="83" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="81" t="n">
+      <c r="C9" s="83" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="81" t="n">
+      <c r="D9" s="83" t="n">
         <f aca="false">B9-C9</f>
         <v>0</v>
       </c>
-      <c r="E9" s="82"/>
-      <c r="F9" s="82"/>
+      <c r="E9" s="84"/>
+      <c r="F9" s="84"/>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="75" t="s">
+      <c r="A10" s="77" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="76" t="n">
+      <c r="B10" s="78" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="76" t="n">
+      <c r="C10" s="78" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="76" t="n">
+      <c r="D10" s="78" t="n">
         <f aca="false">B10-C10</f>
         <v>0</v>
       </c>
-      <c r="E10" s="77"/>
-      <c r="F10" s="77"/>
+      <c r="E10" s="79"/>
+      <c r="F10" s="79"/>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="78" t="s">
+      <c r="A11" s="80" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="79" t="n">
+      <c r="B11" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="79" t="n">
+      <c r="C11" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="79" t="n">
+      <c r="D11" s="81" t="n">
         <f aca="false">B11-C11</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="83" t="s">
+      <c r="A12" s="85" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="53" t="n">
+      <c r="B12" s="55" t="n">
         <f aca="false">SUM(B5:B11)</f>
         <v>800</v>
       </c>
-      <c r="C12" s="53" t="n">
+      <c r="C12" s="55" t="n">
         <f aca="false">SUM(C5:C11)</f>
         <v>0</v>
       </c>
-      <c r="D12" s="53" t="n">
+      <c r="D12" s="55" t="n">
         <f aca="false">B12-C12</f>
         <v>800</v>
       </c>
@@ -2591,745 +2614,745 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="75" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="84" t="s">
+      <c r="A2" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="84"/>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
+      <c r="B2" s="86"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
     </row>
     <row r="3" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="85" t="s">
+      <c r="A4" s="87" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="85" t="s">
+      <c r="B4" s="87" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="85" t="s">
+      <c r="C4" s="87" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="85" t="s">
+      <c r="D4" s="87" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="85" t="s">
+      <c r="E4" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="85" t="s">
+      <c r="F4" s="87" t="s">
         <v>49</v>
       </c>
-      <c r="G4" s="86" t="s">
+      <c r="G4" s="88" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="87" t="n">
+      <c r="A5" s="89" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="88" t="s">
+      <c r="B5" s="90" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="89" t="n">
+      <c r="C5" s="91" t="n">
         <v>50</v>
       </c>
-      <c r="D5" s="90" t="s">
+      <c r="D5" s="92" t="s">
         <v>52</v>
       </c>
-      <c r="E5" s="89" t="n">
+      <c r="E5" s="91" t="n">
         <v>50</v>
       </c>
-      <c r="F5" s="91" t="s">
+      <c r="F5" s="93" t="s">
         <v>53</v>
       </c>
-      <c r="G5" s="92"/>
+      <c r="G5" s="94"/>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="87" t="n">
+      <c r="A6" s="89" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="88"/>
-      <c r="C6" s="89"/>
-      <c r="D6" s="90"/>
-      <c r="E6" s="89"/>
-      <c r="F6" s="91"/>
-      <c r="G6" s="92"/>
+      <c r="B6" s="90"/>
+      <c r="C6" s="91"/>
+      <c r="D6" s="92"/>
+      <c r="E6" s="91"/>
+      <c r="F6" s="93"/>
+      <c r="G6" s="94"/>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="93" t="n">
+      <c r="A7" s="95" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="94" t="s">
+      <c r="B7" s="96" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="95" t="n">
+      <c r="C7" s="97" t="n">
         <v>50</v>
       </c>
-      <c r="D7" s="96" t="s">
+      <c r="D7" s="98" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="95" t="n">
+      <c r="E7" s="97" t="n">
         <v>50</v>
       </c>
-      <c r="F7" s="97" t="s">
+      <c r="F7" s="99" t="s">
         <v>53</v>
       </c>
-      <c r="G7" s="98"/>
+      <c r="G7" s="100"/>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="87" t="n">
+      <c r="A8" s="89" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="88" t="s">
+      <c r="B8" s="90" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="89" t="n">
+      <c r="C8" s="91" t="n">
         <v>50</v>
       </c>
-      <c r="D8" s="90" t="s">
+      <c r="D8" s="92" t="s">
         <v>52</v>
       </c>
-      <c r="E8" s="89" t="n">
+      <c r="E8" s="91" t="n">
         <v>50</v>
       </c>
-      <c r="F8" s="91" t="s">
+      <c r="F8" s="93" t="s">
         <v>53</v>
       </c>
-      <c r="G8" s="92"/>
+      <c r="G8" s="94"/>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="93" t="n">
+      <c r="A9" s="95" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="94" t="s">
+      <c r="B9" s="96" t="s">
         <v>56</v>
       </c>
-      <c r="C9" s="95" t="n">
+      <c r="C9" s="97" t="n">
         <v>50</v>
       </c>
-      <c r="D9" s="96" t="s">
+      <c r="D9" s="98" t="s">
         <v>52</v>
       </c>
-      <c r="E9" s="95" t="n">
+      <c r="E9" s="97" t="n">
         <v>50</v>
       </c>
-      <c r="F9" s="97" t="s">
+      <c r="F9" s="99" t="s">
         <v>53</v>
       </c>
-      <c r="G9" s="98"/>
+      <c r="G9" s="100"/>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="87" t="n">
+      <c r="A10" s="89" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="88" t="s">
+      <c r="B10" s="90" t="s">
         <v>57</v>
       </c>
-      <c r="C10" s="89" t="n">
+      <c r="C10" s="91" t="n">
         <v>50</v>
       </c>
-      <c r="D10" s="90" t="s">
+      <c r="D10" s="92" t="s">
         <v>52</v>
       </c>
-      <c r="E10" s="89" t="n">
+      <c r="E10" s="91" t="n">
         <v>50</v>
       </c>
-      <c r="F10" s="91" t="s">
+      <c r="F10" s="93" t="s">
         <v>53</v>
       </c>
-      <c r="G10" s="92"/>
+      <c r="G10" s="94"/>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="93" t="n">
+      <c r="A11" s="95" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="94" t="s">
+      <c r="B11" s="96" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="95" t="n">
+      <c r="C11" s="97" t="n">
         <v>50</v>
       </c>
-      <c r="D11" s="96" t="s">
+      <c r="D11" s="98" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="95" t="n">
+      <c r="E11" s="97" t="n">
         <v>50</v>
       </c>
-      <c r="F11" s="97" t="s">
+      <c r="F11" s="99" t="s">
         <v>53</v>
       </c>
-      <c r="G11" s="98"/>
+      <c r="G11" s="100"/>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="87" t="n">
+      <c r="A12" s="89" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="88" t="s">
+      <c r="B12" s="90" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="89" t="n">
+      <c r="C12" s="91" t="n">
         <v>50</v>
       </c>
-      <c r="D12" s="90" t="s">
+      <c r="D12" s="92" t="s">
         <v>52</v>
       </c>
-      <c r="E12" s="89" t="n">
+      <c r="E12" s="91" t="n">
         <v>50</v>
       </c>
-      <c r="F12" s="91" t="s">
+      <c r="F12" s="93" t="s">
         <v>53</v>
       </c>
-      <c r="G12" s="92"/>
+      <c r="G12" s="94"/>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="93" t="n">
+      <c r="A13" s="95" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="94" t="s">
+      <c r="B13" s="96" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="95" t="n">
+      <c r="C13" s="97" t="n">
         <v>50</v>
       </c>
-      <c r="D13" s="96" t="s">
+      <c r="D13" s="98" t="s">
         <v>52</v>
       </c>
-      <c r="E13" s="95" t="n">
+      <c r="E13" s="97" t="n">
         <v>50</v>
       </c>
-      <c r="F13" s="97" t="s">
+      <c r="F13" s="99" t="s">
         <v>53</v>
       </c>
-      <c r="G13" s="98"/>
+      <c r="G13" s="100"/>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="87" t="n">
+      <c r="A14" s="89" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="88" t="s">
+      <c r="B14" s="90" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="89" t="n">
+      <c r="C14" s="91" t="n">
         <v>50</v>
       </c>
-      <c r="D14" s="90" t="s">
+      <c r="D14" s="92" t="s">
         <v>52</v>
       </c>
-      <c r="E14" s="89" t="n">
+      <c r="E14" s="91" t="n">
         <v>50</v>
       </c>
-      <c r="F14" s="91" t="s">
+      <c r="F14" s="93" t="s">
         <v>53</v>
       </c>
-      <c r="G14" s="92"/>
+      <c r="G14" s="94"/>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="93" t="n">
+      <c r="A15" s="95" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="94" t="s">
+      <c r="B15" s="96" t="s">
         <v>62</v>
       </c>
-      <c r="C15" s="95" t="n">
+      <c r="C15" s="97" t="n">
         <v>50</v>
       </c>
-      <c r="D15" s="96" t="s">
+      <c r="D15" s="98" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="95" t="n">
+      <c r="E15" s="97" t="n">
         <v>50</v>
       </c>
-      <c r="F15" s="97" t="s">
+      <c r="F15" s="99" t="s">
         <v>53</v>
       </c>
-      <c r="G15" s="98"/>
+      <c r="G15" s="100"/>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="87" t="n">
+      <c r="A16" s="89" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="88" t="s">
+      <c r="B16" s="90" t="s">
         <v>63</v>
       </c>
-      <c r="C16" s="89" t="n">
+      <c r="C16" s="91" t="n">
         <v>50</v>
       </c>
-      <c r="D16" s="91" t="s">
+      <c r="D16" s="93" t="s">
         <v>64</v>
       </c>
-      <c r="E16" s="89" t="n">
+      <c r="E16" s="91" t="n">
         <v>50</v>
       </c>
-      <c r="F16" s="91" t="s">
+      <c r="F16" s="93" t="s">
         <v>53</v>
       </c>
-      <c r="G16" s="92"/>
+      <c r="G16" s="94"/>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="87" t="n">
+      <c r="A17" s="89" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="99" t="s">
+      <c r="B17" s="101" t="s">
         <v>65</v>
       </c>
-      <c r="C17" s="100" t="n">
+      <c r="C17" s="102" t="n">
         <v>50</v>
       </c>
-      <c r="D17" s="101" t="s">
+      <c r="D17" s="103" t="s">
         <v>66</v>
       </c>
-      <c r="E17" s="100" t="n">
+      <c r="E17" s="102" t="n">
         <v>50</v>
       </c>
-      <c r="F17" s="101" t="s">
+      <c r="F17" s="103" t="s">
         <v>53</v>
       </c>
-      <c r="G17" s="102"/>
+      <c r="G17" s="104"/>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="93" t="n">
+      <c r="A18" s="95" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="103" t="s">
+      <c r="B18" s="105" t="s">
         <v>67</v>
       </c>
-      <c r="C18" s="104" t="n">
+      <c r="C18" s="106" t="n">
         <v>50</v>
       </c>
-      <c r="D18" s="105" t="s">
+      <c r="D18" s="107" t="s">
         <v>66</v>
       </c>
-      <c r="E18" s="104" t="n">
+      <c r="E18" s="106" t="n">
         <v>50</v>
       </c>
-      <c r="F18" s="105" t="s">
+      <c r="F18" s="107" t="s">
         <v>53</v>
       </c>
-      <c r="G18" s="106"/>
-    </row>
-    <row r="19" s="108" customFormat="true" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="93" t="n">
+      <c r="G18" s="108"/>
+    </row>
+    <row r="19" s="110" customFormat="true" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="95" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="103" t="s">
+      <c r="B19" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="C19" s="104" t="n">
+      <c r="C19" s="106" t="n">
         <v>50</v>
       </c>
-      <c r="D19" s="105" t="s">
+      <c r="D19" s="107" t="s">
         <v>69</v>
       </c>
-      <c r="E19" s="104" t="n">
+      <c r="E19" s="106" t="n">
         <v>50</v>
       </c>
-      <c r="F19" s="105" t="s">
+      <c r="F19" s="107" t="s">
         <v>53</v>
       </c>
-      <c r="G19" s="107"/>
+      <c r="G19" s="109"/>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="93" t="n">
+      <c r="A20" s="95" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="103" t="s">
+      <c r="B20" s="105" t="s">
         <v>70</v>
       </c>
-      <c r="C20" s="104" t="n">
+      <c r="C20" s="106" t="n">
         <v>50</v>
       </c>
-      <c r="D20" s="105" t="s">
+      <c r="D20" s="107" t="s">
         <v>69</v>
       </c>
-      <c r="E20" s="104" t="n">
+      <c r="E20" s="106" t="n">
         <v>50</v>
       </c>
-      <c r="F20" s="105" t="s">
+      <c r="F20" s="107" t="s">
         <v>53</v>
       </c>
-      <c r="G20" s="98"/>
+      <c r="G20" s="100"/>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="93" t="n">
+      <c r="A21" s="95" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="103" t="s">
+      <c r="B21" s="105" t="s">
         <v>71</v>
       </c>
-      <c r="C21" s="104" t="n">
+      <c r="C21" s="106" t="n">
         <v>50</v>
       </c>
-      <c r="D21" s="105" t="s">
+      <c r="D21" s="107" t="s">
         <v>69</v>
       </c>
-      <c r="E21" s="104" t="n">
+      <c r="E21" s="106" t="n">
         <v>50</v>
       </c>
-      <c r="F21" s="105" t="s">
+      <c r="F21" s="107" t="s">
         <v>53</v>
       </c>
-      <c r="G21" s="107"/>
+      <c r="G21" s="109"/>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="93"/>
-      <c r="B22" s="103"/>
-      <c r="C22" s="104"/>
-      <c r="D22" s="105"/>
-      <c r="E22" s="104"/>
-      <c r="F22" s="105"/>
-      <c r="G22" s="107"/>
+      <c r="A22" s="95"/>
+      <c r="B22" s="105"/>
+      <c r="C22" s="106"/>
+      <c r="D22" s="107"/>
+      <c r="E22" s="106"/>
+      <c r="F22" s="107"/>
+      <c r="G22" s="109"/>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="93"/>
-      <c r="B23" s="103"/>
-      <c r="C23" s="104"/>
-      <c r="D23" s="105"/>
-      <c r="E23" s="104"/>
-      <c r="F23" s="105"/>
-      <c r="G23" s="106"/>
+      <c r="A23" s="95"/>
+      <c r="B23" s="105"/>
+      <c r="C23" s="106"/>
+      <c r="D23" s="107"/>
+      <c r="E23" s="106"/>
+      <c r="F23" s="107"/>
+      <c r="G23" s="108"/>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="93"/>
-      <c r="B24" s="103"/>
-      <c r="C24" s="104"/>
-      <c r="D24" s="105"/>
-      <c r="E24" s="104"/>
-      <c r="F24" s="105"/>
-      <c r="G24" s="106"/>
+      <c r="A24" s="95"/>
+      <c r="B24" s="105"/>
+      <c r="C24" s="106"/>
+      <c r="D24" s="107"/>
+      <c r="E24" s="106"/>
+      <c r="F24" s="107"/>
+      <c r="G24" s="108"/>
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="93"/>
-      <c r="B25" s="103"/>
-      <c r="C25" s="104"/>
-      <c r="D25" s="105"/>
-      <c r="E25" s="104"/>
-      <c r="F25" s="105"/>
-      <c r="G25" s="106"/>
+      <c r="A25" s="95"/>
+      <c r="B25" s="105"/>
+      <c r="C25" s="106"/>
+      <c r="D25" s="107"/>
+      <c r="E25" s="106"/>
+      <c r="F25" s="107"/>
+      <c r="G25" s="108"/>
     </row>
     <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="109" t="s">
+      <c r="A26" s="111" t="s">
         <v>72</v>
       </c>
-      <c r="B26" s="109"/>
-      <c r="C26" s="110" t="n">
+      <c r="B26" s="111"/>
+      <c r="C26" s="112" t="n">
         <v>800</v>
       </c>
-      <c r="D26" s="111"/>
-      <c r="E26" s="110" t="n">
+      <c r="D26" s="113"/>
+      <c r="E26" s="112" t="n">
         <v>0</v>
       </c>
-      <c r="F26" s="111"/>
-      <c r="G26" s="111"/>
+      <c r="F26" s="113"/>
+      <c r="G26" s="113"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="112"/>
-      <c r="B27" s="112"/>
-      <c r="C27" s="113"/>
-      <c r="D27" s="112"/>
-      <c r="E27" s="112"/>
-      <c r="F27" s="112"/>
-      <c r="G27" s="112"/>
+      <c r="A27" s="114"/>
+      <c r="B27" s="114"/>
+      <c r="C27" s="115"/>
+      <c r="D27" s="114"/>
+      <c r="E27" s="114"/>
+      <c r="F27" s="114"/>
+      <c r="G27" s="114"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="112"/>
-      <c r="B28" s="112"/>
-      <c r="C28" s="112"/>
-      <c r="D28" s="112"/>
-      <c r="E28" s="112"/>
-      <c r="F28" s="112"/>
-      <c r="G28" s="112"/>
+      <c r="A28" s="114"/>
+      <c r="B28" s="114"/>
+      <c r="C28" s="114"/>
+      <c r="D28" s="114"/>
+      <c r="E28" s="114"/>
+      <c r="F28" s="114"/>
+      <c r="G28" s="114"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="112"/>
-      <c r="B29" s="112"/>
-      <c r="C29" s="112"/>
-      <c r="D29" s="112"/>
-      <c r="E29" s="112"/>
-      <c r="F29" s="112"/>
-      <c r="G29" s="112"/>
+      <c r="A29" s="114"/>
+      <c r="B29" s="114"/>
+      <c r="C29" s="114"/>
+      <c r="D29" s="114"/>
+      <c r="E29" s="114"/>
+      <c r="F29" s="114"/>
+      <c r="G29" s="114"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="112"/>
-      <c r="B30" s="112"/>
-      <c r="C30" s="112"/>
-      <c r="D30" s="112"/>
-      <c r="E30" s="112"/>
-      <c r="F30" s="112"/>
-      <c r="G30" s="112"/>
+      <c r="A30" s="114"/>
+      <c r="B30" s="114"/>
+      <c r="C30" s="114"/>
+      <c r="D30" s="114"/>
+      <c r="E30" s="114"/>
+      <c r="F30" s="114"/>
+      <c r="G30" s="114"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="112"/>
-      <c r="B31" s="112"/>
-      <c r="C31" s="112"/>
-      <c r="D31" s="112"/>
-      <c r="E31" s="112"/>
-      <c r="F31" s="112"/>
-      <c r="G31" s="112"/>
+      <c r="A31" s="114"/>
+      <c r="B31" s="114"/>
+      <c r="C31" s="114"/>
+      <c r="D31" s="114"/>
+      <c r="E31" s="114"/>
+      <c r="F31" s="114"/>
+      <c r="G31" s="114"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="112"/>
-      <c r="B32" s="112"/>
-      <c r="C32" s="112"/>
-      <c r="D32" s="112"/>
-      <c r="E32" s="112"/>
-      <c r="F32" s="112"/>
-      <c r="G32" s="112"/>
+      <c r="A32" s="114"/>
+      <c r="B32" s="114"/>
+      <c r="C32" s="114"/>
+      <c r="D32" s="114"/>
+      <c r="E32" s="114"/>
+      <c r="F32" s="114"/>
+      <c r="G32" s="114"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="112"/>
-      <c r="B33" s="112"/>
-      <c r="C33" s="112"/>
-      <c r="D33" s="112"/>
-      <c r="E33" s="112"/>
-      <c r="F33" s="112"/>
-      <c r="G33" s="112"/>
+      <c r="A33" s="114"/>
+      <c r="B33" s="114"/>
+      <c r="C33" s="114"/>
+      <c r="D33" s="114"/>
+      <c r="E33" s="114"/>
+      <c r="F33" s="114"/>
+      <c r="G33" s="114"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="112"/>
-      <c r="B34" s="112"/>
-      <c r="C34" s="112"/>
-      <c r="D34" s="112"/>
-      <c r="E34" s="112"/>
-      <c r="F34" s="112"/>
-      <c r="G34" s="112"/>
+      <c r="A34" s="114"/>
+      <c r="B34" s="114"/>
+      <c r="C34" s="114"/>
+      <c r="D34" s="114"/>
+      <c r="E34" s="114"/>
+      <c r="F34" s="114"/>
+      <c r="G34" s="114"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="112"/>
-      <c r="B35" s="112"/>
-      <c r="C35" s="112"/>
-      <c r="D35" s="112"/>
-      <c r="E35" s="112"/>
-      <c r="F35" s="112"/>
-      <c r="G35" s="112"/>
+      <c r="A35" s="114"/>
+      <c r="B35" s="114"/>
+      <c r="C35" s="114"/>
+      <c r="D35" s="114"/>
+      <c r="E35" s="114"/>
+      <c r="F35" s="114"/>
+      <c r="G35" s="114"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="112"/>
-      <c r="B36" s="112"/>
-      <c r="C36" s="112"/>
-      <c r="D36" s="112"/>
-      <c r="E36" s="112"/>
-      <c r="F36" s="112"/>
-      <c r="G36" s="112"/>
+      <c r="A36" s="114"/>
+      <c r="B36" s="114"/>
+      <c r="C36" s="114"/>
+      <c r="D36" s="114"/>
+      <c r="E36" s="114"/>
+      <c r="F36" s="114"/>
+      <c r="G36" s="114"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="112"/>
-      <c r="B37" s="112"/>
-      <c r="C37" s="112"/>
-      <c r="D37" s="112"/>
-      <c r="E37" s="112"/>
-      <c r="F37" s="112"/>
-      <c r="G37" s="112"/>
+      <c r="A37" s="114"/>
+      <c r="B37" s="114"/>
+      <c r="C37" s="114"/>
+      <c r="D37" s="114"/>
+      <c r="E37" s="114"/>
+      <c r="F37" s="114"/>
+      <c r="G37" s="114"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="112"/>
-      <c r="B38" s="112"/>
-      <c r="C38" s="112"/>
-      <c r="D38" s="112"/>
-      <c r="E38" s="112"/>
-      <c r="F38" s="112"/>
-      <c r="G38" s="112"/>
+      <c r="A38" s="114"/>
+      <c r="B38" s="114"/>
+      <c r="C38" s="114"/>
+      <c r="D38" s="114"/>
+      <c r="E38" s="114"/>
+      <c r="F38" s="114"/>
+      <c r="G38" s="114"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="112"/>
-      <c r="B39" s="112"/>
-      <c r="C39" s="112"/>
-      <c r="D39" s="112"/>
-      <c r="E39" s="112"/>
-      <c r="F39" s="112"/>
-      <c r="G39" s="112"/>
+      <c r="A39" s="114"/>
+      <c r="B39" s="114"/>
+      <c r="C39" s="114"/>
+      <c r="D39" s="114"/>
+      <c r="E39" s="114"/>
+      <c r="F39" s="114"/>
+      <c r="G39" s="114"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="112"/>
-      <c r="B40" s="112"/>
-      <c r="C40" s="112"/>
-      <c r="D40" s="112"/>
-      <c r="E40" s="112"/>
-      <c r="F40" s="112"/>
-      <c r="G40" s="112"/>
+      <c r="A40" s="114"/>
+      <c r="B40" s="114"/>
+      <c r="C40" s="114"/>
+      <c r="D40" s="114"/>
+      <c r="E40" s="114"/>
+      <c r="F40" s="114"/>
+      <c r="G40" s="114"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="112"/>
-      <c r="B41" s="112"/>
-      <c r="C41" s="112"/>
-      <c r="D41" s="112"/>
-      <c r="E41" s="112"/>
-      <c r="F41" s="112"/>
-      <c r="G41" s="112"/>
+      <c r="A41" s="114"/>
+      <c r="B41" s="114"/>
+      <c r="C41" s="114"/>
+      <c r="D41" s="114"/>
+      <c r="E41" s="114"/>
+      <c r="F41" s="114"/>
+      <c r="G41" s="114"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="112"/>
-      <c r="B42" s="112"/>
-      <c r="C42" s="112"/>
-      <c r="D42" s="112"/>
-      <c r="E42" s="112"/>
-      <c r="F42" s="112"/>
-      <c r="G42" s="112"/>
+      <c r="A42" s="114"/>
+      <c r="B42" s="114"/>
+      <c r="C42" s="114"/>
+      <c r="D42" s="114"/>
+      <c r="E42" s="114"/>
+      <c r="F42" s="114"/>
+      <c r="G42" s="114"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="112"/>
-      <c r="B43" s="112"/>
-      <c r="C43" s="112"/>
-      <c r="D43" s="112"/>
-      <c r="E43" s="112"/>
-      <c r="F43" s="112"/>
-      <c r="G43" s="112"/>
+      <c r="A43" s="114"/>
+      <c r="B43" s="114"/>
+      <c r="C43" s="114"/>
+      <c r="D43" s="114"/>
+      <c r="E43" s="114"/>
+      <c r="F43" s="114"/>
+      <c r="G43" s="114"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="112"/>
-      <c r="B44" s="112"/>
-      <c r="C44" s="112"/>
-      <c r="D44" s="112"/>
-      <c r="E44" s="112"/>
-      <c r="F44" s="112"/>
-      <c r="G44" s="112"/>
+      <c r="A44" s="114"/>
+      <c r="B44" s="114"/>
+      <c r="C44" s="114"/>
+      <c r="D44" s="114"/>
+      <c r="E44" s="114"/>
+      <c r="F44" s="114"/>
+      <c r="G44" s="114"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="112"/>
-      <c r="B45" s="112"/>
-      <c r="C45" s="112"/>
-      <c r="D45" s="112"/>
-      <c r="E45" s="112"/>
-      <c r="F45" s="112"/>
-      <c r="G45" s="112"/>
+      <c r="A45" s="114"/>
+      <c r="B45" s="114"/>
+      <c r="C45" s="114"/>
+      <c r="D45" s="114"/>
+      <c r="E45" s="114"/>
+      <c r="F45" s="114"/>
+      <c r="G45" s="114"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="112"/>
-      <c r="B46" s="112"/>
-      <c r="C46" s="112"/>
-      <c r="D46" s="112"/>
-      <c r="E46" s="112"/>
-      <c r="F46" s="112"/>
-      <c r="G46" s="112"/>
+      <c r="A46" s="114"/>
+      <c r="B46" s="114"/>
+      <c r="C46" s="114"/>
+      <c r="D46" s="114"/>
+      <c r="E46" s="114"/>
+      <c r="F46" s="114"/>
+      <c r="G46" s="114"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="112"/>
-      <c r="B47" s="112"/>
-      <c r="C47" s="112"/>
-      <c r="D47" s="112"/>
-      <c r="E47" s="112"/>
-      <c r="F47" s="112"/>
-      <c r="G47" s="112"/>
+      <c r="A47" s="114"/>
+      <c r="B47" s="114"/>
+      <c r="C47" s="114"/>
+      <c r="D47" s="114"/>
+      <c r="E47" s="114"/>
+      <c r="F47" s="114"/>
+      <c r="G47" s="114"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="112"/>
-      <c r="B48" s="112"/>
-      <c r="C48" s="112"/>
-      <c r="D48" s="112"/>
-      <c r="E48" s="112"/>
-      <c r="F48" s="112"/>
-      <c r="G48" s="112"/>
+      <c r="A48" s="114"/>
+      <c r="B48" s="114"/>
+      <c r="C48" s="114"/>
+      <c r="D48" s="114"/>
+      <c r="E48" s="114"/>
+      <c r="F48" s="114"/>
+      <c r="G48" s="114"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="112"/>
-      <c r="B49" s="112"/>
-      <c r="C49" s="112"/>
-      <c r="D49" s="112"/>
-      <c r="E49" s="112"/>
-      <c r="F49" s="112"/>
-      <c r="G49" s="112"/>
+      <c r="A49" s="114"/>
+      <c r="B49" s="114"/>
+      <c r="C49" s="114"/>
+      <c r="D49" s="114"/>
+      <c r="E49" s="114"/>
+      <c r="F49" s="114"/>
+      <c r="G49" s="114"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="112"/>
-      <c r="B50" s="112"/>
-      <c r="C50" s="112"/>
-      <c r="D50" s="112"/>
-      <c r="E50" s="112"/>
-      <c r="F50" s="112"/>
-      <c r="G50" s="112"/>
+      <c r="A50" s="114"/>
+      <c r="B50" s="114"/>
+      <c r="C50" s="114"/>
+      <c r="D50" s="114"/>
+      <c r="E50" s="114"/>
+      <c r="F50" s="114"/>
+      <c r="G50" s="114"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="112"/>
-      <c r="B51" s="112"/>
-      <c r="C51" s="112"/>
-      <c r="D51" s="112"/>
-      <c r="E51" s="112"/>
-      <c r="F51" s="112"/>
-      <c r="G51" s="112"/>
+      <c r="A51" s="114"/>
+      <c r="B51" s="114"/>
+      <c r="C51" s="114"/>
+      <c r="D51" s="114"/>
+      <c r="E51" s="114"/>
+      <c r="F51" s="114"/>
+      <c r="G51" s="114"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="112"/>
-      <c r="B52" s="112"/>
-      <c r="C52" s="112"/>
-      <c r="D52" s="112"/>
-      <c r="E52" s="112"/>
-      <c r="F52" s="112"/>
-      <c r="G52" s="112"/>
+      <c r="A52" s="114"/>
+      <c r="B52" s="114"/>
+      <c r="C52" s="114"/>
+      <c r="D52" s="114"/>
+      <c r="E52" s="114"/>
+      <c r="F52" s="114"/>
+      <c r="G52" s="114"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="112"/>
-      <c r="B53" s="112"/>
-      <c r="C53" s="112"/>
-      <c r="D53" s="112"/>
-      <c r="E53" s="112"/>
-      <c r="F53" s="112"/>
-      <c r="G53" s="112"/>
+      <c r="A53" s="114"/>
+      <c r="B53" s="114"/>
+      <c r="C53" s="114"/>
+      <c r="D53" s="114"/>
+      <c r="E53" s="114"/>
+      <c r="F53" s="114"/>
+      <c r="G53" s="114"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="112"/>
-      <c r="B54" s="112"/>
-      <c r="C54" s="112"/>
-      <c r="D54" s="112"/>
-      <c r="E54" s="112"/>
-      <c r="F54" s="112"/>
-      <c r="G54" s="112"/>
+      <c r="A54" s="114"/>
+      <c r="B54" s="114"/>
+      <c r="C54" s="114"/>
+      <c r="D54" s="114"/>
+      <c r="E54" s="114"/>
+      <c r="F54" s="114"/>
+      <c r="G54" s="114"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="112"/>
-      <c r="B55" s="112"/>
-      <c r="C55" s="112"/>
-      <c r="D55" s="112"/>
-      <c r="E55" s="112"/>
-      <c r="F55" s="112"/>
-      <c r="G55" s="112"/>
+      <c r="A55" s="114"/>
+      <c r="B55" s="114"/>
+      <c r="C55" s="114"/>
+      <c r="D55" s="114"/>
+      <c r="E55" s="114"/>
+      <c r="F55" s="114"/>
+      <c r="G55" s="114"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="112"/>
-      <c r="B56" s="112"/>
-      <c r="C56" s="112"/>
-      <c r="D56" s="112"/>
-      <c r="E56" s="112"/>
-      <c r="F56" s="112"/>
-      <c r="G56" s="112"/>
+      <c r="A56" s="114"/>
+      <c r="B56" s="114"/>
+      <c r="C56" s="114"/>
+      <c r="D56" s="114"/>
+      <c r="E56" s="114"/>
+      <c r="F56" s="114"/>
+      <c r="G56" s="114"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="112"/>
-      <c r="B57" s="112"/>
-      <c r="C57" s="112"/>
-      <c r="D57" s="112"/>
-      <c r="E57" s="112"/>
-      <c r="F57" s="112"/>
-      <c r="G57" s="112"/>
+      <c r="A57" s="114"/>
+      <c r="B57" s="114"/>
+      <c r="C57" s="114"/>
+      <c r="D57" s="114"/>
+      <c r="E57" s="114"/>
+      <c r="F57" s="114"/>
+      <c r="G57" s="114"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="112"/>
-      <c r="B58" s="112"/>
-      <c r="C58" s="112"/>
-      <c r="D58" s="112"/>
-      <c r="E58" s="112"/>
-      <c r="F58" s="112"/>
-      <c r="G58" s="112"/>
+      <c r="A58" s="114"/>
+      <c r="B58" s="114"/>
+      <c r="C58" s="114"/>
+      <c r="D58" s="114"/>
+      <c r="E58" s="114"/>
+      <c r="F58" s="114"/>
+      <c r="G58" s="114"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="112"/>
-      <c r="B59" s="112"/>
-      <c r="C59" s="112"/>
-      <c r="D59" s="112"/>
-      <c r="E59" s="112"/>
-      <c r="F59" s="112"/>
-      <c r="G59" s="112"/>
+      <c r="A59" s="114"/>
+      <c r="B59" s="114"/>
+      <c r="C59" s="114"/>
+      <c r="D59" s="114"/>
+      <c r="E59" s="114"/>
+      <c r="F59" s="114"/>
+      <c r="G59" s="114"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3359,12 +3382,12 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="114" t="s">
+      <c r="A1" s="116" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="115" t="s">
+      <c r="A2" s="117" t="s">
         <v>74</v>
       </c>
     </row>
@@ -3393,12 +3416,12 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="114" t="s">
+      <c r="A1" s="116" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="115" t="s">
+      <c r="A2" s="117" t="s">
         <v>76</v>
       </c>
     </row>
@@ -3427,12 +3450,12 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="116" t="s">
+      <c r="A1" s="118" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="117" t="s">
+      <c r="A2" s="119" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3462,7 +3485,7 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="120" t="s">
         <v>79</v>
       </c>
     </row>
@@ -3491,7 +3514,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="117" t="s">
+      <c r="A7" s="119" t="s">
         <v>86</v>
       </c>
     </row>
@@ -3516,7 +3539,7 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="117" t="s">
+      <c r="A13" s="119" t="s">
         <v>91</v>
       </c>
     </row>
@@ -3541,7 +3564,7 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="117" t="s">
+      <c r="A19" s="119" t="s">
         <v>96</v>
       </c>
     </row>
@@ -3562,10 +3585,10 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="119" t="s">
+      <c r="A22" s="121" t="s">
         <v>99</v>
       </c>
-      <c r="B22" s="119" t="n">
+      <c r="B22" s="121" t="n">
         <v>308</v>
       </c>
     </row>

--- a/LibroCuentas_PTP_2026.xlsx
+++ b/LibroCuentas_PTP_2026.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="103">
   <si>
     <t xml:space="preserve">PEÑA TAURINA PEGUERINOS</t>
   </si>
@@ -916,7 +916,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="120">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1093,11 +1093,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1127,14 +1127,6 @@
     </xf>
     <xf numFmtId="168" fontId="17" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="21" fillId="8" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1488,9 +1480,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>3323880</xdr:colOff>
+      <xdr:colOff>3323520</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>123840</xdr:rowOff>
+      <xdr:rowOff>123480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1504,7 +1496,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="600120"/>
-          <a:ext cx="3323880" cy="5705280"/>
+          <a:ext cx="3323520" cy="5704920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1530,9 +1522,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>66600</xdr:colOff>
+      <xdr:colOff>66240</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>4752720</xdr:rowOff>
+      <xdr:rowOff>4752360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1546,7 +1538,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="600120"/>
-          <a:ext cx="5705280" cy="4752720"/>
+          <a:ext cx="5704920" cy="4752360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1572,9 +1564,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>3613320</xdr:colOff>
+      <xdr:colOff>3612960</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>4741920</xdr:rowOff>
+      <xdr:rowOff>4741560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1588,7 +1580,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="566640"/>
-          <a:ext cx="3613320" cy="4756320"/>
+          <a:ext cx="3612960" cy="4755960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1783,7 +1775,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
@@ -2083,105 +2075,110 @@
       <c r="E22" s="34"/>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="36" t="s">
+      <c r="A23" s="33" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B23" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="34"/>
+      <c r="D23" s="35" t="n">
+        <v>83</v>
+      </c>
+      <c r="E23" s="34"/>
+    </row>
+    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="36"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="37" t="n">
-        <f aca="false">SUM(D6:D22)</f>
-        <v>1114.5</v>
-      </c>
-      <c r="E23" s="38" t="n">
-        <f aca="false">SUM(E6:E22)</f>
+      <c r="B24" s="36"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="37" t="n">
+        <f aca="false">SUM(D6:D23)</f>
+        <v>1197.5</v>
+      </c>
+      <c r="E24" s="38" t="n">
+        <f aca="false">SUM(E6:E23)</f>
         <v>618</v>
       </c>
-      <c r="F23" s="39" t="n">
-        <f aca="false">D23-E23</f>
-        <v>496.5</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="40"/>
-      <c r="B24" s="40"/>
-      <c r="C24" s="40"/>
-      <c r="D24" s="41"/>
-      <c r="E24" s="41"/>
-      <c r="F24" s="42"/>
+      <c r="F24" s="39" t="n">
+        <f aca="false">D24-E24</f>
+        <v>579.5</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="43" t="s">
+      <c r="A25" s="40"/>
+      <c r="B25" s="40"/>
+      <c r="C25" s="40"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="42"/>
+    </row>
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="44"/>
-      <c r="C25" s="45"/>
-      <c r="D25" s="46" t="n">
-        <f aca="false">SUM(D6:D22)</f>
-        <v>1114.5</v>
-      </c>
-      <c r="E25" s="46" t="n">
-        <f aca="false">SUM(E6:E22)</f>
+      <c r="B26" s="44"/>
+      <c r="C26" s="45"/>
+      <c r="D26" s="46" t="n">
+        <f aca="false">SUM(D6:D23)</f>
+        <v>1197.5</v>
+      </c>
+      <c r="E26" s="46" t="n">
+        <f aca="false">SUM(E6:E23)</f>
         <v>618</v>
       </c>
-      <c r="F25" s="47" t="n">
-        <f aca="false">D25-E25</f>
-        <v>496.5</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="48" t="s">
+      <c r="F26" s="47" t="n">
+        <f aca="false">D26-E26</f>
+        <v>579.5</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="49"/>
-      <c r="C26" s="50"/>
-      <c r="D26" s="51"/>
-      <c r="E26" s="51"/>
-      <c r="F26" s="52" t="n">
-        <f aca="false">D23-E23</f>
-        <v>496.5</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" s="53"/>
-      <c r="C27" s="54"/>
-      <c r="D27" s="46" t="n">
-        <f aca="false">D25</f>
-        <v>1114.5</v>
-      </c>
-      <c r="E27" s="55" t="n">
-        <f aca="false">E25</f>
-        <v>618</v>
-      </c>
-      <c r="F27" s="56"/>
+      <c r="B27" s="49"/>
+      <c r="C27" s="50"/>
+      <c r="D27" s="51"/>
+      <c r="E27" s="51"/>
+      <c r="F27" s="52" t="n">
+        <f aca="false">D24-E24</f>
+        <v>579.5</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="44"/>
+      <c r="C28" s="45"/>
+      <c r="D28" s="46" t="n">
+        <f aca="false">D26</f>
+        <v>1197.5</v>
+      </c>
+      <c r="E28" s="53" t="n">
+        <f aca="false">E26</f>
+        <v>618</v>
+      </c>
+      <c r="F28" s="54"/>
+    </row>
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="53"/>
-      <c r="C28" s="54"/>
-      <c r="D28" s="55"/>
-      <c r="E28" s="46" t="n">
-        <f aca="false">E23</f>
+      <c r="B29" s="44"/>
+      <c r="C29" s="45"/>
+      <c r="D29" s="53"/>
+      <c r="E29" s="46" t="n">
+        <f aca="false">E24</f>
         <v>618</v>
       </c>
-      <c r="F28" s="56"/>
-    </row>
-    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="40"/>
-      <c r="B29" s="42"/>
-      <c r="C29" s="57"/>
-      <c r="D29" s="41"/>
-      <c r="E29" s="41"/>
-      <c r="F29" s="42"/>
+      <c r="F29" s="54"/>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="40"/>
       <c r="B30" s="42"/>
-      <c r="C30" s="57"/>
+      <c r="C30" s="55"/>
       <c r="D30" s="41"/>
       <c r="E30" s="41"/>
       <c r="F30" s="42"/>
@@ -2189,7 +2186,7 @@
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="40"/>
       <c r="B31" s="42"/>
-      <c r="C31" s="57"/>
+      <c r="C31" s="55"/>
       <c r="D31" s="41"/>
       <c r="E31" s="41"/>
       <c r="F31" s="42"/>
@@ -2197,7 +2194,7 @@
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="40"/>
       <c r="B32" s="42"/>
-      <c r="C32" s="57"/>
+      <c r="C32" s="55"/>
       <c r="D32" s="41"/>
       <c r="E32" s="41"/>
       <c r="F32" s="42"/>
@@ -2205,7 +2202,7 @@
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="40"/>
       <c r="B33" s="42"/>
-      <c r="C33" s="57"/>
+      <c r="C33" s="55"/>
       <c r="D33" s="41"/>
       <c r="E33" s="41"/>
       <c r="F33" s="42"/>
@@ -2213,7 +2210,7 @@
     <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="40"/>
       <c r="B34" s="42"/>
-      <c r="C34" s="57"/>
+      <c r="C34" s="55"/>
       <c r="D34" s="41"/>
       <c r="E34" s="41"/>
       <c r="F34" s="42"/>
@@ -2221,7 +2218,7 @@
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="40"/>
       <c r="B35" s="42"/>
-      <c r="C35" s="57"/>
+      <c r="C35" s="55"/>
       <c r="D35" s="41"/>
       <c r="E35" s="41"/>
       <c r="F35" s="42"/>
@@ -2229,7 +2226,7 @@
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="40"/>
       <c r="B36" s="42"/>
-      <c r="C36" s="57"/>
+      <c r="C36" s="55"/>
       <c r="D36" s="41"/>
       <c r="E36" s="41"/>
       <c r="F36" s="42"/>
@@ -2237,7 +2234,7 @@
     <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="40"/>
       <c r="B37" s="42"/>
-      <c r="C37" s="57"/>
+      <c r="C37" s="55"/>
       <c r="D37" s="41"/>
       <c r="E37" s="41"/>
       <c r="F37" s="42"/>
@@ -2245,7 +2242,7 @@
     <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="40"/>
       <c r="B38" s="42"/>
-      <c r="C38" s="57"/>
+      <c r="C38" s="55"/>
       <c r="D38" s="41"/>
       <c r="E38" s="41"/>
       <c r="F38" s="42"/>
@@ -2253,7 +2250,7 @@
     <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="40"/>
       <c r="B39" s="42"/>
-      <c r="C39" s="57"/>
+      <c r="C39" s="55"/>
       <c r="D39" s="41"/>
       <c r="E39" s="41"/>
       <c r="F39" s="42"/>
@@ -2261,7 +2258,7 @@
     <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="40"/>
       <c r="B40" s="42"/>
-      <c r="C40" s="57"/>
+      <c r="C40" s="55"/>
       <c r="D40" s="41"/>
       <c r="E40" s="41"/>
       <c r="F40" s="42"/>
@@ -2269,7 +2266,7 @@
     <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="40"/>
       <c r="B41" s="42"/>
-      <c r="C41" s="57"/>
+      <c r="C41" s="55"/>
       <c r="D41" s="41"/>
       <c r="E41" s="41"/>
       <c r="F41" s="42"/>
@@ -2277,7 +2274,7 @@
     <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="40"/>
       <c r="B42" s="42"/>
-      <c r="C42" s="57"/>
+      <c r="C42" s="55"/>
       <c r="D42" s="41"/>
       <c r="E42" s="41"/>
       <c r="F42" s="42"/>
@@ -2285,7 +2282,7 @@
     <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="40"/>
       <c r="B43" s="42"/>
-      <c r="C43" s="57"/>
+      <c r="C43" s="55"/>
       <c r="D43" s="41"/>
       <c r="E43" s="41"/>
       <c r="F43" s="42"/>
@@ -2293,7 +2290,7 @@
     <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="40"/>
       <c r="B44" s="42"/>
-      <c r="C44" s="57"/>
+      <c r="C44" s="55"/>
       <c r="D44" s="41"/>
       <c r="E44" s="41"/>
       <c r="F44" s="42"/>
@@ -2301,7 +2298,7 @@
     <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="40"/>
       <c r="B45" s="42"/>
-      <c r="C45" s="57"/>
+      <c r="C45" s="55"/>
       <c r="D45" s="41"/>
       <c r="E45" s="41"/>
       <c r="F45" s="42"/>
@@ -2309,7 +2306,7 @@
     <row r="46" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="40"/>
       <c r="B46" s="42"/>
-      <c r="C46" s="57"/>
+      <c r="C46" s="55"/>
       <c r="D46" s="41"/>
       <c r="E46" s="41"/>
       <c r="F46" s="42"/>
@@ -2317,85 +2314,93 @@
     <row r="47" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="40"/>
       <c r="B47" s="42"/>
-      <c r="C47" s="57"/>
+      <c r="C47" s="55"/>
       <c r="D47" s="41"/>
       <c r="E47" s="41"/>
       <c r="F47" s="42"/>
     </row>
     <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="58"/>
-      <c r="B48" s="59"/>
-      <c r="C48" s="60"/>
-      <c r="D48" s="51"/>
-      <c r="E48" s="51"/>
-      <c r="F48" s="59"/>
+      <c r="A48" s="40"/>
+      <c r="B48" s="42"/>
+      <c r="C48" s="55"/>
+      <c r="D48" s="41"/>
+      <c r="E48" s="41"/>
+      <c r="F48" s="42"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="61"/>
-      <c r="B49" s="53"/>
-      <c r="C49" s="54"/>
-      <c r="D49" s="55"/>
-      <c r="E49" s="55"/>
-      <c r="F49" s="56"/>
+      <c r="A49" s="56"/>
+      <c r="B49" s="57"/>
+      <c r="C49" s="58"/>
+      <c r="D49" s="51"/>
+      <c r="E49" s="51"/>
+      <c r="F49" s="57"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="62"/>
-      <c r="B50" s="59"/>
-      <c r="C50" s="60"/>
-      <c r="D50" s="51"/>
-      <c r="E50" s="51"/>
-      <c r="F50" s="63"/>
+      <c r="A50" s="59"/>
+      <c r="B50" s="44"/>
+      <c r="C50" s="45"/>
+      <c r="D50" s="53"/>
+      <c r="E50" s="53"/>
+      <c r="F50" s="54"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="64"/>
-      <c r="B51" s="53"/>
-      <c r="C51" s="54"/>
-      <c r="D51" s="65"/>
-      <c r="E51" s="55"/>
-      <c r="F51" s="56"/>
+      <c r="A51" s="60"/>
+      <c r="B51" s="57"/>
+      <c r="C51" s="58"/>
+      <c r="D51" s="51"/>
+      <c r="E51" s="51"/>
+      <c r="F51" s="61"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="66"/>
-      <c r="D52" s="55"/>
-      <c r="E52" s="67"/>
-      <c r="F52" s="56"/>
+      <c r="A52" s="62"/>
+      <c r="B52" s="44"/>
+      <c r="C52" s="45"/>
+      <c r="D52" s="63"/>
+      <c r="E52" s="53"/>
+      <c r="F52" s="54"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="68"/>
-      <c r="D53" s="69"/>
-      <c r="E53" s="69"/>
-      <c r="F53" s="70"/>
+      <c r="A53" s="64"/>
+      <c r="D53" s="53"/>
+      <c r="E53" s="65"/>
+      <c r="F53" s="54"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="58"/>
-      <c r="B54" s="49"/>
-      <c r="C54" s="50"/>
-      <c r="D54" s="51"/>
-      <c r="E54" s="51"/>
-      <c r="F54" s="59"/>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="71"/>
-      <c r="B56" s="53"/>
-      <c r="C56" s="54"/>
-      <c r="D56" s="55"/>
-      <c r="E56" s="55"/>
-      <c r="F56" s="72"/>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="73"/>
-      <c r="B57" s="49"/>
-      <c r="C57" s="50"/>
-      <c r="F57" s="74"/>
+      <c r="A54" s="66"/>
+      <c r="D54" s="67"/>
+      <c r="E54" s="67"/>
+      <c r="F54" s="68"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="56"/>
+      <c r="B55" s="49"/>
+      <c r="C55" s="50"/>
+      <c r="D55" s="51"/>
+      <c r="E55" s="51"/>
+      <c r="F55" s="57"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="69"/>
+      <c r="B57" s="44"/>
+      <c r="C57" s="45"/>
+      <c r="D57" s="53"/>
+      <c r="E57" s="53"/>
+      <c r="F57" s="70"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="71"/>
+      <c r="B58" s="49"/>
+      <c r="C58" s="50"/>
+      <c r="F58" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A23:C23"/>
     <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A25:C25"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C8" location="'Ticket Cena'!A1" display="🧾 Ver Ticket Cena"/>
@@ -2424,20 +2429,20 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
     </row>
     <row r="3" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2455,131 +2460,131 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="77" t="s">
+      <c r="A5" s="75" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="78" t="n">
+      <c r="B5" s="76" t="n">
         <v>800</v>
       </c>
-      <c r="C5" s="78" t="n">
+      <c r="C5" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="78" t="n">
+      <c r="D5" s="76" t="n">
         <f aca="false">B5-C5</f>
         <v>800</v>
       </c>
-      <c r="E5" s="79"/>
-      <c r="F5" s="79"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="77" t="s">
+      <c r="A6" s="75" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="78" t="n">
+      <c r="B6" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="C6" s="78" t="n">
+      <c r="C6" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="78" t="n">
+      <c r="D6" s="76" t="n">
         <f aca="false">B6-C6</f>
         <v>0</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="80" t="s">
+      <c r="A7" s="78" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="81" t="n">
+      <c r="B7" s="79" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="81" t="n">
+      <c r="C7" s="79" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="81" t="n">
+      <c r="D7" s="79" t="n">
         <f aca="false">B7-C7</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="80" t="s">
+      <c r="A8" s="78" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="81" t="n">
+      <c r="B8" s="79" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="81" t="n">
+      <c r="C8" s="79" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="81" t="n">
+      <c r="D8" s="79" t="n">
         <f aca="false">B8-C8</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="82" t="s">
+      <c r="A9" s="80" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="83" t="n">
+      <c r="B9" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="83" t="n">
+      <c r="C9" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="83" t="n">
+      <c r="D9" s="81" t="n">
         <f aca="false">B9-C9</f>
         <v>0</v>
       </c>
-      <c r="E9" s="84"/>
-      <c r="F9" s="84"/>
+      <c r="E9" s="82"/>
+      <c r="F9" s="82"/>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="77" t="s">
+      <c r="A10" s="75" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="78" t="n">
+      <c r="B10" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="78" t="n">
+      <c r="C10" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="78" t="n">
+      <c r="D10" s="76" t="n">
         <f aca="false">B10-C10</f>
         <v>0</v>
       </c>
-      <c r="E10" s="79"/>
-      <c r="F10" s="79"/>
+      <c r="E10" s="77"/>
+      <c r="F10" s="77"/>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="80" t="s">
+      <c r="A11" s="78" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="81" t="n">
+      <c r="B11" s="79" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="81" t="n">
+      <c r="C11" s="79" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="81" t="n">
+      <c r="D11" s="79" t="n">
         <f aca="false">B11-C11</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="85" t="s">
+      <c r="A12" s="83" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="55" t="n">
+      <c r="B12" s="53" t="n">
         <f aca="false">SUM(B5:B11)</f>
         <v>800</v>
       </c>
-      <c r="C12" s="55" t="n">
+      <c r="C12" s="53" t="n">
         <f aca="false">SUM(C5:C11)</f>
         <v>0</v>
       </c>
-      <c r="D12" s="55" t="n">
+      <c r="D12" s="53" t="n">
         <f aca="false">B12-C12</f>
         <v>800</v>
       </c>
@@ -2614,745 +2619,745 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="73" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="86" t="s">
+      <c r="A2" s="84" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="86"/>
-      <c r="C2" s="86"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="86"/>
-      <c r="F2" s="86"/>
-      <c r="G2" s="86"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
     </row>
     <row r="3" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="87" t="s">
+      <c r="A4" s="85" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="87" t="s">
+      <c r="B4" s="85" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="87" t="s">
+      <c r="C4" s="85" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="87" t="s">
+      <c r="D4" s="85" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="87" t="s">
+      <c r="E4" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="87" t="s">
+      <c r="F4" s="85" t="s">
         <v>49</v>
       </c>
-      <c r="G4" s="88" t="s">
+      <c r="G4" s="86" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="89" t="n">
+      <c r="A5" s="87" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="90" t="s">
+      <c r="B5" s="88" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="91" t="n">
+      <c r="C5" s="89" t="n">
         <v>50</v>
       </c>
-      <c r="D5" s="92" t="s">
+      <c r="D5" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="E5" s="91" t="n">
+      <c r="E5" s="89" t="n">
         <v>50</v>
       </c>
-      <c r="F5" s="93" t="s">
+      <c r="F5" s="91" t="s">
         <v>53</v>
       </c>
-      <c r="G5" s="94"/>
+      <c r="G5" s="92"/>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="89" t="n">
+      <c r="A6" s="87" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="90"/>
-      <c r="C6" s="91"/>
-      <c r="D6" s="92"/>
-      <c r="E6" s="91"/>
-      <c r="F6" s="93"/>
-      <c r="G6" s="94"/>
+      <c r="B6" s="88"/>
+      <c r="C6" s="89"/>
+      <c r="D6" s="90"/>
+      <c r="E6" s="89"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="92"/>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="95" t="n">
+      <c r="A7" s="93" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="96" t="s">
+      <c r="B7" s="94" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="97" t="n">
+      <c r="C7" s="95" t="n">
         <v>50</v>
       </c>
-      <c r="D7" s="98" t="s">
+      <c r="D7" s="96" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="97" t="n">
+      <c r="E7" s="95" t="n">
         <v>50</v>
       </c>
-      <c r="F7" s="99" t="s">
+      <c r="F7" s="97" t="s">
         <v>53</v>
       </c>
-      <c r="G7" s="100"/>
+      <c r="G7" s="98"/>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="89" t="n">
+      <c r="A8" s="87" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="90" t="s">
+      <c r="B8" s="88" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="91" t="n">
+      <c r="C8" s="89" t="n">
         <v>50</v>
       </c>
-      <c r="D8" s="92" t="s">
+      <c r="D8" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="E8" s="91" t="n">
+      <c r="E8" s="89" t="n">
         <v>50</v>
       </c>
-      <c r="F8" s="93" t="s">
+      <c r="F8" s="91" t="s">
         <v>53</v>
       </c>
-      <c r="G8" s="94"/>
+      <c r="G8" s="92"/>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="95" t="n">
+      <c r="A9" s="93" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="96" t="s">
+      <c r="B9" s="94" t="s">
         <v>56</v>
       </c>
-      <c r="C9" s="97" t="n">
+      <c r="C9" s="95" t="n">
         <v>50</v>
       </c>
-      <c r="D9" s="98" t="s">
+      <c r="D9" s="96" t="s">
         <v>52</v>
       </c>
-      <c r="E9" s="97" t="n">
+      <c r="E9" s="95" t="n">
         <v>50</v>
       </c>
-      <c r="F9" s="99" t="s">
+      <c r="F9" s="97" t="s">
         <v>53</v>
       </c>
-      <c r="G9" s="100"/>
+      <c r="G9" s="98"/>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="89" t="n">
+      <c r="A10" s="87" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="90" t="s">
+      <c r="B10" s="88" t="s">
         <v>57</v>
       </c>
-      <c r="C10" s="91" t="n">
+      <c r="C10" s="89" t="n">
         <v>50</v>
       </c>
-      <c r="D10" s="92" t="s">
+      <c r="D10" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="E10" s="91" t="n">
+      <c r="E10" s="89" t="n">
         <v>50</v>
       </c>
-      <c r="F10" s="93" t="s">
+      <c r="F10" s="91" t="s">
         <v>53</v>
       </c>
-      <c r="G10" s="94"/>
+      <c r="G10" s="92"/>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="95" t="n">
+      <c r="A11" s="93" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="96" t="s">
+      <c r="B11" s="94" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="97" t="n">
+      <c r="C11" s="95" t="n">
         <v>50</v>
       </c>
-      <c r="D11" s="98" t="s">
+      <c r="D11" s="96" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="97" t="n">
+      <c r="E11" s="95" t="n">
         <v>50</v>
       </c>
-      <c r="F11" s="99" t="s">
+      <c r="F11" s="97" t="s">
         <v>53</v>
       </c>
-      <c r="G11" s="100"/>
+      <c r="G11" s="98"/>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="89" t="n">
+      <c r="A12" s="87" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="90" t="s">
+      <c r="B12" s="88" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="91" t="n">
+      <c r="C12" s="89" t="n">
         <v>50</v>
       </c>
-      <c r="D12" s="92" t="s">
+      <c r="D12" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="E12" s="91" t="n">
+      <c r="E12" s="89" t="n">
         <v>50</v>
       </c>
-      <c r="F12" s="93" t="s">
+      <c r="F12" s="91" t="s">
         <v>53</v>
       </c>
-      <c r="G12" s="94"/>
+      <c r="G12" s="92"/>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="95" t="n">
+      <c r="A13" s="93" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="96" t="s">
+      <c r="B13" s="94" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="97" t="n">
+      <c r="C13" s="95" t="n">
         <v>50</v>
       </c>
-      <c r="D13" s="98" t="s">
+      <c r="D13" s="96" t="s">
         <v>52</v>
       </c>
-      <c r="E13" s="97" t="n">
+      <c r="E13" s="95" t="n">
         <v>50</v>
       </c>
-      <c r="F13" s="99" t="s">
+      <c r="F13" s="97" t="s">
         <v>53</v>
       </c>
-      <c r="G13" s="100"/>
+      <c r="G13" s="98"/>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="89" t="n">
+      <c r="A14" s="87" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="90" t="s">
+      <c r="B14" s="88" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="91" t="n">
+      <c r="C14" s="89" t="n">
         <v>50</v>
       </c>
-      <c r="D14" s="92" t="s">
+      <c r="D14" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="E14" s="91" t="n">
+      <c r="E14" s="89" t="n">
         <v>50</v>
       </c>
-      <c r="F14" s="93" t="s">
+      <c r="F14" s="91" t="s">
         <v>53</v>
       </c>
-      <c r="G14" s="94"/>
+      <c r="G14" s="92"/>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="95" t="n">
+      <c r="A15" s="93" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="96" t="s">
+      <c r="B15" s="94" t="s">
         <v>62</v>
       </c>
-      <c r="C15" s="97" t="n">
+      <c r="C15" s="95" t="n">
         <v>50</v>
       </c>
-      <c r="D15" s="98" t="s">
+      <c r="D15" s="96" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="97" t="n">
+      <c r="E15" s="95" t="n">
         <v>50</v>
       </c>
-      <c r="F15" s="99" t="s">
+      <c r="F15" s="97" t="s">
         <v>53</v>
       </c>
-      <c r="G15" s="100"/>
+      <c r="G15" s="98"/>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="89" t="n">
+      <c r="A16" s="87" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="90" t="s">
+      <c r="B16" s="88" t="s">
         <v>63</v>
       </c>
-      <c r="C16" s="91" t="n">
+      <c r="C16" s="89" t="n">
         <v>50</v>
       </c>
-      <c r="D16" s="93" t="s">
+      <c r="D16" s="91" t="s">
         <v>64</v>
       </c>
-      <c r="E16" s="91" t="n">
+      <c r="E16" s="89" t="n">
         <v>50</v>
       </c>
-      <c r="F16" s="93" t="s">
+      <c r="F16" s="91" t="s">
         <v>53</v>
       </c>
-      <c r="G16" s="94"/>
+      <c r="G16" s="92"/>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="89" t="n">
+      <c r="A17" s="87" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="101" t="s">
+      <c r="B17" s="99" t="s">
         <v>65</v>
       </c>
-      <c r="C17" s="102" t="n">
+      <c r="C17" s="100" t="n">
         <v>50</v>
       </c>
-      <c r="D17" s="103" t="s">
+      <c r="D17" s="101" t="s">
         <v>66</v>
       </c>
-      <c r="E17" s="102" t="n">
+      <c r="E17" s="100" t="n">
         <v>50</v>
       </c>
-      <c r="F17" s="103" t="s">
+      <c r="F17" s="101" t="s">
         <v>53</v>
       </c>
-      <c r="G17" s="104"/>
+      <c r="G17" s="102"/>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="95" t="n">
+      <c r="A18" s="93" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="105" t="s">
+      <c r="B18" s="103" t="s">
         <v>67</v>
       </c>
-      <c r="C18" s="106" t="n">
+      <c r="C18" s="104" t="n">
         <v>50</v>
       </c>
-      <c r="D18" s="107" t="s">
+      <c r="D18" s="105" t="s">
         <v>66</v>
       </c>
-      <c r="E18" s="106" t="n">
+      <c r="E18" s="104" t="n">
         <v>50</v>
       </c>
-      <c r="F18" s="107" t="s">
+      <c r="F18" s="105" t="s">
         <v>53</v>
       </c>
-      <c r="G18" s="108"/>
-    </row>
-    <row r="19" s="110" customFormat="true" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="95" t="n">
+      <c r="G18" s="106"/>
+    </row>
+    <row r="19" s="108" customFormat="true" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="93" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="105" t="s">
+      <c r="B19" s="103" t="s">
         <v>68</v>
       </c>
-      <c r="C19" s="106" t="n">
+      <c r="C19" s="104" t="n">
         <v>50</v>
       </c>
-      <c r="D19" s="107" t="s">
+      <c r="D19" s="105" t="s">
         <v>69</v>
       </c>
-      <c r="E19" s="106" t="n">
+      <c r="E19" s="104" t="n">
         <v>50</v>
       </c>
-      <c r="F19" s="107" t="s">
+      <c r="F19" s="105" t="s">
         <v>53</v>
       </c>
-      <c r="G19" s="109"/>
+      <c r="G19" s="107"/>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="95" t="n">
+      <c r="A20" s="93" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="105" t="s">
+      <c r="B20" s="103" t="s">
         <v>70</v>
       </c>
-      <c r="C20" s="106" t="n">
+      <c r="C20" s="104" t="n">
         <v>50</v>
       </c>
-      <c r="D20" s="107" t="s">
+      <c r="D20" s="105" t="s">
         <v>69</v>
       </c>
-      <c r="E20" s="106" t="n">
+      <c r="E20" s="104" t="n">
         <v>50</v>
       </c>
-      <c r="F20" s="107" t="s">
+      <c r="F20" s="105" t="s">
         <v>53</v>
       </c>
-      <c r="G20" s="100"/>
+      <c r="G20" s="98"/>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="95" t="n">
+      <c r="A21" s="93" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="105" t="s">
+      <c r="B21" s="103" t="s">
         <v>71</v>
       </c>
-      <c r="C21" s="106" t="n">
+      <c r="C21" s="104" t="n">
         <v>50</v>
       </c>
-      <c r="D21" s="107" t="s">
+      <c r="D21" s="105" t="s">
         <v>69</v>
       </c>
-      <c r="E21" s="106" t="n">
+      <c r="E21" s="104" t="n">
         <v>50</v>
       </c>
-      <c r="F21" s="107" t="s">
+      <c r="F21" s="105" t="s">
         <v>53</v>
       </c>
-      <c r="G21" s="109"/>
+      <c r="G21" s="107"/>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="95"/>
-      <c r="B22" s="105"/>
-      <c r="C22" s="106"/>
-      <c r="D22" s="107"/>
-      <c r="E22" s="106"/>
-      <c r="F22" s="107"/>
-      <c r="G22" s="109"/>
+      <c r="A22" s="93"/>
+      <c r="B22" s="103"/>
+      <c r="C22" s="104"/>
+      <c r="D22" s="105"/>
+      <c r="E22" s="104"/>
+      <c r="F22" s="105"/>
+      <c r="G22" s="107"/>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="95"/>
-      <c r="B23" s="105"/>
-      <c r="C23" s="106"/>
-      <c r="D23" s="107"/>
-      <c r="E23" s="106"/>
-      <c r="F23" s="107"/>
-      <c r="G23" s="108"/>
+      <c r="A23" s="93"/>
+      <c r="B23" s="103"/>
+      <c r="C23" s="104"/>
+      <c r="D23" s="105"/>
+      <c r="E23" s="104"/>
+      <c r="F23" s="105"/>
+      <c r="G23" s="106"/>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="95"/>
-      <c r="B24" s="105"/>
-      <c r="C24" s="106"/>
-      <c r="D24" s="107"/>
-      <c r="E24" s="106"/>
-      <c r="F24" s="107"/>
-      <c r="G24" s="108"/>
+      <c r="A24" s="93"/>
+      <c r="B24" s="103"/>
+      <c r="C24" s="104"/>
+      <c r="D24" s="105"/>
+      <c r="E24" s="104"/>
+      <c r="F24" s="105"/>
+      <c r="G24" s="106"/>
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="95"/>
-      <c r="B25" s="105"/>
-      <c r="C25" s="106"/>
-      <c r="D25" s="107"/>
-      <c r="E25" s="106"/>
-      <c r="F25" s="107"/>
-      <c r="G25" s="108"/>
+      <c r="A25" s="93"/>
+      <c r="B25" s="103"/>
+      <c r="C25" s="104"/>
+      <c r="D25" s="105"/>
+      <c r="E25" s="104"/>
+      <c r="F25" s="105"/>
+      <c r="G25" s="106"/>
     </row>
     <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="111" t="s">
+      <c r="A26" s="109" t="s">
         <v>72</v>
       </c>
-      <c r="B26" s="111"/>
-      <c r="C26" s="112" t="n">
+      <c r="B26" s="109"/>
+      <c r="C26" s="110" t="n">
         <v>800</v>
       </c>
-      <c r="D26" s="113"/>
-      <c r="E26" s="112" t="n">
+      <c r="D26" s="111"/>
+      <c r="E26" s="110" t="n">
         <v>0</v>
       </c>
-      <c r="F26" s="113"/>
-      <c r="G26" s="113"/>
+      <c r="F26" s="111"/>
+      <c r="G26" s="111"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="114"/>
-      <c r="B27" s="114"/>
-      <c r="C27" s="115"/>
-      <c r="D27" s="114"/>
-      <c r="E27" s="114"/>
-      <c r="F27" s="114"/>
-      <c r="G27" s="114"/>
+      <c r="A27" s="112"/>
+      <c r="B27" s="112"/>
+      <c r="C27" s="113"/>
+      <c r="D27" s="112"/>
+      <c r="E27" s="112"/>
+      <c r="F27" s="112"/>
+      <c r="G27" s="112"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="114"/>
-      <c r="B28" s="114"/>
-      <c r="C28" s="114"/>
-      <c r="D28" s="114"/>
-      <c r="E28" s="114"/>
-      <c r="F28" s="114"/>
-      <c r="G28" s="114"/>
+      <c r="A28" s="112"/>
+      <c r="B28" s="112"/>
+      <c r="C28" s="112"/>
+      <c r="D28" s="112"/>
+      <c r="E28" s="112"/>
+      <c r="F28" s="112"/>
+      <c r="G28" s="112"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="114"/>
-      <c r="B29" s="114"/>
-      <c r="C29" s="114"/>
-      <c r="D29" s="114"/>
-      <c r="E29" s="114"/>
-      <c r="F29" s="114"/>
-      <c r="G29" s="114"/>
+      <c r="A29" s="112"/>
+      <c r="B29" s="112"/>
+      <c r="C29" s="112"/>
+      <c r="D29" s="112"/>
+      <c r="E29" s="112"/>
+      <c r="F29" s="112"/>
+      <c r="G29" s="112"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="114"/>
-      <c r="B30" s="114"/>
-      <c r="C30" s="114"/>
-      <c r="D30" s="114"/>
-      <c r="E30" s="114"/>
-      <c r="F30" s="114"/>
-      <c r="G30" s="114"/>
+      <c r="A30" s="112"/>
+      <c r="B30" s="112"/>
+      <c r="C30" s="112"/>
+      <c r="D30" s="112"/>
+      <c r="E30" s="112"/>
+      <c r="F30" s="112"/>
+      <c r="G30" s="112"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="114"/>
-      <c r="B31" s="114"/>
-      <c r="C31" s="114"/>
-      <c r="D31" s="114"/>
-      <c r="E31" s="114"/>
-      <c r="F31" s="114"/>
-      <c r="G31" s="114"/>
+      <c r="A31" s="112"/>
+      <c r="B31" s="112"/>
+      <c r="C31" s="112"/>
+      <c r="D31" s="112"/>
+      <c r="E31" s="112"/>
+      <c r="F31" s="112"/>
+      <c r="G31" s="112"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="114"/>
-      <c r="B32" s="114"/>
-      <c r="C32" s="114"/>
-      <c r="D32" s="114"/>
-      <c r="E32" s="114"/>
-      <c r="F32" s="114"/>
-      <c r="G32" s="114"/>
+      <c r="A32" s="112"/>
+      <c r="B32" s="112"/>
+      <c r="C32" s="112"/>
+      <c r="D32" s="112"/>
+      <c r="E32" s="112"/>
+      <c r="F32" s="112"/>
+      <c r="G32" s="112"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="114"/>
-      <c r="B33" s="114"/>
-      <c r="C33" s="114"/>
-      <c r="D33" s="114"/>
-      <c r="E33" s="114"/>
-      <c r="F33" s="114"/>
-      <c r="G33" s="114"/>
+      <c r="A33" s="112"/>
+      <c r="B33" s="112"/>
+      <c r="C33" s="112"/>
+      <c r="D33" s="112"/>
+      <c r="E33" s="112"/>
+      <c r="F33" s="112"/>
+      <c r="G33" s="112"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="114"/>
-      <c r="B34" s="114"/>
-      <c r="C34" s="114"/>
-      <c r="D34" s="114"/>
-      <c r="E34" s="114"/>
-      <c r="F34" s="114"/>
-      <c r="G34" s="114"/>
+      <c r="A34" s="112"/>
+      <c r="B34" s="112"/>
+      <c r="C34" s="112"/>
+      <c r="D34" s="112"/>
+      <c r="E34" s="112"/>
+      <c r="F34" s="112"/>
+      <c r="G34" s="112"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="114"/>
-      <c r="B35" s="114"/>
-      <c r="C35" s="114"/>
-      <c r="D35" s="114"/>
-      <c r="E35" s="114"/>
-      <c r="F35" s="114"/>
-      <c r="G35" s="114"/>
+      <c r="A35" s="112"/>
+      <c r="B35" s="112"/>
+      <c r="C35" s="112"/>
+      <c r="D35" s="112"/>
+      <c r="E35" s="112"/>
+      <c r="F35" s="112"/>
+      <c r="G35" s="112"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="114"/>
-      <c r="B36" s="114"/>
-      <c r="C36" s="114"/>
-      <c r="D36" s="114"/>
-      <c r="E36" s="114"/>
-      <c r="F36" s="114"/>
-      <c r="G36" s="114"/>
+      <c r="A36" s="112"/>
+      <c r="B36" s="112"/>
+      <c r="C36" s="112"/>
+      <c r="D36" s="112"/>
+      <c r="E36" s="112"/>
+      <c r="F36" s="112"/>
+      <c r="G36" s="112"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="114"/>
-      <c r="B37" s="114"/>
-      <c r="C37" s="114"/>
-      <c r="D37" s="114"/>
-      <c r="E37" s="114"/>
-      <c r="F37" s="114"/>
-      <c r="G37" s="114"/>
+      <c r="A37" s="112"/>
+      <c r="B37" s="112"/>
+      <c r="C37" s="112"/>
+      <c r="D37" s="112"/>
+      <c r="E37" s="112"/>
+      <c r="F37" s="112"/>
+      <c r="G37" s="112"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="114"/>
-      <c r="B38" s="114"/>
-      <c r="C38" s="114"/>
-      <c r="D38" s="114"/>
-      <c r="E38" s="114"/>
-      <c r="F38" s="114"/>
-      <c r="G38" s="114"/>
+      <c r="A38" s="112"/>
+      <c r="B38" s="112"/>
+      <c r="C38" s="112"/>
+      <c r="D38" s="112"/>
+      <c r="E38" s="112"/>
+      <c r="F38" s="112"/>
+      <c r="G38" s="112"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="114"/>
-      <c r="B39" s="114"/>
-      <c r="C39" s="114"/>
-      <c r="D39" s="114"/>
-      <c r="E39" s="114"/>
-      <c r="F39" s="114"/>
-      <c r="G39" s="114"/>
+      <c r="A39" s="112"/>
+      <c r="B39" s="112"/>
+      <c r="C39" s="112"/>
+      <c r="D39" s="112"/>
+      <c r="E39" s="112"/>
+      <c r="F39" s="112"/>
+      <c r="G39" s="112"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="114"/>
-      <c r="B40" s="114"/>
-      <c r="C40" s="114"/>
-      <c r="D40" s="114"/>
-      <c r="E40" s="114"/>
-      <c r="F40" s="114"/>
-      <c r="G40" s="114"/>
+      <c r="A40" s="112"/>
+      <c r="B40" s="112"/>
+      <c r="C40" s="112"/>
+      <c r="D40" s="112"/>
+      <c r="E40" s="112"/>
+      <c r="F40" s="112"/>
+      <c r="G40" s="112"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="114"/>
-      <c r="B41" s="114"/>
-      <c r="C41" s="114"/>
-      <c r="D41" s="114"/>
-      <c r="E41" s="114"/>
-      <c r="F41" s="114"/>
-      <c r="G41" s="114"/>
+      <c r="A41" s="112"/>
+      <c r="B41" s="112"/>
+      <c r="C41" s="112"/>
+      <c r="D41" s="112"/>
+      <c r="E41" s="112"/>
+      <c r="F41" s="112"/>
+      <c r="G41" s="112"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="114"/>
-      <c r="B42" s="114"/>
-      <c r="C42" s="114"/>
-      <c r="D42" s="114"/>
-      <c r="E42" s="114"/>
-      <c r="F42" s="114"/>
-      <c r="G42" s="114"/>
+      <c r="A42" s="112"/>
+      <c r="B42" s="112"/>
+      <c r="C42" s="112"/>
+      <c r="D42" s="112"/>
+      <c r="E42" s="112"/>
+      <c r="F42" s="112"/>
+      <c r="G42" s="112"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="114"/>
-      <c r="B43" s="114"/>
-      <c r="C43" s="114"/>
-      <c r="D43" s="114"/>
-      <c r="E43" s="114"/>
-      <c r="F43" s="114"/>
-      <c r="G43" s="114"/>
+      <c r="A43" s="112"/>
+      <c r="B43" s="112"/>
+      <c r="C43" s="112"/>
+      <c r="D43" s="112"/>
+      <c r="E43" s="112"/>
+      <c r="F43" s="112"/>
+      <c r="G43" s="112"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="114"/>
-      <c r="B44" s="114"/>
-      <c r="C44" s="114"/>
-      <c r="D44" s="114"/>
-      <c r="E44" s="114"/>
-      <c r="F44" s="114"/>
-      <c r="G44" s="114"/>
+      <c r="A44" s="112"/>
+      <c r="B44" s="112"/>
+      <c r="C44" s="112"/>
+      <c r="D44" s="112"/>
+      <c r="E44" s="112"/>
+      <c r="F44" s="112"/>
+      <c r="G44" s="112"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="114"/>
-      <c r="B45" s="114"/>
-      <c r="C45" s="114"/>
-      <c r="D45" s="114"/>
-      <c r="E45" s="114"/>
-      <c r="F45" s="114"/>
-      <c r="G45" s="114"/>
+      <c r="A45" s="112"/>
+      <c r="B45" s="112"/>
+      <c r="C45" s="112"/>
+      <c r="D45" s="112"/>
+      <c r="E45" s="112"/>
+      <c r="F45" s="112"/>
+      <c r="G45" s="112"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="114"/>
-      <c r="B46" s="114"/>
-      <c r="C46" s="114"/>
-      <c r="D46" s="114"/>
-      <c r="E46" s="114"/>
-      <c r="F46" s="114"/>
-      <c r="G46" s="114"/>
+      <c r="A46" s="112"/>
+      <c r="B46" s="112"/>
+      <c r="C46" s="112"/>
+      <c r="D46" s="112"/>
+      <c r="E46" s="112"/>
+      <c r="F46" s="112"/>
+      <c r="G46" s="112"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="114"/>
-      <c r="B47" s="114"/>
-      <c r="C47" s="114"/>
-      <c r="D47" s="114"/>
-      <c r="E47" s="114"/>
-      <c r="F47" s="114"/>
-      <c r="G47" s="114"/>
+      <c r="A47" s="112"/>
+      <c r="B47" s="112"/>
+      <c r="C47" s="112"/>
+      <c r="D47" s="112"/>
+      <c r="E47" s="112"/>
+      <c r="F47" s="112"/>
+      <c r="G47" s="112"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="114"/>
-      <c r="B48" s="114"/>
-      <c r="C48" s="114"/>
-      <c r="D48" s="114"/>
-      <c r="E48" s="114"/>
-      <c r="F48" s="114"/>
-      <c r="G48" s="114"/>
+      <c r="A48" s="112"/>
+      <c r="B48" s="112"/>
+      <c r="C48" s="112"/>
+      <c r="D48" s="112"/>
+      <c r="E48" s="112"/>
+      <c r="F48" s="112"/>
+      <c r="G48" s="112"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="114"/>
-      <c r="B49" s="114"/>
-      <c r="C49" s="114"/>
-      <c r="D49" s="114"/>
-      <c r="E49" s="114"/>
-      <c r="F49" s="114"/>
-      <c r="G49" s="114"/>
+      <c r="A49" s="112"/>
+      <c r="B49" s="112"/>
+      <c r="C49" s="112"/>
+      <c r="D49" s="112"/>
+      <c r="E49" s="112"/>
+      <c r="F49" s="112"/>
+      <c r="G49" s="112"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="114"/>
-      <c r="B50" s="114"/>
-      <c r="C50" s="114"/>
-      <c r="D50" s="114"/>
-      <c r="E50" s="114"/>
-      <c r="F50" s="114"/>
-      <c r="G50" s="114"/>
+      <c r="A50" s="112"/>
+      <c r="B50" s="112"/>
+      <c r="C50" s="112"/>
+      <c r="D50" s="112"/>
+      <c r="E50" s="112"/>
+      <c r="F50" s="112"/>
+      <c r="G50" s="112"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="114"/>
-      <c r="B51" s="114"/>
-      <c r="C51" s="114"/>
-      <c r="D51" s="114"/>
-      <c r="E51" s="114"/>
-      <c r="F51" s="114"/>
-      <c r="G51" s="114"/>
+      <c r="A51" s="112"/>
+      <c r="B51" s="112"/>
+      <c r="C51" s="112"/>
+      <c r="D51" s="112"/>
+      <c r="E51" s="112"/>
+      <c r="F51" s="112"/>
+      <c r="G51" s="112"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="114"/>
-      <c r="B52" s="114"/>
-      <c r="C52" s="114"/>
-      <c r="D52" s="114"/>
-      <c r="E52" s="114"/>
-      <c r="F52" s="114"/>
-      <c r="G52" s="114"/>
+      <c r="A52" s="112"/>
+      <c r="B52" s="112"/>
+      <c r="C52" s="112"/>
+      <c r="D52" s="112"/>
+      <c r="E52" s="112"/>
+      <c r="F52" s="112"/>
+      <c r="G52" s="112"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="114"/>
-      <c r="B53" s="114"/>
-      <c r="C53" s="114"/>
-      <c r="D53" s="114"/>
-      <c r="E53" s="114"/>
-      <c r="F53" s="114"/>
-      <c r="G53" s="114"/>
+      <c r="A53" s="112"/>
+      <c r="B53" s="112"/>
+      <c r="C53" s="112"/>
+      <c r="D53" s="112"/>
+      <c r="E53" s="112"/>
+      <c r="F53" s="112"/>
+      <c r="G53" s="112"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="114"/>
-      <c r="B54" s="114"/>
-      <c r="C54" s="114"/>
-      <c r="D54" s="114"/>
-      <c r="E54" s="114"/>
-      <c r="F54" s="114"/>
-      <c r="G54" s="114"/>
+      <c r="A54" s="112"/>
+      <c r="B54" s="112"/>
+      <c r="C54" s="112"/>
+      <c r="D54" s="112"/>
+      <c r="E54" s="112"/>
+      <c r="F54" s="112"/>
+      <c r="G54" s="112"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="114"/>
-      <c r="B55" s="114"/>
-      <c r="C55" s="114"/>
-      <c r="D55" s="114"/>
-      <c r="E55" s="114"/>
-      <c r="F55" s="114"/>
-      <c r="G55" s="114"/>
+      <c r="A55" s="112"/>
+      <c r="B55" s="112"/>
+      <c r="C55" s="112"/>
+      <c r="D55" s="112"/>
+      <c r="E55" s="112"/>
+      <c r="F55" s="112"/>
+      <c r="G55" s="112"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="114"/>
-      <c r="B56" s="114"/>
-      <c r="C56" s="114"/>
-      <c r="D56" s="114"/>
-      <c r="E56" s="114"/>
-      <c r="F56" s="114"/>
-      <c r="G56" s="114"/>
+      <c r="A56" s="112"/>
+      <c r="B56" s="112"/>
+      <c r="C56" s="112"/>
+      <c r="D56" s="112"/>
+      <c r="E56" s="112"/>
+      <c r="F56" s="112"/>
+      <c r="G56" s="112"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="114"/>
-      <c r="B57" s="114"/>
-      <c r="C57" s="114"/>
-      <c r="D57" s="114"/>
-      <c r="E57" s="114"/>
-      <c r="F57" s="114"/>
-      <c r="G57" s="114"/>
+      <c r="A57" s="112"/>
+      <c r="B57" s="112"/>
+      <c r="C57" s="112"/>
+      <c r="D57" s="112"/>
+      <c r="E57" s="112"/>
+      <c r="F57" s="112"/>
+      <c r="G57" s="112"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="114"/>
-      <c r="B58" s="114"/>
-      <c r="C58" s="114"/>
-      <c r="D58" s="114"/>
-      <c r="E58" s="114"/>
-      <c r="F58" s="114"/>
-      <c r="G58" s="114"/>
+      <c r="A58" s="112"/>
+      <c r="B58" s="112"/>
+      <c r="C58" s="112"/>
+      <c r="D58" s="112"/>
+      <c r="E58" s="112"/>
+      <c r="F58" s="112"/>
+      <c r="G58" s="112"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="114"/>
-      <c r="B59" s="114"/>
-      <c r="C59" s="114"/>
-      <c r="D59" s="114"/>
-      <c r="E59" s="114"/>
-      <c r="F59" s="114"/>
-      <c r="G59" s="114"/>
+      <c r="A59" s="112"/>
+      <c r="B59" s="112"/>
+      <c r="C59" s="112"/>
+      <c r="D59" s="112"/>
+      <c r="E59" s="112"/>
+      <c r="F59" s="112"/>
+      <c r="G59" s="112"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3382,12 +3387,12 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="116" t="s">
+      <c r="A1" s="114" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="117" t="s">
+      <c r="A2" s="115" t="s">
         <v>74</v>
       </c>
     </row>
@@ -3416,12 +3421,12 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="116" t="s">
+      <c r="A1" s="114" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="117" t="s">
+      <c r="A2" s="115" t="s">
         <v>76</v>
       </c>
     </row>
@@ -3450,12 +3455,12 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="116" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="119" t="s">
+      <c r="A2" s="117" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3485,7 +3490,7 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="118" t="s">
         <v>79</v>
       </c>
     </row>
@@ -3514,7 +3519,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="119" t="s">
+      <c r="A7" s="117" t="s">
         <v>86</v>
       </c>
     </row>
@@ -3539,7 +3544,7 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="119" t="s">
+      <c r="A13" s="117" t="s">
         <v>91</v>
       </c>
     </row>
@@ -3564,7 +3569,7 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="119" t="s">
+      <c r="A19" s="117" t="s">
         <v>96</v>
       </c>
     </row>
@@ -3585,10 +3590,10 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="121" t="s">
+      <c r="A22" s="119" t="s">
         <v>99</v>
       </c>
-      <c r="B22" s="121" t="n">
+      <c r="B22" s="119" t="n">
         <v>308</v>
       </c>
     </row>

--- a/LibroCuentas_PTP_2026.xlsx
+++ b/LibroCuentas_PTP_2026.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="104">
   <si>
     <t xml:space="preserve">PEÑA TAURINA PEGUERINOS</t>
   </si>
@@ -98,6 +98,9 @@
   </si>
   <si>
     <t xml:space="preserve">Devolución entrada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pago toro de fuego</t>
   </si>
   <si>
     <t xml:space="preserve">📊 TOTAL PARCIAL</t>
@@ -1480,9 +1483,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>3323520</xdr:colOff>
+      <xdr:colOff>3323160</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>123480</xdr:rowOff>
+      <xdr:rowOff>123120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1496,7 +1499,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="600120"/>
-          <a:ext cx="3323520" cy="5704920"/>
+          <a:ext cx="3323160" cy="5704560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1522,9 +1525,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>66240</xdr:colOff>
+      <xdr:colOff>65880</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>4752360</xdr:rowOff>
+      <xdr:rowOff>4752000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1538,7 +1541,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="600120"/>
-          <a:ext cx="5704920" cy="4752360"/>
+          <a:ext cx="5704560" cy="4752000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1564,9 +1567,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>3612960</xdr:colOff>
+      <xdr:colOff>3612600</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>4741560</xdr:rowOff>
+      <xdr:rowOff>4741200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1580,7 +1583,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="566640"/>
-          <a:ext cx="3612960" cy="4755960"/>
+          <a:ext cx="3612600" cy="4755600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1775,7 +1778,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
@@ -2088,79 +2091,76 @@
       <c r="E23" s="34"/>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="36" t="s">
+      <c r="A24" s="16" t="n">
+        <v>46249</v>
+      </c>
+      <c r="B24" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="36"/>
-      <c r="C24" s="36"/>
-      <c r="D24" s="37" t="n">
-        <f aca="false">SUM(D6:D23)</f>
+      <c r="C24" s="18"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="36"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="37" t="n">
+        <f aca="false">SUM(D6:D24)</f>
         <v>1197.5</v>
       </c>
-      <c r="E24" s="38" t="n">
-        <f aca="false">SUM(E6:E23)</f>
-        <v>618</v>
-      </c>
-      <c r="F24" s="39" t="n">
-        <f aca="false">D24-E24</f>
-        <v>579.5</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="40"/>
-      <c r="B25" s="40"/>
-      <c r="C25" s="40"/>
-      <c r="D25" s="41"/>
-      <c r="E25" s="41"/>
-      <c r="F25" s="42"/>
+      <c r="E25" s="38" t="n">
+        <f aca="false">SUM(E6:E24)</f>
+        <v>718</v>
+      </c>
+      <c r="F25" s="39" t="n">
+        <f aca="false">D25-E25</f>
+        <v>479.5</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="B26" s="44"/>
-      <c r="C26" s="45"/>
-      <c r="D26" s="46" t="n">
-        <f aca="false">SUM(D6:D23)</f>
+      <c r="A26" s="40"/>
+      <c r="B26" s="40"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="42"/>
+    </row>
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="44"/>
+      <c r="C27" s="45"/>
+      <c r="D27" s="46" t="n">
+        <f aca="false">SUM(D6:D24)</f>
         <v>1197.5</v>
       </c>
-      <c r="E26" s="46" t="n">
-        <f aca="false">SUM(E6:E23)</f>
-        <v>618</v>
-      </c>
-      <c r="F26" s="47" t="n">
-        <f aca="false">D26-E26</f>
-        <v>579.5</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="48" t="s">
-        <v>26</v>
-      </c>
-      <c r="B27" s="49"/>
-      <c r="C27" s="50"/>
-      <c r="D27" s="51"/>
-      <c r="E27" s="51"/>
-      <c r="F27" s="52" t="n">
-        <f aca="false">D24-E24</f>
-        <v>579.5</v>
+      <c r="E27" s="46" t="n">
+        <f aca="false">SUM(E6:E24)</f>
+        <v>718</v>
+      </c>
+      <c r="F27" s="47" t="n">
+        <f aca="false">D27-E27</f>
+        <v>479.5</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="43" t="s">
+      <c r="A28" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="44"/>
-      <c r="C28" s="45"/>
-      <c r="D28" s="46" t="n">
-        <f aca="false">D26</f>
-        <v>1197.5</v>
-      </c>
-      <c r="E28" s="53" t="n">
-        <f aca="false">E26</f>
-        <v>618</v>
-      </c>
-      <c r="F28" s="54"/>
+      <c r="B28" s="49"/>
+      <c r="C28" s="50"/>
+      <c r="D28" s="51"/>
+      <c r="E28" s="51"/>
+      <c r="F28" s="52" t="n">
+        <f aca="false">D27-E27</f>
+        <v>479.5</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="43" t="s">
@@ -2168,20 +2168,28 @@
       </c>
       <c r="B29" s="44"/>
       <c r="C29" s="45"/>
-      <c r="D29" s="53"/>
-      <c r="E29" s="46" t="n">
-        <f aca="false">E24</f>
-        <v>618</v>
+      <c r="D29" s="46" t="n">
+        <f aca="false">D27</f>
+        <v>1197.5</v>
+      </c>
+      <c r="E29" s="53" t="n">
+        <f aca="false">E27</f>
+        <v>718</v>
       </c>
       <c r="F29" s="54"/>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="40"/>
-      <c r="B30" s="42"/>
-      <c r="C30" s="55"/>
-      <c r="D30" s="41"/>
-      <c r="E30" s="41"/>
-      <c r="F30" s="42"/>
+      <c r="A30" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="44"/>
+      <c r="C30" s="45"/>
+      <c r="D30" s="53"/>
+      <c r="E30" s="46" t="n">
+        <f aca="false">E25</f>
+        <v>718</v>
+      </c>
+      <c r="F30" s="54"/>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="40"/>
@@ -2328,79 +2336,87 @@
       <c r="F48" s="42"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="56"/>
-      <c r="B49" s="57"/>
-      <c r="C49" s="58"/>
-      <c r="D49" s="51"/>
-      <c r="E49" s="51"/>
-      <c r="F49" s="57"/>
+      <c r="A49" s="40"/>
+      <c r="B49" s="42"/>
+      <c r="C49" s="55"/>
+      <c r="D49" s="41"/>
+      <c r="E49" s="41"/>
+      <c r="F49" s="42"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="59"/>
-      <c r="B50" s="44"/>
-      <c r="C50" s="45"/>
-      <c r="D50" s="53"/>
-      <c r="E50" s="53"/>
-      <c r="F50" s="54"/>
+      <c r="A50" s="56"/>
+      <c r="B50" s="57"/>
+      <c r="C50" s="58"/>
+      <c r="D50" s="51"/>
+      <c r="E50" s="51"/>
+      <c r="F50" s="57"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="60"/>
-      <c r="B51" s="57"/>
-      <c r="C51" s="58"/>
-      <c r="D51" s="51"/>
-      <c r="E51" s="51"/>
-      <c r="F51" s="61"/>
+      <c r="A51" s="59"/>
+      <c r="B51" s="44"/>
+      <c r="C51" s="45"/>
+      <c r="D51" s="53"/>
+      <c r="E51" s="53"/>
+      <c r="F51" s="54"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="62"/>
-      <c r="B52" s="44"/>
-      <c r="C52" s="45"/>
-      <c r="D52" s="63"/>
-      <c r="E52" s="53"/>
-      <c r="F52" s="54"/>
+      <c r="A52" s="60"/>
+      <c r="B52" s="57"/>
+      <c r="C52" s="58"/>
+      <c r="D52" s="51"/>
+      <c r="E52" s="51"/>
+      <c r="F52" s="61"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="64"/>
-      <c r="D53" s="53"/>
-      <c r="E53" s="65"/>
+      <c r="A53" s="62"/>
+      <c r="B53" s="44"/>
+      <c r="C53" s="45"/>
+      <c r="D53" s="63"/>
+      <c r="E53" s="53"/>
       <c r="F53" s="54"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="66"/>
-      <c r="D54" s="67"/>
-      <c r="E54" s="67"/>
-      <c r="F54" s="68"/>
+      <c r="A54" s="64"/>
+      <c r="D54" s="53"/>
+      <c r="E54" s="65"/>
+      <c r="F54" s="54"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="56"/>
-      <c r="B55" s="49"/>
-      <c r="C55" s="50"/>
-      <c r="D55" s="51"/>
-      <c r="E55" s="51"/>
-      <c r="F55" s="57"/>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="69"/>
-      <c r="B57" s="44"/>
-      <c r="C57" s="45"/>
-      <c r="D57" s="53"/>
-      <c r="E57" s="53"/>
-      <c r="F57" s="70"/>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="71"/>
-      <c r="B58" s="49"/>
-      <c r="C58" s="50"/>
-      <c r="F58" s="72"/>
+      <c r="A55" s="66"/>
+      <c r="D55" s="67"/>
+      <c r="E55" s="67"/>
+      <c r="F55" s="68"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="56"/>
+      <c r="B56" s="49"/>
+      <c r="C56" s="50"/>
+      <c r="D56" s="51"/>
+      <c r="E56" s="51"/>
+      <c r="F56" s="57"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="69"/>
+      <c r="B58" s="44"/>
+      <c r="C58" s="45"/>
+      <c r="D58" s="53"/>
+      <c r="E58" s="53"/>
+      <c r="F58" s="70"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="71"/>
+      <c r="B59" s="49"/>
+      <c r="C59" s="50"/>
+      <c r="F59" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A24:C24"/>
     <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A26:C26"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C8" location="'Ticket Cena'!A1" display="🧾 Ver Ticket Cena"/>
@@ -2430,7 +2446,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="73" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B1" s="73"/>
       <c r="C1" s="73"/>
@@ -2447,21 +2463,21 @@
     <row r="3" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="75" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B5" s="76" t="n">
         <v>800</v>
@@ -2478,7 +2494,7 @@
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="75" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B6" s="76" t="n">
         <v>0</v>
@@ -2495,7 +2511,7 @@
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="78" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" s="79" t="n">
         <v>0</v>
@@ -2510,7 +2526,7 @@
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="78" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="79" t="n">
         <v>0</v>
@@ -2525,7 +2541,7 @@
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="80" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" s="81" t="n">
         <v>0</v>
@@ -2542,7 +2558,7 @@
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="75" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B10" s="76" t="n">
         <v>0</v>
@@ -2559,7 +2575,7 @@
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="78" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="79" t="n">
         <v>0</v>
@@ -2574,7 +2590,7 @@
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="83" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12" s="53" t="n">
         <f aca="false">SUM(B5:B11)</f>
@@ -2620,7 +2636,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="73" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B1" s="73"/>
       <c r="C1" s="73"/>
@@ -2631,7 +2647,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="84" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B2" s="84"/>
       <c r="C2" s="84"/>
@@ -2643,25 +2659,25 @@
     <row r="3" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="85" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B4" s="85" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C4" s="85" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D4" s="85" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E4" s="85" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F4" s="85" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G4" s="86" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2669,19 +2685,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="88" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C5" s="89" t="n">
         <v>50</v>
       </c>
       <c r="D5" s="90" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E5" s="89" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="91" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G5" s="92"/>
     </row>
@@ -2701,19 +2717,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="94" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C7" s="95" t="n">
         <v>50</v>
       </c>
       <c r="D7" s="96" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E7" s="95" t="n">
         <v>50</v>
       </c>
       <c r="F7" s="97" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G7" s="98"/>
     </row>
@@ -2722,19 +2738,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="88" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C8" s="89" t="n">
         <v>50</v>
       </c>
       <c r="D8" s="90" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E8" s="89" t="n">
         <v>50</v>
       </c>
       <c r="F8" s="91" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G8" s="92"/>
     </row>
@@ -2743,19 +2759,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="94" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C9" s="95" t="n">
         <v>50</v>
       </c>
       <c r="D9" s="96" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E9" s="95" t="n">
         <v>50</v>
       </c>
       <c r="F9" s="97" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G9" s="98"/>
     </row>
@@ -2764,19 +2780,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="88" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C10" s="89" t="n">
         <v>50</v>
       </c>
       <c r="D10" s="90" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E10" s="89" t="n">
         <v>50</v>
       </c>
       <c r="F10" s="91" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G10" s="92"/>
     </row>
@@ -2785,19 +2801,19 @@
         <v>7</v>
       </c>
       <c r="B11" s="94" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C11" s="95" t="n">
         <v>50</v>
       </c>
       <c r="D11" s="96" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E11" s="95" t="n">
         <v>50</v>
       </c>
       <c r="F11" s="97" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G11" s="98"/>
     </row>
@@ -2806,19 +2822,19 @@
         <v>8</v>
       </c>
       <c r="B12" s="88" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C12" s="89" t="n">
         <v>50</v>
       </c>
       <c r="D12" s="90" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E12" s="89" t="n">
         <v>50</v>
       </c>
       <c r="F12" s="91" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G12" s="92"/>
     </row>
@@ -2827,19 +2843,19 @@
         <v>9</v>
       </c>
       <c r="B13" s="94" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C13" s="95" t="n">
         <v>50</v>
       </c>
       <c r="D13" s="96" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E13" s="95" t="n">
         <v>50</v>
       </c>
       <c r="F13" s="97" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G13" s="98"/>
     </row>
@@ -2848,19 +2864,19 @@
         <v>10</v>
       </c>
       <c r="B14" s="88" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C14" s="89" t="n">
         <v>50</v>
       </c>
       <c r="D14" s="90" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E14" s="89" t="n">
         <v>50</v>
       </c>
       <c r="F14" s="91" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G14" s="92"/>
     </row>
@@ -2869,19 +2885,19 @@
         <v>11</v>
       </c>
       <c r="B15" s="94" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C15" s="95" t="n">
         <v>50</v>
       </c>
       <c r="D15" s="96" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E15" s="95" t="n">
         <v>50</v>
       </c>
       <c r="F15" s="97" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G15" s="98"/>
     </row>
@@ -2890,19 +2906,19 @@
         <v>12</v>
       </c>
       <c r="B16" s="88" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C16" s="89" t="n">
         <v>50</v>
       </c>
       <c r="D16" s="91" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E16" s="89" t="n">
         <v>50</v>
       </c>
       <c r="F16" s="91" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G16" s="92"/>
     </row>
@@ -2911,19 +2927,19 @@
         <v>13</v>
       </c>
       <c r="B17" s="99" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C17" s="100" t="n">
         <v>50</v>
       </c>
       <c r="D17" s="101" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E17" s="100" t="n">
         <v>50</v>
       </c>
       <c r="F17" s="101" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G17" s="102"/>
     </row>
@@ -2932,19 +2948,19 @@
         <v>14</v>
       </c>
       <c r="B18" s="103" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C18" s="104" t="n">
         <v>50</v>
       </c>
       <c r="D18" s="105" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E18" s="104" t="n">
         <v>50</v>
       </c>
       <c r="F18" s="105" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G18" s="106"/>
     </row>
@@ -2953,19 +2969,19 @@
         <v>15</v>
       </c>
       <c r="B19" s="103" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C19" s="104" t="n">
         <v>50</v>
       </c>
       <c r="D19" s="105" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E19" s="104" t="n">
         <v>50</v>
       </c>
       <c r="F19" s="105" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G19" s="107"/>
     </row>
@@ -2974,19 +2990,19 @@
         <v>16</v>
       </c>
       <c r="B20" s="103" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C20" s="104" t="n">
         <v>50</v>
       </c>
       <c r="D20" s="105" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E20" s="104" t="n">
         <v>50</v>
       </c>
       <c r="F20" s="105" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G20" s="98"/>
     </row>
@@ -2995,19 +3011,19 @@
         <v>17</v>
       </c>
       <c r="B21" s="103" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C21" s="104" t="n">
         <v>50</v>
       </c>
       <c r="D21" s="105" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E21" s="104" t="n">
         <v>50</v>
       </c>
       <c r="F21" s="105" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G21" s="107"/>
     </row>
@@ -3049,7 +3065,7 @@
     </row>
     <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="109" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B26" s="109"/>
       <c r="C26" s="110" t="n">
@@ -3388,12 +3404,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="114" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="115" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="409.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3422,12 +3438,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="114" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="115" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="379.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3456,12 +3472,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="116" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="117" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="379.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3491,91 +3507,91 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="118" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="117" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="117" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="117" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B20" s="1" t="n">
         <v>280</v>
@@ -3583,7 +3599,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B21" s="1" t="n">
         <v>28</v>
@@ -3591,7 +3607,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="119" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B22" s="119" t="n">
         <v>308</v>
@@ -3599,17 +3615,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/LibroCuentas_PTP_2026.xlsx
+++ b/LibroCuentas_PTP_2026.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="104">
   <si>
     <t xml:space="preserve">PEÑA TAURINA PEGUERINOS</t>
   </si>
@@ -1483,9 +1483,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>3323160</xdr:colOff>
+      <xdr:colOff>3322800</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>123120</xdr:rowOff>
+      <xdr:rowOff>122760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1499,7 +1499,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="600120"/>
-          <a:ext cx="3323160" cy="5704560"/>
+          <a:ext cx="3322800" cy="5704200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1525,9 +1525,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>65880</xdr:colOff>
+      <xdr:colOff>65520</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>4752000</xdr:rowOff>
+      <xdr:rowOff>4751640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1541,7 +1541,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="600120"/>
-          <a:ext cx="5704560" cy="4752000"/>
+          <a:ext cx="5704200" cy="4751640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1567,9 +1567,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>3612600</xdr:colOff>
+      <xdr:colOff>3612240</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>4741200</xdr:rowOff>
+      <xdr:rowOff>4740840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1583,7 +1583,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="566640"/>
-          <a:ext cx="3612600" cy="4755600"/>
+          <a:ext cx="3612240" cy="4755240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1778,7 +1778,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
@@ -2104,108 +2104,118 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="36" t="s">
+      <c r="A25" s="33" t="n">
+        <v>46256</v>
+      </c>
+      <c r="B25" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="34"/>
+      <c r="D25" s="35" t="n">
+        <v>34</v>
+      </c>
+      <c r="E25" s="34"/>
+    </row>
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="33" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B26" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="34"/>
+      <c r="D26" s="35" t="n">
+        <v>34</v>
+      </c>
+      <c r="E26" s="34"/>
+    </row>
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="36"/>
-      <c r="C25" s="36"/>
-      <c r="D25" s="37" t="n">
-        <f aca="false">SUM(D6:D24)</f>
-        <v>1197.5</v>
-      </c>
-      <c r="E25" s="38" t="n">
-        <f aca="false">SUM(E6:E24)</f>
+      <c r="B27" s="36"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="37" t="n">
+        <f aca="false">SUM(D6:D26)</f>
+        <v>1265.5</v>
+      </c>
+      <c r="E27" s="38" t="n">
+        <f aca="false">SUM(E6:E26)</f>
         <v>718</v>
       </c>
-      <c r="F25" s="39" t="n">
-        <f aca="false">D25-E25</f>
-        <v>479.5</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="40"/>
-      <c r="B26" s="40"/>
-      <c r="C26" s="40"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="42"/>
-    </row>
-    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="B27" s="44"/>
-      <c r="C27" s="45"/>
-      <c r="D27" s="46" t="n">
-        <f aca="false">SUM(D6:D24)</f>
-        <v>1197.5</v>
-      </c>
-      <c r="E27" s="46" t="n">
-        <f aca="false">SUM(E6:E24)</f>
-        <v>718</v>
-      </c>
-      <c r="F27" s="47" t="n">
+      <c r="F27" s="39" t="n">
         <f aca="false">D27-E27</f>
-        <v>479.5</v>
+        <v>547.5</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="B28" s="49"/>
-      <c r="C28" s="50"/>
-      <c r="D28" s="51"/>
-      <c r="E28" s="51"/>
-      <c r="F28" s="52" t="n">
-        <f aca="false">D27-E27</f>
-        <v>479.5</v>
-      </c>
+      <c r="A28" s="40"/>
+      <c r="B28" s="40"/>
+      <c r="C28" s="40"/>
+      <c r="D28" s="41"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="42"/>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="43" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B29" s="44"/>
       <c r="C29" s="45"/>
       <c r="D29" s="46" t="n">
-        <f aca="false">D27</f>
-        <v>1197.5</v>
-      </c>
-      <c r="E29" s="53" t="n">
+        <f aca="false">SUM(D6:D26)</f>
+        <v>1265.5</v>
+      </c>
+      <c r="E29" s="46" t="n">
+        <f aca="false">SUM(E6:E26)</f>
+        <v>718</v>
+      </c>
+      <c r="F29" s="47" t="n">
+        <f aca="false">D29-E29</f>
+        <v>547.5</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" s="49"/>
+      <c r="C30" s="50"/>
+      <c r="D30" s="51"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="52" t="n">
+        <f aca="false">D29-E29</f>
+        <v>547.5</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="43" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" s="44"/>
+      <c r="C31" s="45"/>
+      <c r="D31" s="46" t="n">
+        <f aca="false">D29</f>
+        <v>1265.5</v>
+      </c>
+      <c r="E31" s="53" t="n">
+        <f aca="false">E29</f>
+        <v>718</v>
+      </c>
+      <c r="F31" s="54"/>
+    </row>
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="B32" s="44"/>
+      <c r="C32" s="45"/>
+      <c r="D32" s="53"/>
+      <c r="E32" s="46" t="n">
         <f aca="false">E27</f>
         <v>718</v>
       </c>
-      <c r="F29" s="54"/>
-    </row>
-    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="43" t="s">
-        <v>29</v>
-      </c>
-      <c r="B30" s="44"/>
-      <c r="C30" s="45"/>
-      <c r="D30" s="53"/>
-      <c r="E30" s="46" t="n">
-        <f aca="false">E25</f>
-        <v>718</v>
-      </c>
-      <c r="F30" s="54"/>
-    </row>
-    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="40"/>
-      <c r="B31" s="42"/>
-      <c r="C31" s="55"/>
-      <c r="D31" s="41"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="42"/>
-    </row>
-    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="40"/>
-      <c r="B32" s="42"/>
-      <c r="C32" s="55"/>
-      <c r="D32" s="41"/>
-      <c r="E32" s="41"/>
-      <c r="F32" s="42"/>
+      <c r="F32" s="54"/>
     </row>
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="40"/>
@@ -2344,79 +2354,95 @@
       <c r="F49" s="42"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="56"/>
-      <c r="B50" s="57"/>
-      <c r="C50" s="58"/>
-      <c r="D50" s="51"/>
-      <c r="E50" s="51"/>
-      <c r="F50" s="57"/>
+      <c r="A50" s="40"/>
+      <c r="B50" s="42"/>
+      <c r="C50" s="55"/>
+      <c r="D50" s="41"/>
+      <c r="E50" s="41"/>
+      <c r="F50" s="42"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="59"/>
-      <c r="B51" s="44"/>
-      <c r="C51" s="45"/>
-      <c r="D51" s="53"/>
-      <c r="E51" s="53"/>
-      <c r="F51" s="54"/>
+      <c r="A51" s="40"/>
+      <c r="B51" s="42"/>
+      <c r="C51" s="55"/>
+      <c r="D51" s="41"/>
+      <c r="E51" s="41"/>
+      <c r="F51" s="42"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="60"/>
+      <c r="A52" s="56"/>
       <c r="B52" s="57"/>
       <c r="C52" s="58"/>
       <c r="D52" s="51"/>
       <c r="E52" s="51"/>
-      <c r="F52" s="61"/>
+      <c r="F52" s="57"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="62"/>
+      <c r="A53" s="59"/>
       <c r="B53" s="44"/>
       <c r="C53" s="45"/>
-      <c r="D53" s="63"/>
+      <c r="D53" s="53"/>
       <c r="E53" s="53"/>
       <c r="F53" s="54"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="64"/>
-      <c r="D54" s="53"/>
-      <c r="E54" s="65"/>
-      <c r="F54" s="54"/>
+      <c r="A54" s="60"/>
+      <c r="B54" s="57"/>
+      <c r="C54" s="58"/>
+      <c r="D54" s="51"/>
+      <c r="E54" s="51"/>
+      <c r="F54" s="61"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="66"/>
-      <c r="D55" s="67"/>
-      <c r="E55" s="67"/>
-      <c r="F55" s="68"/>
+      <c r="A55" s="62"/>
+      <c r="B55" s="44"/>
+      <c r="C55" s="45"/>
+      <c r="D55" s="63"/>
+      <c r="E55" s="53"/>
+      <c r="F55" s="54"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="56"/>
-      <c r="B56" s="49"/>
-      <c r="C56" s="50"/>
-      <c r="D56" s="51"/>
-      <c r="E56" s="51"/>
-      <c r="F56" s="57"/>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="A56" s="64"/>
+      <c r="D56" s="53"/>
+      <c r="E56" s="65"/>
+      <c r="F56" s="54"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="66"/>
+      <c r="D57" s="67"/>
+      <c r="E57" s="67"/>
+      <c r="F57" s="68"/>
+    </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="69"/>
-      <c r="B58" s="44"/>
-      <c r="C58" s="45"/>
-      <c r="D58" s="53"/>
-      <c r="E58" s="53"/>
-      <c r="F58" s="70"/>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="71"/>
-      <c r="B59" s="49"/>
-      <c r="C59" s="50"/>
-      <c r="F59" s="72"/>
+      <c r="A58" s="56"/>
+      <c r="B58" s="49"/>
+      <c r="C58" s="50"/>
+      <c r="D58" s="51"/>
+      <c r="E58" s="51"/>
+      <c r="F58" s="57"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="69"/>
+      <c r="B60" s="44"/>
+      <c r="C60" s="45"/>
+      <c r="D60" s="53"/>
+      <c r="E60" s="53"/>
+      <c r="F60" s="70"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="71"/>
+      <c r="B61" s="49"/>
+      <c r="C61" s="50"/>
+      <c r="F61" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A28:C28"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C8" location="'Ticket Cena'!A1" display="🧾 Ver Ticket Cena"/>
